--- a/excel/机型库-根据算法部修改-回放信号.xlsx
+++ b/excel/机型库-根据算法部修改-回放信号.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ancha\Desktop\1.3-测试251-好用数据\lz_engine_autotest-加速用-设备1-235\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ancha\Desktop\1.3-测试251-好用数据\lz_engine_autotest\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7756" uniqueCount="2624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7774" uniqueCount="2624">
   <si>
     <t>ID (命名：协议-子协议-品牌-机型-频段-详细频率)</t>
   </si>
@@ -8280,7 +8280,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AD539"/>
   <sheetFormatPr defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -8377,7 +8376,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>29</v>
@@ -8421,7 +8420,7 @@
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
     </row>
-    <row r="3" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>29</v>
@@ -8467,7 +8466,7 @@
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
     </row>
-    <row r="4" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>29</v>
@@ -8511,7 +8510,7 @@
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
     </row>
-    <row r="5" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>29</v>
@@ -8555,7 +8554,7 @@
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
     </row>
-    <row r="6" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>29</v>
@@ -8599,7 +8598,7 @@
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
     </row>
-    <row r="7" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>29</v>
@@ -8643,7 +8642,7 @@
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
     </row>
-    <row r="8" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>29</v>
@@ -8685,7 +8684,7 @@
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
     </row>
-    <row r="9" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
         <v>29</v>
@@ -8729,7 +8728,7 @@
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
     </row>
-    <row r="10" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
         <v>29</v>
@@ -8799,7 +8798,7 @@
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
     </row>
-    <row r="11" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>29</v>
@@ -8871,7 +8870,7 @@
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
     </row>
-    <row r="12" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
         <v>29</v>
@@ -8943,7 +8942,7 @@
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
     </row>
-    <row r="13" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
         <v>29</v>
@@ -9017,7 +9016,7 @@
       <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
     </row>
-    <row r="14" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
         <v>29</v>
@@ -9061,7 +9060,7 @@
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
     </row>
-    <row r="15" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
         <v>29</v>
@@ -9105,7 +9104,7 @@
       <c r="AC15" s="1"/>
       <c r="AD15" s="1"/>
     </row>
-    <row r="16" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
         <v>29</v>
@@ -9149,7 +9148,7 @@
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
     </row>
-    <row r="17" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
         <v>29</v>
@@ -9193,7 +9192,7 @@
       <c r="AC17" s="1"/>
       <c r="AD17" s="1"/>
     </row>
-    <row r="18" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>29</v>
@@ -9237,7 +9236,7 @@
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
     </row>
-    <row r="19" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
         <v>29</v>
@@ -9295,7 +9294,7 @@
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
     </row>
-    <row r="20" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
         <v>29</v>
@@ -9353,7 +9352,7 @@
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
     </row>
-    <row r="21" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
         <v>29</v>
@@ -9411,7 +9410,7 @@
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
     </row>
-    <row r="22" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
         <v>29</v>
@@ -9469,7 +9468,7 @@
       <c r="AC22" s="1"/>
       <c r="AD22" s="1"/>
     </row>
-    <row r="23" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
         <v>29</v>
@@ -9527,7 +9526,7 @@
       <c r="AC23" s="1"/>
       <c r="AD23" s="1"/>
     </row>
-    <row r="24" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
         <v>29</v>
@@ -9591,7 +9590,7 @@
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
     </row>
-    <row r="25" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
         <v>29</v>
@@ -9641,7 +9640,7 @@
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
     </row>
-    <row r="26" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
         <v>29</v>
@@ -9685,7 +9684,7 @@
       <c r="AC26" s="1"/>
       <c r="AD26" s="1"/>
     </row>
-    <row r="27" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
         <v>29</v>
@@ -9729,7 +9728,7 @@
       <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
     </row>
-    <row r="28" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
         <v>29</v>
@@ -9773,7 +9772,7 @@
       <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
     </row>
-    <row r="29" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
         <v>29</v>
@@ -9845,7 +9844,7 @@
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
     </row>
-    <row r="30" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
         <v>29</v>
@@ -9917,7 +9916,7 @@
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
     </row>
-    <row r="31" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
         <v>29</v>
@@ -9989,7 +9988,7 @@
       <c r="AC31" s="1"/>
       <c r="AD31" s="1"/>
     </row>
-    <row r="32" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
         <v>29</v>
@@ -10033,7 +10032,7 @@
       <c r="AC32" s="1"/>
       <c r="AD32" s="1"/>
     </row>
-    <row r="33" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
         <v>29</v>
@@ -10077,7 +10076,7 @@
       <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
     </row>
-    <row r="34" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
         <v>29</v>
@@ -10149,7 +10148,7 @@
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
     </row>
-    <row r="35" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="1" t="s">
         <v>29</v>
@@ -10221,7 +10220,7 @@
       <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
     </row>
-    <row r="36" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
         <v>29</v>
@@ -10295,7 +10294,7 @@
       <c r="AC36" s="1"/>
       <c r="AD36" s="1"/>
     </row>
-    <row r="37" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
         <v>29</v>
@@ -10369,7 +10368,7 @@
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
     </row>
-    <row r="38" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
         <v>29</v>
@@ -10413,7 +10412,7 @@
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
     </row>
-    <row r="39" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1" t="s">
         <v>29</v>
@@ -10457,7 +10456,7 @@
       <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
     </row>
-    <row r="40" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1" t="s">
         <v>29</v>
@@ -10501,7 +10500,7 @@
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
     </row>
-    <row r="41" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
         <v>29</v>
@@ -10545,7 +10544,7 @@
       <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
     </row>
-    <row r="42" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
         <v>29</v>
@@ -10615,7 +10614,7 @@
       <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
     </row>
-    <row r="43" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
         <v>29</v>
@@ -10685,7 +10684,7 @@
       <c r="AC43" s="1"/>
       <c r="AD43" s="1"/>
     </row>
-    <row r="44" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="s">
         <v>29</v>
@@ -10759,7 +10758,7 @@
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
     </row>
-    <row r="45" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="1" t="s">
         <v>29</v>
@@ -10803,7 +10802,7 @@
       <c r="AC45" s="1"/>
       <c r="AD45" s="1"/>
     </row>
-    <row r="46" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="1" t="s">
         <v>29</v>
@@ -10847,7 +10846,7 @@
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
     </row>
-    <row r="47" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
       <c r="B47" s="1" t="s">
         <v>29</v>
@@ -10919,7 +10918,7 @@
       <c r="AC47" s="1"/>
       <c r="AD47" s="1"/>
     </row>
-    <row r="48" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
         <v>29</v>
@@ -10991,7 +10990,7 @@
       <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
     </row>
-    <row r="49" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="1" t="s">
         <v>29</v>
@@ -11035,7 +11034,7 @@
       <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
     </row>
-    <row r="50" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
         <v>29</v>
@@ -11079,7 +11078,7 @@
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
     </row>
-    <row r="51" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1"/>
       <c r="B51" s="1" t="s">
         <v>29</v>
@@ -11123,7 +11122,7 @@
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
     </row>
-    <row r="52" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
       <c r="B52" s="1" t="s">
         <v>29</v>
@@ -11167,7 +11166,7 @@
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
     </row>
-    <row r="53" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="1" t="s">
         <v>29</v>
@@ -11211,7 +11210,7 @@
       <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
     </row>
-    <row r="54" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
         <v>29</v>
@@ -11255,7 +11254,7 @@
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
     </row>
-    <row r="55" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
         <v>29</v>
@@ -11299,7 +11298,7 @@
       <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
     </row>
-    <row r="56" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
         <v>29</v>
@@ -11343,7 +11342,7 @@
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
     </row>
-    <row r="57" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1" t="s">
         <v>29</v>
@@ -11387,7 +11386,7 @@
       <c r="AC57" s="1"/>
       <c r="AD57" s="1"/>
     </row>
-    <row r="58" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1" t="s">
         <v>29</v>
@@ -11431,7 +11430,7 @@
       <c r="AC58" s="1"/>
       <c r="AD58" s="1"/>
     </row>
-    <row r="59" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1" t="s">
         <v>29</v>
@@ -11475,7 +11474,7 @@
       <c r="AC59" s="1"/>
       <c r="AD59" s="1"/>
     </row>
-    <row r="60" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1" t="s">
         <v>29</v>
@@ -11549,7 +11548,7 @@
       </c>
       <c r="AD60" s="1"/>
     </row>
-    <row r="61" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
       <c r="B61" s="1" t="s">
         <v>29</v>
@@ -11623,7 +11622,7 @@
       <c r="AC61" s="1"/>
       <c r="AD61" s="1"/>
     </row>
-    <row r="62" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="1" t="s">
         <v>29</v>
@@ -11695,7 +11694,7 @@
       <c r="AC62" s="1"/>
       <c r="AD62" s="1"/>
     </row>
-    <row r="63" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="1" t="s">
         <v>29</v>
@@ -11739,7 +11738,7 @@
       <c r="AC63" s="1"/>
       <c r="AD63" s="1"/>
     </row>
-    <row r="64" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
       <c r="B64" s="1" t="s">
         <v>29</v>
@@ -11811,7 +11810,7 @@
       <c r="AC64" s="1"/>
       <c r="AD64" s="1"/>
     </row>
-    <row r="65" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1" t="s">
         <v>29</v>
@@ -11883,7 +11882,7 @@
       <c r="AC65" s="1"/>
       <c r="AD65" s="1"/>
     </row>
-    <row r="66" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="1" t="s">
         <v>29</v>
@@ -11927,7 +11926,7 @@
       <c r="AC66" s="1"/>
       <c r="AD66" s="1"/>
     </row>
-    <row r="67" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="1" t="s">
         <v>29</v>
@@ -11971,7 +11970,7 @@
       <c r="AC67" s="1"/>
       <c r="AD67" s="1"/>
     </row>
-    <row r="68" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1" t="s">
         <v>29</v>
@@ -12015,7 +12014,7 @@
       <c r="AC68" s="1"/>
       <c r="AD68" s="1"/>
     </row>
-    <row r="69" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="B69" s="1" t="s">
         <v>29</v>
@@ -12059,7 +12058,7 @@
       <c r="AC69" s="1"/>
       <c r="AD69" s="1"/>
     </row>
-    <row r="70" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="1" t="s">
         <v>254</v>
@@ -12117,7 +12116,7 @@
       <c r="AC70" s="1"/>
       <c r="AD70" s="1"/>
     </row>
-    <row r="71" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
       <c r="B71" s="1" t="s">
         <v>254</v>
@@ -12173,7 +12172,7 @@
       <c r="AC71" s="1"/>
       <c r="AD71" s="1"/>
     </row>
-    <row r="72" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
       <c r="B72" s="1" t="s">
         <v>254</v>
@@ -12231,7 +12230,7 @@
       <c r="AC72" s="1"/>
       <c r="AD72" s="1"/>
     </row>
-    <row r="73" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1" t="s">
         <v>254</v>
@@ -12287,7 +12286,7 @@
       <c r="AC73" s="1"/>
       <c r="AD73" s="1"/>
     </row>
-    <row r="74" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="1" t="s">
         <v>254</v>
@@ -12349,7 +12348,7 @@
       <c r="AC74" s="1"/>
       <c r="AD74" s="1"/>
     </row>
-    <row r="75" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="1" t="s">
         <v>254</v>
@@ -12393,7 +12392,7 @@
       <c r="AC75" s="1"/>
       <c r="AD75" s="1"/>
     </row>
-    <row r="76" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="1" t="s">
         <v>254</v>
@@ -12437,7 +12436,7 @@
       <c r="AC76" s="1"/>
       <c r="AD76" s="1"/>
     </row>
-    <row r="77" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="1" t="s">
         <v>254</v>
@@ -12509,7 +12508,7 @@
       <c r="AC77" s="1"/>
       <c r="AD77" s="1"/>
     </row>
-    <row r="78" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="1" t="s">
         <v>254</v>
@@ -12559,7 +12558,7 @@
       <c r="AC78" s="1"/>
       <c r="AD78" s="1"/>
     </row>
-    <row r="79" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="1" t="s">
         <v>254</v>
@@ -12603,7 +12602,7 @@
       <c r="AC79" s="1"/>
       <c r="AD79" s="1"/>
     </row>
-    <row r="80" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="1" t="s">
         <v>254</v>
@@ -12671,7 +12670,7 @@
       </c>
       <c r="AD80" s="1"/>
     </row>
-    <row r="81" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="1" t="s">
         <v>254</v>
@@ -12715,7 +12714,7 @@
       <c r="AC81" s="1"/>
       <c r="AD81" s="1"/>
     </row>
-    <row r="82" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1" t="s">
         <v>254</v>
@@ -12759,7 +12758,7 @@
       <c r="AC82" s="1"/>
       <c r="AD82" s="1"/>
     </row>
-    <row r="83" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="1" t="s">
         <v>254</v>
@@ -12803,7 +12802,7 @@
       <c r="AC83" s="1"/>
       <c r="AD83" s="1"/>
     </row>
-    <row r="84" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="1" t="s">
         <v>254</v>
@@ -12869,7 +12868,7 @@
       <c r="AC84" s="1"/>
       <c r="AD84" s="1"/>
     </row>
-    <row r="85" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="1" t="s">
         <v>254</v>
@@ -12929,7 +12928,7 @@
       <c r="AC85" s="1"/>
       <c r="AD85" s="1"/>
     </row>
-    <row r="86" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="1" t="s">
         <v>254</v>
@@ -12993,7 +12992,7 @@
       </c>
       <c r="AD86" s="1"/>
     </row>
-    <row r="87" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="1" t="s">
         <v>254</v>
@@ -13057,7 +13056,7 @@
       <c r="AC87" s="1"/>
       <c r="AD87" s="1"/>
     </row>
-    <row r="88" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="1" t="s">
         <v>328</v>
@@ -13129,7 +13128,7 @@
       <c r="AC88" s="1"/>
       <c r="AD88" s="1"/>
     </row>
-    <row r="89" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="1" t="s">
         <v>328</v>
@@ -13201,7 +13200,7 @@
       <c r="AC89" s="1"/>
       <c r="AD89" s="1"/>
     </row>
-    <row r="90" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="1" t="s">
         <v>328</v>
@@ -13273,7 +13272,7 @@
       <c r="AC90" s="1"/>
       <c r="AD90" s="1"/>
     </row>
-    <row r="91" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="1" t="s">
         <v>328</v>
@@ -13345,7 +13344,7 @@
       <c r="AC91" s="1"/>
       <c r="AD91" s="1"/>
     </row>
-    <row r="92" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="1" t="s">
         <v>328</v>
@@ -13389,7 +13388,7 @@
       <c r="AC92" s="1"/>
       <c r="AD92" s="1"/>
     </row>
-    <row r="93" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="1" t="s">
         <v>328</v>
@@ -13459,7 +13458,7 @@
       <c r="AC93" s="1"/>
       <c r="AD93" s="1"/>
     </row>
-    <row r="94" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1" t="s">
         <v>367</v>
@@ -13531,7 +13530,7 @@
       <c r="AC94" s="1"/>
       <c r="AD94" s="1"/>
     </row>
-    <row r="95" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1" t="s">
         <v>367</v>
@@ -13603,7 +13602,7 @@
       <c r="AC95" s="1"/>
       <c r="AD95" s="1"/>
     </row>
-    <row r="96" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1" t="s">
         <v>367</v>
@@ -13675,7 +13674,7 @@
       <c r="AC96" s="1"/>
       <c r="AD96" s="1"/>
     </row>
-    <row r="97" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="B97" s="1" t="s">
         <v>367</v>
@@ -13747,7 +13746,7 @@
       <c r="AC97" s="1"/>
       <c r="AD97" s="1"/>
     </row>
-    <row r="98" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1" t="s">
         <v>367</v>
@@ -13819,7 +13818,7 @@
       <c r="AC98" s="1"/>
       <c r="AD98" s="1"/>
     </row>
-    <row r="99" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1" t="s">
         <v>367</v>
@@ -13879,7 +13878,7 @@
       <c r="AC99" s="1"/>
       <c r="AD99" s="1"/>
     </row>
-    <row r="100" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1" t="s">
         <v>367</v>
@@ -13951,7 +13950,7 @@
       <c r="AC100" s="1"/>
       <c r="AD100" s="1"/>
     </row>
-    <row r="101" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1" t="s">
         <v>412</v>
@@ -14023,7 +14022,7 @@
       <c r="AC101" s="1"/>
       <c r="AD101" s="1"/>
     </row>
-    <row r="102" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1" t="s">
         <v>412</v>
@@ -14095,7 +14094,7 @@
       <c r="AC102" s="1"/>
       <c r="AD102" s="1"/>
     </row>
-    <row r="103" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1" t="s">
         <v>412</v>
@@ -14167,7 +14166,7 @@
       <c r="AC103" s="1"/>
       <c r="AD103" s="1"/>
     </row>
-    <row r="104" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1" t="s">
         <v>430</v>
@@ -14239,7 +14238,7 @@
       <c r="AC104" s="1"/>
       <c r="AD104" s="1"/>
     </row>
-    <row r="105" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1" t="s">
         <v>430</v>
@@ -14311,7 +14310,7 @@
       <c r="AC105" s="1"/>
       <c r="AD105" s="1"/>
     </row>
-    <row r="106" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1" t="s">
         <v>430</v>
@@ -14383,7 +14382,7 @@
       <c r="AC106" s="1"/>
       <c r="AD106" s="1"/>
     </row>
-    <row r="107" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1" t="s">
         <v>430</v>
@@ -14443,7 +14442,7 @@
       <c r="AC107" s="1"/>
       <c r="AD107" s="1"/>
     </row>
-    <row r="108" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1" t="s">
         <v>462</v>
@@ -14515,7 +14514,7 @@
       <c r="AC108" s="1"/>
       <c r="AD108" s="1"/>
     </row>
-    <row r="109" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1" t="s">
         <v>474</v>
@@ -14581,7 +14580,7 @@
       <c r="AC109" s="1"/>
       <c r="AD109" s="1"/>
     </row>
-    <row r="110" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1" t="s">
         <v>474</v>
@@ -14653,7 +14652,7 @@
       <c r="AC110" s="1"/>
       <c r="AD110" s="1"/>
     </row>
-    <row r="111" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1" t="s">
         <v>487</v>
@@ -14725,7 +14724,7 @@
       <c r="AC111" s="1"/>
       <c r="AD111" s="1"/>
     </row>
-    <row r="112" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1" t="s">
         <v>496</v>
@@ -14769,7 +14768,7 @@
       <c r="AC112" s="1"/>
       <c r="AD112" s="1"/>
     </row>
-    <row r="113" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1" t="s">
         <v>499</v>
@@ -14841,7 +14840,7 @@
       <c r="AC113" s="1"/>
       <c r="AD113" s="1"/>
     </row>
-    <row r="114" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1" t="s">
         <v>499</v>
@@ -14901,7 +14900,7 @@
       <c r="AC114" s="1"/>
       <c r="AD114" s="1"/>
     </row>
-    <row r="115" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1" t="s">
         <v>499</v>
@@ -14945,7 +14944,7 @@
       <c r="AC115" s="1"/>
       <c r="AD115" s="1"/>
     </row>
-    <row r="116" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1" t="s">
         <v>499</v>
@@ -15017,7 +15016,7 @@
       <c r="AC116" s="1"/>
       <c r="AD116" s="1"/>
     </row>
-    <row r="117" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1" t="s">
         <v>499</v>
@@ -15089,7 +15088,7 @@
       <c r="AC117" s="1"/>
       <c r="AD117" s="1"/>
     </row>
-    <row r="118" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1" t="s">
         <v>499</v>
@@ -15163,7 +15162,7 @@
       <c r="AC118" s="1"/>
       <c r="AD118" s="1"/>
     </row>
-    <row r="119" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1" t="s">
         <v>545</v>
@@ -15235,7 +15234,7 @@
       <c r="AC119" s="1"/>
       <c r="AD119" s="1"/>
     </row>
-    <row r="120" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1" t="s">
         <v>545</v>
@@ -15279,7 +15278,7 @@
       <c r="AC120" s="1"/>
       <c r="AD120" s="1"/>
     </row>
-    <row r="121" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1" t="s">
         <v>545</v>
@@ -15351,7 +15350,7 @@
       <c r="AC121" s="1"/>
       <c r="AD121" s="1"/>
     </row>
-    <row r="122" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1" t="s">
         <v>545</v>
@@ -15425,7 +15424,7 @@
       <c r="AC122" s="1"/>
       <c r="AD122" s="1"/>
     </row>
-    <row r="123" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1" t="s">
         <v>545</v>
@@ -15497,7 +15496,7 @@
       <c r="AC123" s="1"/>
       <c r="AD123" s="1"/>
     </row>
-    <row r="124" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1" t="s">
         <v>545</v>
@@ -15541,7 +15540,7 @@
       <c r="AC124" s="1"/>
       <c r="AD124" s="1"/>
     </row>
-    <row r="125" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1" t="s">
         <v>578</v>
@@ -15611,7 +15610,7 @@
       <c r="AC125" s="1"/>
       <c r="AD125" s="1"/>
     </row>
-    <row r="126" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1" t="s">
         <v>578</v>
@@ -15681,7 +15680,7 @@
       <c r="AC126" s="1"/>
       <c r="AD126" s="1"/>
     </row>
-    <row r="127" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1" t="s">
         <v>578</v>
@@ -15755,7 +15754,7 @@
       <c r="AC127" s="1"/>
       <c r="AD127" s="1"/>
     </row>
-    <row r="128" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1" t="s">
         <v>578</v>
@@ -15829,7 +15828,7 @@
       <c r="AC128" s="1"/>
       <c r="AD128" s="1"/>
     </row>
-    <row r="129" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1" t="s">
         <v>578</v>
@@ -15899,7 +15898,7 @@
       <c r="AC129" s="1"/>
       <c r="AD129" s="1"/>
     </row>
-    <row r="130" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1" t="s">
         <v>578</v>
@@ -15969,7 +15968,7 @@
       <c r="AC130" s="1"/>
       <c r="AD130" s="1"/>
     </row>
-    <row r="131" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1" t="s">
         <v>578</v>
@@ -16013,7 +16012,7 @@
       <c r="AC131" s="1"/>
       <c r="AD131" s="1"/>
     </row>
-    <row r="132" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1" t="s">
         <v>578</v>
@@ -16083,7 +16082,7 @@
       <c r="AC132" s="1"/>
       <c r="AD132" s="1"/>
     </row>
-    <row r="133" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1" t="s">
         <v>578</v>
@@ -16153,7 +16152,7 @@
       <c r="AC133" s="1"/>
       <c r="AD133" s="1"/>
     </row>
-    <row r="134" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1" t="s">
         <v>578</v>
@@ -16223,7 +16222,7 @@
       <c r="AC134" s="1"/>
       <c r="AD134" s="1"/>
     </row>
-    <row r="135" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1" t="s">
         <v>578</v>
@@ -16295,7 +16294,7 @@
       <c r="AC135" s="1"/>
       <c r="AD135" s="1"/>
     </row>
-    <row r="136" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1" t="s">
         <v>578</v>
@@ -16365,7 +16364,7 @@
       <c r="AC136" s="1"/>
       <c r="AD136" s="1"/>
     </row>
-    <row r="137" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1" t="s">
         <v>578</v>
@@ -16435,7 +16434,7 @@
       <c r="AC137" s="1"/>
       <c r="AD137" s="1"/>
     </row>
-    <row r="138" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1" t="s">
         <v>578</v>
@@ -16499,7 +16498,7 @@
       <c r="AC138" s="1"/>
       <c r="AD138" s="1"/>
     </row>
-    <row r="139" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1" t="s">
         <v>578</v>
@@ -16559,7 +16558,7 @@
       <c r="AC139" s="1"/>
       <c r="AD139" s="1"/>
     </row>
-    <row r="140" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1" t="s">
         <v>668</v>
@@ -16631,7 +16630,7 @@
       <c r="AC140" s="1"/>
       <c r="AD140" s="1"/>
     </row>
-    <row r="141" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1" t="s">
         <v>668</v>
@@ -16707,7 +16706,7 @@
       <c r="AC141" s="1"/>
       <c r="AD141" s="1"/>
     </row>
-    <row r="142" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1" t="s">
         <v>668</v>
@@ -16779,7 +16778,7 @@
       <c r="AC142" s="1"/>
       <c r="AD142" s="1"/>
     </row>
-    <row r="143" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1" t="s">
         <v>668</v>
@@ -16851,7 +16850,7 @@
       <c r="AC143" s="1"/>
       <c r="AD143" s="1"/>
     </row>
-    <row r="144" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1" t="s">
         <v>702</v>
@@ -16923,7 +16922,7 @@
       <c r="AC144" s="1"/>
       <c r="AD144" s="1"/>
     </row>
-    <row r="145" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1" t="s">
         <v>702</v>
@@ -16995,7 +16994,7 @@
       <c r="AC145" s="1"/>
       <c r="AD145" s="1"/>
     </row>
-    <row r="146" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1" t="s">
         <v>702</v>
@@ -17067,7 +17066,7 @@
       <c r="AC146" s="1"/>
       <c r="AD146" s="1"/>
     </row>
-    <row r="147" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1" t="s">
         <v>702</v>
@@ -17139,7 +17138,7 @@
       <c r="AC147" s="1"/>
       <c r="AD147" s="1"/>
     </row>
-    <row r="148" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1" t="s">
         <v>726</v>
@@ -17211,7 +17210,7 @@
       <c r="AC148" s="1"/>
       <c r="AD148" s="1"/>
     </row>
-    <row r="149" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1" t="s">
         <v>726</v>
@@ -17255,7 +17254,7 @@
       <c r="AC149" s="1"/>
       <c r="AD149" s="1"/>
     </row>
-    <row r="150" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1" t="s">
         <v>726</v>
@@ -17327,7 +17326,7 @@
       <c r="AC150" s="1"/>
       <c r="AD150" s="1"/>
     </row>
-    <row r="151" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1" t="s">
         <v>726</v>
@@ -17391,7 +17390,7 @@
       <c r="AC151" s="1"/>
       <c r="AD151" s="1"/>
     </row>
-    <row r="152" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1" t="s">
         <v>749</v>
@@ -17463,7 +17462,7 @@
       <c r="AC152" s="1"/>
       <c r="AD152" s="1"/>
     </row>
-    <row r="153" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1" t="s">
         <v>749</v>
@@ -17507,7 +17506,7 @@
       <c r="AC153" s="1"/>
       <c r="AD153" s="1"/>
     </row>
-    <row r="154" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1" t="s">
         <v>749</v>
@@ -17551,7 +17550,7 @@
       <c r="AC154" s="1"/>
       <c r="AD154" s="1"/>
     </row>
-    <row r="155" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1" t="s">
         <v>749</v>
@@ -17595,7 +17594,7 @@
       <c r="AC155" s="1"/>
       <c r="AD155" s="1"/>
     </row>
-    <row r="156" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1" t="s">
         <v>749</v>
@@ -17639,7 +17638,7 @@
       <c r="AC156" s="1"/>
       <c r="AD156" s="1"/>
     </row>
-    <row r="157" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1" t="s">
         <v>749</v>
@@ -17705,7 +17704,7 @@
       <c r="AC157" s="1"/>
       <c r="AD157" s="1"/>
     </row>
-    <row r="158" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1" t="s">
         <v>749</v>
@@ -17771,7 +17770,7 @@
       <c r="AC158" s="1"/>
       <c r="AD158" s="1"/>
     </row>
-    <row r="159" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1" t="s">
         <v>749</v>
@@ -17837,7 +17836,7 @@
       <c r="AC159" s="1"/>
       <c r="AD159" s="1"/>
     </row>
-    <row r="160" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1" t="s">
         <v>777</v>
@@ -17909,7 +17908,7 @@
       <c r="AC160" s="1"/>
       <c r="AD160" s="1"/>
     </row>
-    <row r="161" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1" t="s">
         <v>777</v>
@@ -17981,7 +17980,7 @@
       <c r="AC161" s="1"/>
       <c r="AD161" s="1"/>
     </row>
-    <row r="162" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1" t="s">
         <v>777</v>
@@ -18053,7 +18052,7 @@
       <c r="AC162" s="1"/>
       <c r="AD162" s="1"/>
     </row>
-    <row r="163" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1" t="s">
         <v>777</v>
@@ -18125,7 +18124,7 @@
       <c r="AC163" s="1"/>
       <c r="AD163" s="1"/>
     </row>
-    <row r="164" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1" t="s">
         <v>777</v>
@@ -18197,7 +18196,7 @@
       <c r="AC164" s="1"/>
       <c r="AD164" s="1"/>
     </row>
-    <row r="165" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1" t="s">
         <v>777</v>
@@ -18269,7 +18268,7 @@
       <c r="AC165" s="1"/>
       <c r="AD165" s="1"/>
     </row>
-    <row r="166" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1" t="s">
         <v>777</v>
@@ -18341,7 +18340,7 @@
       <c r="AC166" s="1"/>
       <c r="AD166" s="1"/>
     </row>
-    <row r="167" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1" t="s">
         <v>777</v>
@@ -18413,7 +18412,7 @@
       <c r="AC167" s="1"/>
       <c r="AD167" s="1"/>
     </row>
-    <row r="168" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1" t="s">
         <v>777</v>
@@ -18485,7 +18484,7 @@
       <c r="AC168" s="1"/>
       <c r="AD168" s="1"/>
     </row>
-    <row r="169" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1" t="s">
         <v>777</v>
@@ -18529,7 +18528,7 @@
       <c r="AC169" s="1"/>
       <c r="AD169" s="1"/>
     </row>
-    <row r="170" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1" t="s">
         <v>777</v>
@@ -18589,7 +18588,7 @@
       <c r="AC170" s="1"/>
       <c r="AD170" s="1"/>
     </row>
-    <row r="171" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1" t="s">
         <v>777</v>
@@ -18633,7 +18632,7 @@
       <c r="AC171" s="1"/>
       <c r="AD171" s="1"/>
     </row>
-    <row r="172" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1" t="s">
         <v>851</v>
@@ -18705,7 +18704,7 @@
       <c r="AC172" s="1"/>
       <c r="AD172" s="1"/>
     </row>
-    <row r="173" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1" t="s">
         <v>851</v>
@@ -18777,7 +18776,7 @@
       <c r="AC173" s="1"/>
       <c r="AD173" s="1"/>
     </row>
-    <row r="174" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1" t="s">
         <v>851</v>
@@ -18849,7 +18848,7 @@
       <c r="AC174" s="1"/>
       <c r="AD174" s="1"/>
     </row>
-    <row r="175" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1" t="s">
         <v>851</v>
@@ -18893,7 +18892,7 @@
       <c r="AC175" s="1"/>
       <c r="AD175" s="1"/>
     </row>
-    <row r="176" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1" t="s">
         <v>851</v>
@@ -18965,7 +18964,7 @@
       <c r="AC176" s="1"/>
       <c r="AD176" s="1"/>
     </row>
-    <row r="177" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1" t="s">
         <v>851</v>
@@ -19037,7 +19036,7 @@
       <c r="AC177" s="1"/>
       <c r="AD177" s="1"/>
     </row>
-    <row r="178" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1" t="s">
         <v>851</v>
@@ -19109,7 +19108,7 @@
       <c r="AC178" s="1"/>
       <c r="AD178" s="1"/>
     </row>
-    <row r="179" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1" t="s">
         <v>851</v>
@@ -19181,7 +19180,7 @@
       <c r="AC179" s="1"/>
       <c r="AD179" s="1"/>
     </row>
-    <row r="180" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1" t="s">
         <v>851</v>
@@ -19253,7 +19252,7 @@
       <c r="AC180" s="1"/>
       <c r="AD180" s="1"/>
     </row>
-    <row r="181" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1" t="s">
         <v>911</v>
@@ -19297,7 +19296,7 @@
       <c r="AC181" s="1"/>
       <c r="AD181" s="1"/>
     </row>
-    <row r="182" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1" t="s">
         <v>911</v>
@@ -19341,7 +19340,7 @@
       <c r="AC182" s="1"/>
       <c r="AD182" s="1"/>
     </row>
-    <row r="183" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1" t="s">
         <v>911</v>
@@ -19385,7 +19384,7 @@
       <c r="AC183" s="1"/>
       <c r="AD183" s="1"/>
     </row>
-    <row r="184" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1" t="s">
         <v>911</v>
@@ -19429,7 +19428,7 @@
       <c r="AC184" s="1"/>
       <c r="AD184" s="1"/>
     </row>
-    <row r="185" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1" t="s">
         <v>911</v>
@@ -19473,7 +19472,7 @@
       <c r="AC185" s="1"/>
       <c r="AD185" s="1"/>
     </row>
-    <row r="186" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1" t="s">
         <v>911</v>
@@ -19517,7 +19516,7 @@
       <c r="AC186" s="1"/>
       <c r="AD186" s="1"/>
     </row>
-    <row r="187" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1" t="s">
         <v>911</v>
@@ -19561,7 +19560,7 @@
       <c r="AC187" s="1"/>
       <c r="AD187" s="1"/>
     </row>
-    <row r="188" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1" t="s">
         <v>918</v>
@@ -19605,7 +19604,7 @@
       <c r="AC188" s="1"/>
       <c r="AD188" s="1"/>
     </row>
-    <row r="189" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1" t="s">
         <v>918</v>
@@ -19649,7 +19648,7 @@
       <c r="AC189" s="1"/>
       <c r="AD189" s="1"/>
     </row>
-    <row r="190" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1" t="s">
         <v>918</v>
@@ -19721,7 +19720,7 @@
       <c r="AC190" s="1"/>
       <c r="AD190" s="1"/>
     </row>
-    <row r="191" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1" t="s">
         <v>918</v>
@@ -19765,7 +19764,7 @@
       <c r="AC191" s="1"/>
       <c r="AD191" s="1"/>
     </row>
-    <row r="192" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1" t="s">
         <v>928</v>
@@ -19837,7 +19836,7 @@
       <c r="AC192" s="1"/>
       <c r="AD192" s="1"/>
     </row>
-    <row r="193" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1" t="s">
         <v>928</v>
@@ -19911,7 +19910,7 @@
       </c>
       <c r="AD193" s="1"/>
     </row>
-    <row r="194" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1" t="s">
         <v>928</v>
@@ -19985,7 +19984,7 @@
       </c>
       <c r="AD194" s="1"/>
     </row>
-    <row r="195" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1" t="s">
         <v>928</v>
@@ -20057,7 +20056,7 @@
       <c r="AC195" s="1"/>
       <c r="AD195" s="1"/>
     </row>
-    <row r="196" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1" t="s">
         <v>928</v>
@@ -20101,7 +20100,7 @@
       <c r="AC196" s="1"/>
       <c r="AD196" s="1"/>
     </row>
-    <row r="197" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1" t="s">
         <v>957</v>
@@ -20173,7 +20172,7 @@
       <c r="AC197" s="1"/>
       <c r="AD197" s="1"/>
     </row>
-    <row r="198" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1" t="s">
         <v>957</v>
@@ -20245,7 +20244,7 @@
       <c r="AC198" s="1"/>
       <c r="AD198" s="1"/>
     </row>
-    <row r="199" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1" t="s">
         <v>957</v>
@@ -20289,7 +20288,7 @@
       <c r="AC199" s="1"/>
       <c r="AD199" s="1"/>
     </row>
-    <row r="200" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1" t="s">
         <v>977</v>
@@ -20333,7 +20332,7 @@
       <c r="AC200" s="1"/>
       <c r="AD200" s="1"/>
     </row>
-    <row r="201" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1" t="s">
         <v>977</v>
@@ -20377,7 +20376,7 @@
       <c r="AC201" s="1"/>
       <c r="AD201" s="1"/>
     </row>
-    <row r="202" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1" t="s">
         <v>977</v>
@@ -20421,7 +20420,7 @@
       <c r="AC202" s="1"/>
       <c r="AD202" s="1"/>
     </row>
-    <row r="203" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1" t="s">
         <v>977</v>
@@ -20465,7 +20464,7 @@
       <c r="AC203" s="1"/>
       <c r="AD203" s="1"/>
     </row>
-    <row r="204" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1" t="s">
         <v>977</v>
@@ -20509,7 +20508,7 @@
       <c r="AC204" s="1"/>
       <c r="AD204" s="1"/>
     </row>
-    <row r="205" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1" t="s">
         <v>977</v>
@@ -20577,7 +20576,7 @@
       <c r="AC205" s="1"/>
       <c r="AD205" s="1"/>
     </row>
-    <row r="206" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1" t="s">
         <v>989</v>
@@ -20649,7 +20648,7 @@
       <c r="AC206" s="1"/>
       <c r="AD206" s="1"/>
     </row>
-    <row r="207" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1" t="s">
         <v>989</v>
@@ -20693,7 +20692,7 @@
       <c r="AC207" s="1"/>
       <c r="AD207" s="1"/>
     </row>
-    <row r="208" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1" t="s">
         <v>989</v>
@@ -20737,7 +20736,7 @@
       <c r="AC208" s="1"/>
       <c r="AD208" s="1"/>
     </row>
-    <row r="209" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1" t="s">
         <v>989</v>
@@ -20781,7 +20780,7 @@
       <c r="AC209" s="1"/>
       <c r="AD209" s="1"/>
     </row>
-    <row r="210" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1" t="s">
         <v>989</v>
@@ -20825,7 +20824,7 @@
       <c r="AC210" s="1"/>
       <c r="AD210" s="1"/>
     </row>
-    <row r="211" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1" t="s">
         <v>989</v>
@@ -20897,7 +20896,7 @@
       <c r="AC211" s="1"/>
       <c r="AD211" s="1"/>
     </row>
-    <row r="212" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1" t="s">
         <v>989</v>
@@ -20941,7 +20940,7 @@
       <c r="AC212" s="1"/>
       <c r="AD212" s="1"/>
     </row>
-    <row r="213" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1" t="s">
         <v>1006</v>
@@ -21007,7 +21006,7 @@
       <c r="AC213" s="1"/>
       <c r="AD213" s="1"/>
     </row>
-    <row r="214" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1" t="s">
         <v>1006</v>
@@ -21079,7 +21078,7 @@
       <c r="AC214" s="1"/>
       <c r="AD214" s="1"/>
     </row>
-    <row r="215" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1" t="s">
         <v>1006</v>
@@ -21147,7 +21146,7 @@
       <c r="AC215" s="1"/>
       <c r="AD215" s="1"/>
     </row>
-    <row r="216" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1" t="s">
         <v>1006</v>
@@ -21219,7 +21218,7 @@
       <c r="AC216" s="1"/>
       <c r="AD216" s="1"/>
     </row>
-    <row r="217" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1" t="s">
         <v>1035</v>
@@ -21291,7 +21290,7 @@
       <c r="AC217" s="1"/>
       <c r="AD217" s="1"/>
     </row>
-    <row r="218" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1" t="s">
         <v>1035</v>
@@ -21335,7 +21334,7 @@
       <c r="AC218" s="1"/>
       <c r="AD218" s="1"/>
     </row>
-    <row r="219" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1" t="s">
         <v>1046</v>
@@ -21379,7 +21378,7 @@
       <c r="AC219" s="1"/>
       <c r="AD219" s="1"/>
     </row>
-    <row r="220" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1" t="s">
         <v>1046</v>
@@ -21423,7 +21422,7 @@
       <c r="AC220" s="1"/>
       <c r="AD220" s="1"/>
     </row>
-    <row r="221" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1" t="s">
         <v>1049</v>
@@ -21493,7 +21492,7 @@
       <c r="AC221" s="1"/>
       <c r="AD221" s="1"/>
     </row>
-    <row r="222" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1" t="s">
         <v>1049</v>
@@ -21557,7 +21556,7 @@
       <c r="AC222" s="1"/>
       <c r="AD222" s="1"/>
     </row>
-    <row r="223" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1" t="s">
         <v>1066</v>
@@ -21601,7 +21600,7 @@
       <c r="AC223" s="1"/>
       <c r="AD223" s="1"/>
     </row>
-    <row r="224" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1" t="s">
         <v>1067</v>
@@ -21673,7 +21672,7 @@
       <c r="AC224" s="1"/>
       <c r="AD224" s="1"/>
     </row>
-    <row r="225" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1" t="s">
         <v>1076</v>
@@ -21717,7 +21716,7 @@
       <c r="AC225" s="1"/>
       <c r="AD225" s="1"/>
     </row>
-    <row r="226" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1" t="s">
         <v>1077</v>
@@ -21761,7 +21760,7 @@
       <c r="AC226" s="1"/>
       <c r="AD226" s="1"/>
     </row>
-    <row r="227" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1" t="s">
         <v>1078</v>
@@ -21833,7 +21832,7 @@
       <c r="AC227" s="1"/>
       <c r="AD227" s="1"/>
     </row>
-    <row r="228" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1" t="s">
         <v>1088</v>
@@ -21877,7 +21876,7 @@
       <c r="AC228" s="1"/>
       <c r="AD228" s="1"/>
     </row>
-    <row r="229" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1" t="s">
         <v>1090</v>
@@ -21935,7 +21934,7 @@
       <c r="AC229" s="1"/>
       <c r="AD229" s="1"/>
     </row>
-    <row r="230" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1" t="s">
         <v>1097</v>
@@ -21993,7 +21992,7 @@
       <c r="AC230" s="1"/>
       <c r="AD230" s="1"/>
     </row>
-    <row r="231" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1" t="s">
         <v>1103</v>
@@ -22037,7 +22036,7 @@
       <c r="AC231" s="1"/>
       <c r="AD231" s="1"/>
     </row>
-    <row r="232" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1" t="s">
         <v>1105</v>
@@ -22081,7 +22080,7 @@
       <c r="AC232" s="1"/>
       <c r="AD232" s="1"/>
     </row>
-    <row r="233" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1" t="s">
         <v>1107</v>
@@ -22125,7 +22124,7 @@
       <c r="AC233" s="1"/>
       <c r="AD233" s="1"/>
     </row>
-    <row r="234" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1" t="s">
         <v>1108</v>
@@ -22197,7 +22196,7 @@
       <c r="AC234" s="1"/>
       <c r="AD234" s="1"/>
     </row>
-    <row r="235" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1" t="s">
         <v>1118</v>
@@ -22269,7 +22268,7 @@
       <c r="AC235" s="1"/>
       <c r="AD235" s="1"/>
     </row>
-    <row r="236" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1" t="s">
         <v>1128</v>
@@ -22313,7 +22312,7 @@
       <c r="AC236" s="1"/>
       <c r="AD236" s="1"/>
     </row>
-    <row r="237" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1" t="s">
         <v>1130</v>
@@ -22375,7 +22374,7 @@
       <c r="AC237" s="1"/>
       <c r="AD237" s="1"/>
     </row>
-    <row r="238" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1" t="s">
         <v>1130</v>
@@ -22419,7 +22418,7 @@
       <c r="AC238" s="1"/>
       <c r="AD238" s="1"/>
     </row>
-    <row r="239" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1" t="s">
         <v>1139</v>
@@ -22463,7 +22462,7 @@
       <c r="AC239" s="1"/>
       <c r="AD239" s="1"/>
     </row>
-    <row r="240" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1" t="s">
         <v>1140</v>
@@ -22507,7 +22506,7 @@
       <c r="AC240" s="1"/>
       <c r="AD240" s="1"/>
     </row>
-    <row r="241" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1" t="s">
         <v>1130</v>
@@ -22575,7 +22574,7 @@
       <c r="AC241" s="1"/>
       <c r="AD241" s="1"/>
     </row>
-    <row r="242" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1" t="s">
         <v>1149</v>
@@ -22649,7 +22648,7 @@
       <c r="AC242" s="1"/>
       <c r="AD242" s="1"/>
     </row>
-    <row r="243" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1" t="s">
         <v>1156</v>
@@ -22721,7 +22720,7 @@
       <c r="AC243" s="1"/>
       <c r="AD243" s="1"/>
     </row>
-    <row r="244" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1" t="s">
         <v>1163</v>
@@ -22779,7 +22778,7 @@
       <c r="AC244" s="1"/>
       <c r="AD244" s="1"/>
     </row>
-    <row r="245" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1" t="s">
         <v>1171</v>
@@ -22837,7 +22836,7 @@
       <c r="AC245" s="1"/>
       <c r="AD245" s="1"/>
     </row>
-    <row r="246" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="1"/>
       <c r="B246" s="1" t="s">
         <v>1178</v>
@@ -22881,7 +22880,7 @@
       <c r="AC246" s="1"/>
       <c r="AD246" s="1"/>
     </row>
-    <row r="247" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="1"/>
       <c r="B247" s="1" t="s">
         <v>1179</v>
@@ -22953,7 +22952,7 @@
       <c r="AC247" s="1"/>
       <c r="AD247" s="1"/>
     </row>
-    <row r="248" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1" t="s">
         <v>1179</v>
@@ -23025,7 +23024,7 @@
       <c r="AC248" s="1"/>
       <c r="AD248" s="1"/>
     </row>
-    <row r="249" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="1"/>
       <c r="B249" s="1" t="s">
         <v>1193</v>
@@ -23069,7 +23068,7 @@
       <c r="AC249" s="1"/>
       <c r="AD249" s="1"/>
     </row>
-    <row r="250" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1" t="s">
         <v>1196</v>
@@ -23127,7 +23126,7 @@
       <c r="AC250" s="1"/>
       <c r="AD250" s="1"/>
     </row>
-    <row r="251" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="1"/>
       <c r="B251" s="1" t="s">
         <v>1201</v>
@@ -23199,7 +23198,7 @@
       <c r="AC251" s="1"/>
       <c r="AD251" s="1"/>
     </row>
-    <row r="252" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="1"/>
       <c r="B252" s="1" t="s">
         <v>1209</v>
@@ -23243,7 +23242,7 @@
       <c r="AC252" s="1"/>
       <c r="AD252" s="1"/>
     </row>
-    <row r="253" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1" t="s">
         <v>1211</v>
@@ -23301,7 +23300,7 @@
       <c r="AC253" s="1"/>
       <c r="AD253" s="1"/>
     </row>
-    <row r="254" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="1"/>
       <c r="B254" s="1" t="s">
         <v>1218</v>
@@ -23345,7 +23344,7 @@
       <c r="AC254" s="1"/>
       <c r="AD254" s="1"/>
     </row>
-    <row r="255" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1" t="s">
         <v>1220</v>
@@ -23389,7 +23388,7 @@
       <c r="AC255" s="1"/>
       <c r="AD255" s="1"/>
     </row>
-    <row r="256" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="B256" s="1" t="s">
         <v>1222</v>
@@ -23433,7 +23432,7 @@
       <c r="AC256" s="1"/>
       <c r="AD256" s="1"/>
     </row>
-    <row r="257" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="B257" s="1" t="s">
         <v>1223</v>
@@ -23477,7 +23476,7 @@
       <c r="AC257" s="1"/>
       <c r="AD257" s="1"/>
     </row>
-    <row r="258" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1" t="s">
         <v>1218</v>
@@ -23521,7 +23520,7 @@
       <c r="AC258" s="1"/>
       <c r="AD258" s="1"/>
     </row>
-    <row r="259" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="1"/>
       <c r="B259" s="1" t="s">
         <v>1225</v>
@@ -23565,7 +23564,7 @@
       <c r="AC259" s="1"/>
       <c r="AD259" s="1"/>
     </row>
-    <row r="260" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="1"/>
       <c r="B260" s="1" t="s">
         <v>1227</v>
@@ -23609,7 +23608,7 @@
       <c r="AC260" s="1"/>
       <c r="AD260" s="1"/>
     </row>
-    <row r="261" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="1"/>
       <c r="B261" s="1" t="s">
         <v>1228</v>
@@ -23653,7 +23652,7 @@
       <c r="AC261" s="1"/>
       <c r="AD261" s="1"/>
     </row>
-    <row r="262" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="1"/>
       <c r="B262" s="1" t="s">
         <v>1230</v>
@@ -23697,7 +23696,7 @@
       <c r="AC262" s="1"/>
       <c r="AD262" s="1"/>
     </row>
-    <row r="263" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="1"/>
       <c r="B263" s="1" t="s">
         <v>1231</v>
@@ -23741,7 +23740,7 @@
       <c r="AC263" s="1"/>
       <c r="AD263" s="1"/>
     </row>
-    <row r="264" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="1"/>
       <c r="B264" s="1" t="s">
         <v>1232</v>
@@ -23785,7 +23784,7 @@
       <c r="AC264" s="1"/>
       <c r="AD264" s="1"/>
     </row>
-    <row r="265" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="1"/>
       <c r="B265" s="1" t="s">
         <v>1234</v>
@@ -23829,7 +23828,7 @@
       <c r="AC265" s="1"/>
       <c r="AD265" s="1"/>
     </row>
-    <row r="266" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="1"/>
       <c r="B266" s="1" t="s">
         <v>1236</v>
@@ -23873,7 +23872,7 @@
       <c r="AC266" s="1"/>
       <c r="AD266" s="1"/>
     </row>
-    <row r="267" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="1"/>
       <c r="B267" s="1" t="s">
         <v>1238</v>
@@ -23917,7 +23916,7 @@
       <c r="AC267" s="1"/>
       <c r="AD267" s="1"/>
     </row>
-    <row r="268" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="1"/>
       <c r="B268" s="1" t="s">
         <v>1240</v>
@@ -23989,7 +23988,7 @@
       <c r="AC268" s="1"/>
       <c r="AD268" s="1"/>
     </row>
-    <row r="269" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="1"/>
       <c r="B269" s="1" t="s">
         <v>1240</v>
@@ -24033,7 +24032,7 @@
       <c r="AC269" s="1"/>
       <c r="AD269" s="1"/>
     </row>
-    <row r="270" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1" t="s">
         <v>1240</v>
@@ -24077,7 +24076,7 @@
       <c r="AC270" s="1"/>
       <c r="AD270" s="1"/>
     </row>
-    <row r="271" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="1"/>
       <c r="B271" s="1" t="s">
         <v>1240</v>
@@ -24121,7 +24120,7 @@
       <c r="AC271" s="1"/>
       <c r="AD271" s="1"/>
     </row>
-    <row r="272" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="1"/>
       <c r="B272" s="1" t="s">
         <v>1240</v>
@@ -24191,7 +24190,7 @@
       <c r="AC272" s="1"/>
       <c r="AD272" s="1"/>
     </row>
-    <row r="273" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="1"/>
       <c r="B273" s="1" t="s">
         <v>1262</v>
@@ -24235,7 +24234,7 @@
       <c r="AC273" s="1"/>
       <c r="AD273" s="1"/>
     </row>
-    <row r="274" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="1"/>
       <c r="B274" s="1" t="s">
         <v>1262</v>
@@ -24279,7 +24278,7 @@
       <c r="AC274" s="1"/>
       <c r="AD274" s="1"/>
     </row>
-    <row r="275" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="1"/>
       <c r="B275" s="1" t="s">
         <v>1266</v>
@@ -24351,7 +24350,7 @@
       </c>
       <c r="AD275" s="1"/>
     </row>
-    <row r="276" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="1"/>
       <c r="B276" s="1" t="s">
         <v>1266</v>
@@ -24423,7 +24422,7 @@
       </c>
       <c r="AD276" s="1"/>
     </row>
-    <row r="277" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="1"/>
       <c r="B277" s="1" t="s">
         <v>1266</v>
@@ -24495,7 +24494,7 @@
       </c>
       <c r="AD277" s="1"/>
     </row>
-    <row r="278" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="1"/>
       <c r="B278" s="1" t="s">
         <v>1266</v>
@@ -24567,7 +24566,7 @@
       </c>
       <c r="AD278" s="1"/>
     </row>
-    <row r="279" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="1"/>
       <c r="B279" s="1" t="s">
         <v>1266</v>
@@ -24639,7 +24638,7 @@
       </c>
       <c r="AD279" s="1"/>
     </row>
-    <row r="280" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="1"/>
       <c r="B280" s="1" t="s">
         <v>1266</v>
@@ -24711,7 +24710,7 @@
       <c r="AC280" s="1"/>
       <c r="AD280" s="1"/>
     </row>
-    <row r="281" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="1"/>
       <c r="B281" s="1" t="s">
         <v>1303</v>
@@ -24783,7 +24782,7 @@
       <c r="AC281" s="1"/>
       <c r="AD281" s="1"/>
     </row>
-    <row r="282" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="1"/>
       <c r="B282" s="1" t="s">
         <v>1303</v>
@@ -24843,7 +24842,7 @@
       <c r="AC282" s="1"/>
       <c r="AD282" s="1"/>
     </row>
-    <row r="283" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="1"/>
       <c r="B283" s="1" t="s">
         <v>1321</v>
@@ -24887,7 +24886,7 @@
       <c r="AC283" s="1"/>
       <c r="AD283" s="1"/>
     </row>
-    <row r="284" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="1"/>
       <c r="B284" s="1" t="s">
         <v>1321</v>
@@ -24959,7 +24958,7 @@
       <c r="AC284" s="1"/>
       <c r="AD284" s="1"/>
     </row>
-    <row r="285" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="1"/>
       <c r="B285" s="1" t="s">
         <v>1333</v>
@@ -25031,7 +25030,7 @@
       <c r="AC285" s="1"/>
       <c r="AD285" s="1"/>
     </row>
-    <row r="286" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="1"/>
       <c r="B286" s="1" t="s">
         <v>1333</v>
@@ -25101,7 +25100,7 @@
       <c r="AC286" s="1"/>
       <c r="AD286" s="1"/>
     </row>
-    <row r="287" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="1"/>
       <c r="B287" s="1" t="s">
         <v>1351</v>
@@ -25173,7 +25172,7 @@
       <c r="AC287" s="1"/>
       <c r="AD287" s="1"/>
     </row>
-    <row r="288" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="1"/>
       <c r="B288" s="1" t="s">
         <v>1351</v>
@@ -25237,7 +25236,7 @@
       <c r="AC288" s="1"/>
       <c r="AD288" s="1"/>
     </row>
-    <row r="289" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="1"/>
       <c r="B289" s="1" t="s">
         <v>1351</v>
@@ -25309,7 +25308,7 @@
       <c r="AC289" s="1"/>
       <c r="AD289" s="1"/>
     </row>
-    <row r="290" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="1"/>
       <c r="B290" s="1" t="s">
         <v>1351</v>
@@ -25379,7 +25378,7 @@
       <c r="AC290" s="1"/>
       <c r="AD290" s="1"/>
     </row>
-    <row r="291" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="1"/>
       <c r="B291" s="1" t="s">
         <v>1384</v>
@@ -25453,7 +25452,7 @@
       <c r="AC291" s="1"/>
       <c r="AD291" s="1"/>
     </row>
-    <row r="292" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="1"/>
       <c r="B292" s="1" t="s">
         <v>1384</v>
@@ -25515,7 +25514,7 @@
       <c r="AC292" s="1"/>
       <c r="AD292" s="1"/>
     </row>
-    <row r="293" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="1"/>
       <c r="B293" s="1" t="s">
         <v>1384</v>
@@ -25559,7 +25558,7 @@
       <c r="AC293" s="1"/>
       <c r="AD293" s="1"/>
     </row>
-    <row r="294" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="1"/>
       <c r="B294" s="1" t="s">
         <v>1400</v>
@@ -25619,7 +25618,7 @@
       <c r="AC294" s="1"/>
       <c r="AD294" s="1"/>
     </row>
-    <row r="295" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="1"/>
       <c r="B295" s="1" t="s">
         <v>1400</v>
@@ -25679,7 +25678,7 @@
       <c r="AC295" s="1"/>
       <c r="AD295" s="1"/>
     </row>
-    <row r="296" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="1"/>
       <c r="B296" s="1" t="s">
         <v>1400</v>
@@ -25739,7 +25738,7 @@
       <c r="AC296" s="1"/>
       <c r="AD296" s="1"/>
     </row>
-    <row r="297" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="1"/>
       <c r="B297" s="1" t="s">
         <v>1400</v>
@@ -25799,7 +25798,7 @@
       <c r="AC297" s="1"/>
       <c r="AD297" s="1"/>
     </row>
-    <row r="298" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="1"/>
       <c r="B298" s="1" t="s">
         <v>1400</v>
@@ -25859,7 +25858,7 @@
       <c r="AC298" s="1"/>
       <c r="AD298" s="1"/>
     </row>
-    <row r="299" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="1"/>
       <c r="B299" s="1" t="s">
         <v>1417</v>
@@ -25923,7 +25922,7 @@
       <c r="AC299" s="1"/>
       <c r="AD299" s="1"/>
     </row>
-    <row r="300" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="1"/>
       <c r="B300" s="1" t="s">
         <v>1427</v>
@@ -25995,7 +25994,7 @@
       <c r="AC300" s="1"/>
       <c r="AD300" s="1"/>
     </row>
-    <row r="301" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="1"/>
       <c r="B301" s="1" t="s">
         <v>1427</v>
@@ -26049,7 +26048,7 @@
       <c r="AC301" s="1"/>
       <c r="AD301" s="1"/>
     </row>
-    <row r="302" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="1"/>
       <c r="B302" s="1" t="s">
         <v>1427</v>
@@ -26103,7 +26102,7 @@
       <c r="AC302" s="1"/>
       <c r="AD302" s="1"/>
     </row>
-    <row r="303" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="1"/>
       <c r="B303" s="1" t="s">
         <v>1427</v>
@@ -26157,7 +26156,7 @@
       <c r="AC303" s="1"/>
       <c r="AD303" s="1"/>
     </row>
-    <row r="304" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="1"/>
       <c r="B304" s="1" t="s">
         <v>1427</v>
@@ -26209,7 +26208,7 @@
       <c r="AC304" s="1"/>
       <c r="AD304" s="1"/>
     </row>
-    <row r="305" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="1"/>
       <c r="B305" s="1" t="s">
         <v>1427</v>
@@ -26261,7 +26260,7 @@
       <c r="AC305" s="1"/>
       <c r="AD305" s="1"/>
     </row>
-    <row r="306" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="1"/>
       <c r="B306" s="1" t="s">
         <v>1427</v>
@@ -26305,7 +26304,7 @@
       <c r="AC306" s="1"/>
       <c r="AD306" s="1"/>
     </row>
-    <row r="307" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="1"/>
       <c r="B307" s="1" t="s">
         <v>1427</v>
@@ -26349,7 +26348,7 @@
       <c r="AC307" s="1"/>
       <c r="AD307" s="1"/>
     </row>
-    <row r="308" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="1"/>
       <c r="B308" s="1" t="s">
         <v>1444</v>
@@ -26421,7 +26420,7 @@
       <c r="AC308" s="1"/>
       <c r="AD308" s="1"/>
     </row>
-    <row r="309" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="1"/>
       <c r="B309" s="1" t="s">
         <v>1455</v>
@@ -26493,7 +26492,7 @@
       <c r="AC309" s="1"/>
       <c r="AD309" s="1"/>
     </row>
-    <row r="310" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1" t="s">
         <v>1466</v>
@@ -26551,7 +26550,7 @@
       <c r="AC310" s="1"/>
       <c r="AD310" s="1"/>
     </row>
-    <row r="311" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="1"/>
       <c r="B311" s="1" t="s">
         <v>1472</v>
@@ -26595,7 +26594,7 @@
       <c r="AC311" s="1"/>
       <c r="AD311" s="1"/>
     </row>
-    <row r="312" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="1"/>
       <c r="B312" s="1" t="s">
         <v>1474</v>
@@ -26655,7 +26654,7 @@
       <c r="AC312" s="1"/>
       <c r="AD312" s="1"/>
     </row>
-    <row r="313" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="1"/>
       <c r="B313" s="1" t="s">
         <v>1483</v>
@@ -26721,7 +26720,7 @@
       </c>
       <c r="AD313" s="1"/>
     </row>
-    <row r="314" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="1"/>
       <c r="B314" s="1" t="s">
         <v>1490</v>
@@ -26767,7 +26766,7 @@
       <c r="AC314" s="1"/>
       <c r="AD314" s="1"/>
     </row>
-    <row r="315" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="1"/>
       <c r="B315" s="1" t="s">
         <v>1494</v>
@@ -26833,7 +26832,7 @@
       <c r="AC315" s="1"/>
       <c r="AD315" s="1"/>
     </row>
-    <row r="316" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="1"/>
       <c r="B316" s="1" t="s">
         <v>1502</v>
@@ -26885,7 +26884,7 @@
       <c r="AC316" s="1"/>
       <c r="AD316" s="1"/>
     </row>
-    <row r="317" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="1"/>
       <c r="B317" s="1" t="s">
         <v>1504</v>
@@ -26957,7 +26956,7 @@
       </c>
       <c r="AD317" s="1"/>
     </row>
-    <row r="318" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="1"/>
       <c r="B318" s="1" t="s">
         <v>1504</v>
@@ -27023,7 +27022,7 @@
       </c>
       <c r="AD318" s="1"/>
     </row>
-    <row r="319" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="1"/>
       <c r="B319" s="1" t="s">
         <v>1504</v>
@@ -27095,7 +27094,7 @@
       <c r="AC319" s="1"/>
       <c r="AD319" s="1"/>
     </row>
-    <row r="320" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="1"/>
       <c r="B320" s="1" t="s">
         <v>1504</v>
@@ -27167,7 +27166,7 @@
       <c r="AC320" s="1"/>
       <c r="AD320" s="1"/>
     </row>
-    <row r="321" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="1"/>
       <c r="B321" s="1" t="s">
         <v>1504</v>
@@ -27229,7 +27228,7 @@
       <c r="AC321" s="1"/>
       <c r="AD321" s="1"/>
     </row>
-    <row r="322" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="1"/>
       <c r="B322" s="1" t="s">
         <v>1540</v>
@@ -27299,7 +27298,7 @@
       </c>
       <c r="AD322" s="1"/>
     </row>
-    <row r="323" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="1"/>
       <c r="B323" s="1" t="s">
         <v>1540</v>
@@ -27357,7 +27356,7 @@
       <c r="AC323" s="1"/>
       <c r="AD323" s="1"/>
     </row>
-    <row r="324" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="1"/>
       <c r="B324" s="1" t="s">
         <v>1540</v>
@@ -27429,7 +27428,7 @@
       </c>
       <c r="AD324" s="1"/>
     </row>
-    <row r="325" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="1"/>
       <c r="B325" s="1" t="s">
         <v>1540</v>
@@ -27473,7 +27472,7 @@
       <c r="AC325" s="1"/>
       <c r="AD325" s="1"/>
     </row>
-    <row r="326" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="1"/>
       <c r="B326" s="1" t="s">
         <v>1561</v>
@@ -27537,7 +27536,7 @@
       </c>
       <c r="AD326" s="1"/>
     </row>
-    <row r="327" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="1"/>
       <c r="B327" s="1" t="s">
         <v>1569</v>
@@ -27595,7 +27594,7 @@
       <c r="AC327" s="1"/>
       <c r="AD327" s="1"/>
     </row>
-    <row r="328" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="1"/>
       <c r="B328" s="1" t="s">
         <v>1333</v>
@@ -27667,7 +27666,7 @@
       <c r="AC328" s="1"/>
       <c r="AD328" s="1"/>
     </row>
-    <row r="329" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="1"/>
       <c r="B329" s="1" t="s">
         <v>1584</v>
@@ -27727,7 +27726,7 @@
       <c r="AC329" s="1"/>
       <c r="AD329" s="1"/>
     </row>
-    <row r="330" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="1"/>
       <c r="B330" s="1" t="s">
         <v>1584</v>
@@ -27787,7 +27786,7 @@
       <c r="AC330" s="1"/>
       <c r="AD330" s="1"/>
     </row>
-    <row r="331" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="1"/>
       <c r="B331" s="1" t="s">
         <v>1427</v>
@@ -27851,7 +27850,7 @@
       <c r="AC331" s="1"/>
       <c r="AD331" s="1"/>
     </row>
-    <row r="332" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="1"/>
       <c r="B332" s="1" t="s">
         <v>1427</v>
@@ -27917,7 +27916,7 @@
       <c r="AC332" s="1"/>
       <c r="AD332" s="1"/>
     </row>
-    <row r="333" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="1"/>
       <c r="B333" s="1" t="s">
         <v>1601</v>
@@ -27979,7 +27978,7 @@
       <c r="AC333" s="1"/>
       <c r="AD333" s="1"/>
     </row>
-    <row r="334" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="1"/>
       <c r="B334" s="1" t="s">
         <v>1601</v>
@@ -28023,7 +28022,7 @@
       <c r="AC334" s="1"/>
       <c r="AD334" s="1"/>
     </row>
-    <row r="335" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="1"/>
       <c r="B335" s="1" t="s">
         <v>1611</v>
@@ -28083,7 +28082,7 @@
       <c r="AC335" s="1"/>
       <c r="AD335" s="1"/>
     </row>
-    <row r="336" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="1"/>
       <c r="B336" s="1" t="s">
         <v>1611</v>
@@ -28141,7 +28140,7 @@
       <c r="AC336" s="1"/>
       <c r="AD336" s="1"/>
     </row>
-    <row r="337" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="1"/>
       <c r="B337" s="1" t="s">
         <v>1611</v>
@@ -28199,7 +28198,7 @@
       <c r="AC337" s="1"/>
       <c r="AD337" s="1"/>
     </row>
-    <row r="338" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="1"/>
       <c r="B338" s="1" t="s">
         <v>1611</v>
@@ -28255,7 +28254,7 @@
       <c r="AC338" s="1"/>
       <c r="AD338" s="1"/>
     </row>
-    <row r="339" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="1"/>
       <c r="B339" s="1" t="s">
         <v>1611</v>
@@ -28311,7 +28310,7 @@
       <c r="AC339" s="1"/>
       <c r="AD339" s="1"/>
     </row>
-    <row r="340" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="1"/>
       <c r="B340" s="1" t="s">
         <v>1635</v>
@@ -28383,7 +28382,7 @@
       <c r="AC340" s="1"/>
       <c r="AD340" s="1"/>
     </row>
-    <row r="341" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="1"/>
       <c r="B341" s="1" t="s">
         <v>1644</v>
@@ -28455,7 +28454,7 @@
       <c r="AC341" s="1"/>
       <c r="AD341" s="1"/>
     </row>
-    <row r="342" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="1"/>
       <c r="B342" s="1" t="s">
         <v>339</v>
@@ -28529,7 +28528,7 @@
       </c>
       <c r="AD342" s="1"/>
     </row>
-    <row r="343" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="1"/>
       <c r="B343" s="1" t="s">
         <v>339</v>
@@ -28603,7 +28602,7 @@
       </c>
       <c r="AD343" s="1"/>
     </row>
-    <row r="344" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="1"/>
       <c r="B344" s="1" t="s">
         <v>339</v>
@@ -28677,7 +28676,7 @@
       </c>
       <c r="AD344" s="1"/>
     </row>
-    <row r="345" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="1"/>
       <c r="B345" s="1" t="s">
         <v>339</v>
@@ -28751,7 +28750,7 @@
       </c>
       <c r="AD345" s="1"/>
     </row>
-    <row r="346" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="1"/>
       <c r="B346" s="1" t="s">
         <v>339</v>
@@ -28813,7 +28812,7 @@
       <c r="AC346" s="1"/>
       <c r="AD346" s="1"/>
     </row>
-    <row r="347" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="1"/>
       <c r="B347" s="1" t="s">
         <v>1674</v>
@@ -28885,7 +28884,7 @@
       <c r="AC347" s="1"/>
       <c r="AD347" s="1"/>
     </row>
-    <row r="348" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="1"/>
       <c r="B348" s="1" t="s">
         <v>1674</v>
@@ -28957,7 +28956,7 @@
       <c r="AC348" s="1"/>
       <c r="AD348" s="1"/>
     </row>
-    <row r="349" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="1"/>
       <c r="B349" s="1" t="s">
         <v>1601</v>
@@ -29001,7 +29000,7 @@
       <c r="AC349" s="1"/>
       <c r="AD349" s="1"/>
     </row>
-    <row r="350" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="1"/>
       <c r="B350" s="1" t="s">
         <v>1601</v>
@@ -29045,7 +29044,7 @@
       <c r="AC350" s="1"/>
       <c r="AD350" s="1"/>
     </row>
-    <row r="351" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="1"/>
       <c r="B351" s="1" t="s">
         <v>1601</v>
@@ -29089,7 +29088,7 @@
       <c r="AC351" s="1"/>
       <c r="AD351" s="1"/>
     </row>
-    <row r="352" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="1"/>
       <c r="B352" s="1" t="s">
         <v>1601</v>
@@ -29133,7 +29132,7 @@
       <c r="AC352" s="1"/>
       <c r="AD352" s="1"/>
     </row>
-    <row r="353" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="1"/>
       <c r="B353" s="1" t="s">
         <v>1601</v>
@@ -29177,7 +29176,7 @@
       <c r="AC353" s="1"/>
       <c r="AD353" s="1"/>
     </row>
-    <row r="354" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="1"/>
       <c r="B354" s="1" t="s">
         <v>1694</v>
@@ -29249,7 +29248,7 @@
       <c r="AC354" s="1"/>
       <c r="AD354" s="1"/>
     </row>
-    <row r="355" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="1"/>
       <c r="B355" s="1" t="s">
         <v>1601</v>
@@ -29307,7 +29306,7 @@
       <c r="AC355" s="1"/>
       <c r="AD355" s="1"/>
     </row>
-    <row r="356" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="1"/>
       <c r="B356" s="1" t="s">
         <v>1601</v>
@@ -29373,7 +29372,7 @@
       </c>
       <c r="AD356" s="1"/>
     </row>
-    <row r="357" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="1"/>
       <c r="B357" s="1" t="s">
         <v>1719</v>
@@ -29441,7 +29440,7 @@
       <c r="AC357" s="1"/>
       <c r="AD357" s="1"/>
     </row>
-    <row r="358" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="1"/>
       <c r="B358" s="1" t="s">
         <v>1726</v>
@@ -29507,7 +29506,7 @@
       <c r="AC358" s="1"/>
       <c r="AD358" s="1"/>
     </row>
-    <row r="359" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="1"/>
       <c r="B359" s="1" t="s">
         <v>1333</v>
@@ -29573,7 +29572,7 @@
       <c r="AC359" s="1"/>
       <c r="AD359" s="1"/>
     </row>
-    <row r="360" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="1"/>
       <c r="B360" s="1" t="s">
         <v>1737</v>
@@ -29641,7 +29640,7 @@
       <c r="AC360" s="1"/>
       <c r="AD360" s="1"/>
     </row>
-    <row r="361" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="1"/>
       <c r="B361" s="1" t="s">
         <v>1737</v>
@@ -29709,7 +29708,7 @@
       <c r="AC361" s="1"/>
       <c r="AD361" s="1"/>
     </row>
-    <row r="362" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="1"/>
       <c r="B362" s="1" t="s">
         <v>1749</v>
@@ -29777,7 +29776,7 @@
       <c r="AC362" s="1"/>
       <c r="AD362" s="1"/>
     </row>
-    <row r="363" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="1"/>
       <c r="B363" s="1" t="s">
         <v>1757</v>
@@ -29845,7 +29844,7 @@
       <c r="AC363" s="1"/>
       <c r="AD363" s="1"/>
     </row>
-    <row r="364" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="1"/>
       <c r="B364" s="1" t="s">
         <v>1757</v>
@@ -29913,7 +29912,7 @@
       <c r="AC364" s="1"/>
       <c r="AD364" s="1"/>
     </row>
-    <row r="365" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="1"/>
       <c r="B365" s="1" t="s">
         <v>1770</v>
@@ -29981,7 +29980,7 @@
       <c r="AC365" s="1"/>
       <c r="AD365" s="1"/>
     </row>
-    <row r="366" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="1"/>
       <c r="B366" s="1" t="s">
         <v>1770</v>
@@ -30049,7 +30048,7 @@
       <c r="AC366" s="1"/>
       <c r="AD366" s="1"/>
     </row>
-    <row r="367" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="1"/>
       <c r="B367" s="1" t="s">
         <v>1780</v>
@@ -30117,7 +30116,7 @@
       <c r="AC367" s="1"/>
       <c r="AD367" s="1"/>
     </row>
-    <row r="368" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="1"/>
       <c r="B368" s="1" t="s">
         <v>1780</v>
@@ -30185,7 +30184,7 @@
       <c r="AC368" s="1"/>
       <c r="AD368" s="1"/>
     </row>
-    <row r="369" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="1"/>
       <c r="B369" s="1" t="s">
         <v>1780</v>
@@ -30253,7 +30252,7 @@
       <c r="AC369" s="1"/>
       <c r="AD369" s="1"/>
     </row>
-    <row r="370" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="1"/>
       <c r="B370" s="1" t="s">
         <v>1780</v>
@@ -30321,7 +30320,7 @@
       <c r="AC370" s="1"/>
       <c r="AD370" s="1"/>
     </row>
-    <row r="371" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="1"/>
       <c r="B371" s="1" t="s">
         <v>1780</v>
@@ -30389,7 +30388,7 @@
       <c r="AC371" s="1"/>
       <c r="AD371" s="1"/>
     </row>
-    <row r="372" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="1"/>
       <c r="B372" s="1" t="s">
         <v>1780</v>
@@ -30457,7 +30456,7 @@
       <c r="AC372" s="1"/>
       <c r="AD372" s="1"/>
     </row>
-    <row r="373" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="1"/>
       <c r="B373" s="1" t="s">
         <v>1780</v>
@@ -30525,7 +30524,7 @@
       <c r="AC373" s="1"/>
       <c r="AD373" s="1"/>
     </row>
-    <row r="374" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="1"/>
       <c r="B374" s="1" t="s">
         <v>1780</v>
@@ -30593,7 +30592,7 @@
       <c r="AC374" s="1"/>
       <c r="AD374" s="1"/>
     </row>
-    <row r="375" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="1"/>
       <c r="B375" s="1" t="s">
         <v>1780</v>
@@ -30653,7 +30652,7 @@
       <c r="AC375" s="1"/>
       <c r="AD375" s="1"/>
     </row>
-    <row r="376" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="1"/>
       <c r="B376" s="1" t="s">
         <v>1780</v>
@@ -30713,7 +30712,7 @@
       <c r="AC376" s="1"/>
       <c r="AD376" s="1"/>
     </row>
-    <row r="377" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="1"/>
       <c r="B377" s="1" t="s">
         <v>1780</v>
@@ -30773,7 +30772,7 @@
       <c r="AC377" s="1"/>
       <c r="AD377" s="1"/>
     </row>
-    <row r="378" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="1"/>
       <c r="B378" s="1" t="s">
         <v>1780</v>
@@ -30833,7 +30832,7 @@
       <c r="AC378" s="1"/>
       <c r="AD378" s="1"/>
     </row>
-    <row r="379" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="1"/>
       <c r="B379" s="1" t="s">
         <v>1780</v>
@@ -30893,7 +30892,7 @@
       <c r="AC379" s="1"/>
       <c r="AD379" s="1"/>
     </row>
-    <row r="380" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="1"/>
       <c r="B380" s="1" t="s">
         <v>1780</v>
@@ -30953,7 +30952,7 @@
       <c r="AC380" s="1"/>
       <c r="AD380" s="1"/>
     </row>
-    <row r="381" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="1"/>
       <c r="B381" s="1" t="s">
         <v>1780</v>
@@ -31013,7 +31012,7 @@
       <c r="AC381" s="1"/>
       <c r="AD381" s="1"/>
     </row>
-    <row r="382" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="1"/>
       <c r="B382" s="1" t="s">
         <v>1780</v>
@@ -31073,7 +31072,7 @@
       <c r="AC382" s="1"/>
       <c r="AD382" s="1"/>
     </row>
-    <row r="383" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="1"/>
       <c r="B383" s="1" t="s">
         <v>1780</v>
@@ -31133,7 +31132,7 @@
       <c r="AC383" s="1"/>
       <c r="AD383" s="1"/>
     </row>
-    <row r="384" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="1"/>
       <c r="B384" s="1" t="s">
         <v>1780</v>
@@ -31193,7 +31192,7 @@
       <c r="AC384" s="1"/>
       <c r="AD384" s="1"/>
     </row>
-    <row r="385" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="1"/>
       <c r="B385" s="1" t="s">
         <v>1780</v>
@@ -31253,7 +31252,7 @@
       <c r="AC385" s="1"/>
       <c r="AD385" s="1"/>
     </row>
-    <row r="386" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="1"/>
       <c r="B386" s="1" t="s">
         <v>1780</v>
@@ -31313,7 +31312,7 @@
       <c r="AC386" s="1"/>
       <c r="AD386" s="1"/>
     </row>
-    <row r="387" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="1"/>
       <c r="B387" s="1" t="s">
         <v>1780</v>
@@ -31373,7 +31372,7 @@
       <c r="AC387" s="1"/>
       <c r="AD387" s="1"/>
     </row>
-    <row r="388" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="1"/>
       <c r="B388" s="1" t="s">
         <v>1780</v>
@@ -31433,7 +31432,7 @@
       <c r="AC388" s="1"/>
       <c r="AD388" s="1"/>
     </row>
-    <row r="389" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="1"/>
       <c r="B389" s="1" t="s">
         <v>1780</v>
@@ -31493,7 +31492,7 @@
       <c r="AC389" s="1"/>
       <c r="AD389" s="1"/>
     </row>
-    <row r="390" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="1"/>
       <c r="B390" s="1" t="s">
         <v>1780</v>
@@ -31553,7 +31552,7 @@
       <c r="AC390" s="1"/>
       <c r="AD390" s="1"/>
     </row>
-    <row r="391" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="1"/>
       <c r="B391" s="1" t="s">
         <v>1780</v>
@@ -31613,7 +31612,7 @@
       <c r="AC391" s="1"/>
       <c r="AD391" s="1"/>
     </row>
-    <row r="392" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="1"/>
       <c r="B392" s="1" t="s">
         <v>1780</v>
@@ -31673,7 +31672,7 @@
       <c r="AC392" s="1"/>
       <c r="AD392" s="1"/>
     </row>
-    <row r="393" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="1"/>
       <c r="B393" s="1" t="s">
         <v>1780</v>
@@ -31733,7 +31732,7 @@
       <c r="AC393" s="1"/>
       <c r="AD393" s="1"/>
     </row>
-    <row r="394" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="1"/>
       <c r="B394" s="1" t="s">
         <v>1780</v>
@@ -31793,7 +31792,7 @@
       <c r="AC394" s="1"/>
       <c r="AD394" s="1"/>
     </row>
-    <row r="395" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="1"/>
       <c r="B395" s="1" t="s">
         <v>1780</v>
@@ -31853,7 +31852,7 @@
       <c r="AC395" s="1"/>
       <c r="AD395" s="1"/>
     </row>
-    <row r="396" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="1"/>
       <c r="B396" s="1" t="s">
         <v>1780</v>
@@ -31913,7 +31912,7 @@
       <c r="AC396" s="1"/>
       <c r="AD396" s="1"/>
     </row>
-    <row r="397" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" s="1"/>
       <c r="B397" s="1" t="s">
         <v>1780</v>
@@ -31973,7 +31972,7 @@
       <c r="AC397" s="1"/>
       <c r="AD397" s="1"/>
     </row>
-    <row r="398" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="1"/>
       <c r="B398" s="1" t="s">
         <v>1780</v>
@@ -32033,7 +32032,7 @@
       <c r="AC398" s="1"/>
       <c r="AD398" s="1"/>
     </row>
-    <row r="399" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="1"/>
       <c r="B399" s="1" t="s">
         <v>1780</v>
@@ -32093,7 +32092,7 @@
       <c r="AC399" s="1"/>
       <c r="AD399" s="1"/>
     </row>
-    <row r="400" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="1"/>
       <c r="B400" s="1" t="s">
         <v>1780</v>
@@ -32153,7 +32152,7 @@
       <c r="AC400" s="1"/>
       <c r="AD400" s="1"/>
     </row>
-    <row r="401" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="1"/>
       <c r="B401" s="1" t="s">
         <v>1780</v>
@@ -32213,7 +32212,7 @@
       <c r="AC401" s="1"/>
       <c r="AD401" s="1"/>
     </row>
-    <row r="402" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="1"/>
       <c r="B402" s="1" t="s">
         <v>1780</v>
@@ -32273,7 +32272,7 @@
       <c r="AC402" s="1"/>
       <c r="AD402" s="1"/>
     </row>
-    <row r="403" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" s="1"/>
       <c r="B403" s="1" t="s">
         <v>1780</v>
@@ -32333,7 +32332,7 @@
       <c r="AC403" s="1"/>
       <c r="AD403" s="1"/>
     </row>
-    <row r="404" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" s="1"/>
       <c r="B404" s="1" t="s">
         <v>1780</v>
@@ -32401,7 +32400,7 @@
       <c r="AC404" s="1"/>
       <c r="AD404" s="1"/>
     </row>
-    <row r="405" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" s="1"/>
       <c r="B405" s="1" t="s">
         <v>1780</v>
@@ -32461,7 +32460,7 @@
       <c r="AC405" s="1"/>
       <c r="AD405" s="1"/>
     </row>
-    <row r="406" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="1"/>
       <c r="B406" s="1" t="s">
         <v>1780</v>
@@ -32521,7 +32520,7 @@
       <c r="AC406" s="1"/>
       <c r="AD406" s="1"/>
     </row>
-    <row r="407" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" s="1"/>
       <c r="B407" s="1" t="s">
         <v>1780</v>
@@ -32589,7 +32588,7 @@
       <c r="AC407" s="1"/>
       <c r="AD407" s="1"/>
     </row>
-    <row r="408" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="1"/>
       <c r="B408" s="1" t="s">
         <v>1780</v>
@@ -32657,7 +32656,7 @@
       <c r="AC408" s="1"/>
       <c r="AD408" s="1"/>
     </row>
-    <row r="409" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409" s="1"/>
       <c r="B409" s="1" t="s">
         <v>1780</v>
@@ -32725,7 +32724,7 @@
       <c r="AC409" s="1"/>
       <c r="AD409" s="1"/>
     </row>
-    <row r="410" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" s="1"/>
       <c r="B410" s="1" t="s">
         <v>1780</v>
@@ -32793,7 +32792,7 @@
       <c r="AC410" s="1"/>
       <c r="AD410" s="1"/>
     </row>
-    <row r="411" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411" s="1"/>
       <c r="B411" s="1" t="s">
         <v>1780</v>
@@ -32861,7 +32860,7 @@
       <c r="AC411" s="1"/>
       <c r="AD411" s="1"/>
     </row>
-    <row r="412" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="1"/>
       <c r="B412" s="1" t="s">
         <v>1780</v>
@@ -32929,7 +32928,7 @@
       <c r="AC412" s="1"/>
       <c r="AD412" s="1"/>
     </row>
-    <row r="413" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="1"/>
       <c r="B413" s="1" t="s">
         <v>1780</v>
@@ -32997,7 +32996,7 @@
       <c r="AC413" s="1"/>
       <c r="AD413" s="1"/>
     </row>
-    <row r="414" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" s="1"/>
       <c r="B414" s="1" t="s">
         <v>1780</v>
@@ -33065,7 +33064,7 @@
       <c r="AC414" s="1"/>
       <c r="AD414" s="1"/>
     </row>
-    <row r="415" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="1"/>
       <c r="B415" s="1" t="s">
         <v>1780</v>
@@ -33133,7 +33132,7 @@
       <c r="AC415" s="1"/>
       <c r="AD415" s="1"/>
     </row>
-    <row r="416" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="1"/>
       <c r="B416" s="1" t="s">
         <v>1780</v>
@@ -33201,7 +33200,7 @@
       <c r="AC416" s="1"/>
       <c r="AD416" s="1"/>
     </row>
-    <row r="417" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" s="1"/>
       <c r="B417" s="1" t="s">
         <v>1780</v>
@@ -33269,7 +33268,7 @@
       <c r="AC417" s="1"/>
       <c r="AD417" s="1"/>
     </row>
-    <row r="418" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="1"/>
       <c r="B418" s="1" t="s">
         <v>1780</v>
@@ -33329,7 +33328,7 @@
       <c r="AC418" s="1"/>
       <c r="AD418" s="1"/>
     </row>
-    <row r="419" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" s="1"/>
       <c r="B419" s="1" t="s">
         <v>1780</v>
@@ -33389,7 +33388,7 @@
       <c r="AC419" s="1"/>
       <c r="AD419" s="1"/>
     </row>
-    <row r="420" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" s="1"/>
       <c r="B420" s="1" t="s">
         <v>1780</v>
@@ -33449,7 +33448,7 @@
       <c r="AC420" s="1"/>
       <c r="AD420" s="1"/>
     </row>
-    <row r="421" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="1"/>
       <c r="B421" s="1" t="s">
         <v>1780</v>
@@ -33509,7 +33508,7 @@
       <c r="AC421" s="1"/>
       <c r="AD421" s="1"/>
     </row>
-    <row r="422" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="1"/>
       <c r="B422" s="1" t="s">
         <v>1780</v>
@@ -33569,7 +33568,7 @@
       <c r="AC422" s="1"/>
       <c r="AD422" s="1"/>
     </row>
-    <row r="423" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="1"/>
       <c r="B423" s="1" t="s">
         <v>1780</v>
@@ -33629,7 +33628,7 @@
       <c r="AC423" s="1"/>
       <c r="AD423" s="1"/>
     </row>
-    <row r="424" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="1"/>
       <c r="B424" s="1" t="s">
         <v>1780</v>
@@ -33689,7 +33688,7 @@
       <c r="AC424" s="1"/>
       <c r="AD424" s="1"/>
     </row>
-    <row r="425" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="1"/>
       <c r="B425" s="1" t="s">
         <v>1780</v>
@@ -33749,7 +33748,7 @@
       <c r="AC425" s="1"/>
       <c r="AD425" s="1"/>
     </row>
-    <row r="426" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="1"/>
       <c r="B426" s="1" t="s">
         <v>1780</v>
@@ -33809,7 +33808,7 @@
       <c r="AC426" s="1"/>
       <c r="AD426" s="1"/>
     </row>
-    <row r="427" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="1"/>
       <c r="B427" s="1" t="s">
         <v>1780</v>
@@ -33869,7 +33868,7 @@
       <c r="AC427" s="1"/>
       <c r="AD427" s="1"/>
     </row>
-    <row r="428" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="1"/>
       <c r="B428" s="1" t="s">
         <v>1780</v>
@@ -33929,7 +33928,7 @@
       <c r="AC428" s="1"/>
       <c r="AD428" s="1"/>
     </row>
-    <row r="429" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="1"/>
       <c r="B429" s="1" t="s">
         <v>1780</v>
@@ -33989,7 +33988,7 @@
       <c r="AC429" s="1"/>
       <c r="AD429" s="1"/>
     </row>
-    <row r="430" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="1"/>
       <c r="B430" s="1" t="s">
         <v>1780</v>
@@ -34049,7 +34048,7 @@
       <c r="AC430" s="1"/>
       <c r="AD430" s="1"/>
     </row>
-    <row r="431" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="1"/>
       <c r="B431" s="1" t="s">
         <v>1780</v>
@@ -34109,7 +34108,7 @@
       <c r="AC431" s="1"/>
       <c r="AD431" s="1"/>
     </row>
-    <row r="432" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="1"/>
       <c r="B432" s="1" t="s">
         <v>1780</v>
@@ -34169,7 +34168,7 @@
       <c r="AC432" s="1"/>
       <c r="AD432" s="1"/>
     </row>
-    <row r="433" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="1"/>
       <c r="B433" s="1" t="s">
         <v>1780</v>
@@ -34229,7 +34228,7 @@
       <c r="AC433" s="1"/>
       <c r="AD433" s="1"/>
     </row>
-    <row r="434" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="1"/>
       <c r="B434" s="1" t="s">
         <v>1780</v>
@@ -34289,7 +34288,7 @@
       <c r="AC434" s="1"/>
       <c r="AD434" s="1"/>
     </row>
-    <row r="435" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="1"/>
       <c r="B435" s="1" t="s">
         <v>1780</v>
@@ -34349,7 +34348,7 @@
       <c r="AC435" s="1"/>
       <c r="AD435" s="1"/>
     </row>
-    <row r="436" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="1"/>
       <c r="B436" s="1" t="s">
         <v>1780</v>
@@ -34409,7 +34408,7 @@
       <c r="AC436" s="1"/>
       <c r="AD436" s="1"/>
     </row>
-    <row r="437" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="1"/>
       <c r="B437" s="1" t="s">
         <v>1780</v>
@@ -34469,7 +34468,7 @@
       <c r="AC437" s="1"/>
       <c r="AD437" s="1"/>
     </row>
-    <row r="438" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="1"/>
       <c r="B438" s="1" t="s">
         <v>1780</v>
@@ -34529,7 +34528,7 @@
       <c r="AC438" s="1"/>
       <c r="AD438" s="1"/>
     </row>
-    <row r="439" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" s="1"/>
       <c r="B439" s="1" t="s">
         <v>1780</v>
@@ -34589,7 +34588,7 @@
       <c r="AC439" s="1"/>
       <c r="AD439" s="1"/>
     </row>
-    <row r="440" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" s="1"/>
       <c r="B440" s="1" t="s">
         <v>1780</v>
@@ -34649,7 +34648,7 @@
       <c r="AC440" s="1"/>
       <c r="AD440" s="1"/>
     </row>
-    <row r="441" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="1"/>
       <c r="B441" s="1" t="s">
         <v>1780</v>
@@ -34709,7 +34708,7 @@
       <c r="AC441" s="1"/>
       <c r="AD441" s="1"/>
     </row>
-    <row r="442" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="1"/>
       <c r="B442" s="1" t="s">
         <v>1780</v>
@@ -34769,7 +34768,7 @@
       <c r="AC442" s="1"/>
       <c r="AD442" s="1"/>
     </row>
-    <row r="443" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="1"/>
       <c r="B443" s="1" t="s">
         <v>1780</v>
@@ -34829,7 +34828,7 @@
       <c r="AC443" s="1"/>
       <c r="AD443" s="1"/>
     </row>
-    <row r="444" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="1"/>
       <c r="B444" s="1" t="s">
         <v>1780</v>
@@ -34889,7 +34888,7 @@
       <c r="AC444" s="1"/>
       <c r="AD444" s="1"/>
     </row>
-    <row r="445" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="1"/>
       <c r="B445" s="1" t="s">
         <v>1780</v>
@@ -34949,7 +34948,7 @@
       <c r="AC445" s="1"/>
       <c r="AD445" s="1"/>
     </row>
-    <row r="446" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="1"/>
       <c r="B446" s="1" t="s">
         <v>1780</v>
@@ -35009,7 +35008,7 @@
       <c r="AC446" s="1"/>
       <c r="AD446" s="1"/>
     </row>
-    <row r="447" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="1"/>
       <c r="B447" s="1" t="s">
         <v>1780</v>
@@ -35069,7 +35068,7 @@
       <c r="AC447" s="1"/>
       <c r="AD447" s="1"/>
     </row>
-    <row r="448" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" s="1"/>
       <c r="B448" s="1" t="s">
         <v>1780</v>
@@ -35129,7 +35128,7 @@
       <c r="AC448" s="1"/>
       <c r="AD448" s="1"/>
     </row>
-    <row r="449" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="1"/>
       <c r="B449" s="1" t="s">
         <v>1780</v>
@@ -35189,7 +35188,7 @@
       <c r="AC449" s="1"/>
       <c r="AD449" s="1"/>
     </row>
-    <row r="450" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="1"/>
       <c r="B450" s="1" t="s">
         <v>1780</v>
@@ -35249,7 +35248,7 @@
       <c r="AC450" s="1"/>
       <c r="AD450" s="1"/>
     </row>
-    <row r="451" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="1"/>
       <c r="B451" s="1" t="s">
         <v>1780</v>
@@ -35309,7 +35308,7 @@
       <c r="AC451" s="1"/>
       <c r="AD451" s="1"/>
     </row>
-    <row r="452" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="1"/>
       <c r="B452" s="1" t="s">
         <v>1780</v>
@@ -35369,7 +35368,7 @@
       <c r="AC452" s="1"/>
       <c r="AD452" s="1"/>
     </row>
-    <row r="453" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="1"/>
       <c r="B453" s="1" t="s">
         <v>29</v>
@@ -35437,7 +35436,7 @@
       <c r="AC453" s="1"/>
       <c r="AD453" s="1"/>
     </row>
-    <row r="454" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="1"/>
       <c r="B454" s="1" t="s">
         <v>29</v>
@@ -35505,7 +35504,7 @@
       <c r="AC454" s="1"/>
       <c r="AD454" s="1"/>
     </row>
-    <row r="455" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="1"/>
       <c r="B455" s="1" t="s">
         <v>29</v>
@@ -35573,7 +35572,7 @@
       <c r="AC455" s="1"/>
       <c r="AD455" s="1"/>
     </row>
-    <row r="456" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="1"/>
       <c r="B456" s="1" t="s">
         <v>2190</v>
@@ -35627,7 +35626,7 @@
       <c r="AC456" s="1"/>
       <c r="AD456" s="1"/>
     </row>
-    <row r="457" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="1"/>
       <c r="B457" s="1" t="s">
         <v>2193</v>
@@ -35689,7 +35688,7 @@
       <c r="AC457" s="1"/>
       <c r="AD457" s="1"/>
     </row>
-    <row r="458" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="1"/>
       <c r="B458" s="1" t="s">
         <v>2193</v>
@@ -35751,7 +35750,7 @@
       <c r="AC458" s="1"/>
       <c r="AD458" s="1"/>
     </row>
-    <row r="459" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="1"/>
       <c r="B459" s="1" t="s">
         <v>2204</v>
@@ -35819,7 +35818,7 @@
       <c r="AC459" s="1"/>
       <c r="AD459" s="1"/>
     </row>
-    <row r="460" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="1"/>
       <c r="B460" s="1" t="s">
         <v>1726</v>
@@ -35885,7 +35884,7 @@
       <c r="AC460" s="1"/>
       <c r="AD460" s="1"/>
     </row>
-    <row r="461" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" s="1"/>
       <c r="B461" s="1" t="s">
         <v>2217</v>
@@ -35947,7 +35946,7 @@
       <c r="AC461" s="1"/>
       <c r="AD461" s="1"/>
     </row>
-    <row r="462" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="1"/>
       <c r="B462" s="1" t="s">
         <v>499</v>
@@ -36013,7 +36012,7 @@
       <c r="AC462" s="1"/>
       <c r="AD462" s="1"/>
     </row>
-    <row r="463" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="1"/>
       <c r="B463" s="1" t="s">
         <v>2231</v>
@@ -36083,7 +36082,7 @@
       <c r="AC463" s="1"/>
       <c r="AD463" s="1"/>
     </row>
-    <row r="464" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" s="1"/>
       <c r="B464" s="1" t="s">
         <v>2231</v>
@@ -36153,7 +36152,7 @@
       <c r="AC464" s="1"/>
       <c r="AD464" s="1"/>
     </row>
-    <row r="465" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="1"/>
       <c r="B465" s="1" t="s">
         <v>2242</v>
@@ -36219,7 +36218,7 @@
       <c r="AC465" s="1"/>
       <c r="AD465" s="1"/>
     </row>
-    <row r="466" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="1"/>
       <c r="B466" s="1" t="s">
         <v>2242</v>
@@ -36285,7 +36284,7 @@
       <c r="AC466" s="1"/>
       <c r="AD466" s="1"/>
     </row>
-    <row r="467" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="1"/>
       <c r="B467" s="1" t="s">
         <v>2242</v>
@@ -36351,7 +36350,7 @@
       <c r="AC467" s="1"/>
       <c r="AD467" s="1"/>
     </row>
-    <row r="468" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="1"/>
       <c r="B468" s="1" t="s">
         <v>2242</v>
@@ -36417,7 +36416,7 @@
       <c r="AC468" s="1"/>
       <c r="AD468" s="1"/>
     </row>
-    <row r="469" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="1"/>
       <c r="B469" s="1" t="s">
         <v>2242</v>
@@ -36483,7 +36482,7 @@
       <c r="AC469" s="1"/>
       <c r="AD469" s="1"/>
     </row>
-    <row r="470" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="1"/>
       <c r="B470" s="1" t="s">
         <v>2266</v>
@@ -36549,7 +36548,7 @@
       <c r="AC470" s="1"/>
       <c r="AD470" s="1"/>
     </row>
-    <row r="471" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="1"/>
       <c r="B471" s="1" t="s">
         <v>2266</v>
@@ -36615,7 +36614,7 @@
       <c r="AC471" s="1"/>
       <c r="AD471" s="1"/>
     </row>
-    <row r="472" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="1"/>
       <c r="B472" s="1" t="s">
         <v>2266</v>
@@ -36681,7 +36680,7 @@
       <c r="AC472" s="1"/>
       <c r="AD472" s="1"/>
     </row>
-    <row r="473" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="1"/>
       <c r="B473" s="1" t="s">
         <v>499</v>
@@ -36747,7 +36746,7 @@
       <c r="AC473" s="1"/>
       <c r="AD473" s="1"/>
     </row>
-    <row r="474" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="1"/>
       <c r="B474" s="1" t="s">
         <v>499</v>
@@ -36813,7 +36812,7 @@
       <c r="AC474" s="1"/>
       <c r="AD474" s="1"/>
     </row>
-    <row r="475" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="1"/>
       <c r="B475" s="1" t="s">
         <v>2290</v>
@@ -36879,7 +36878,7 @@
       <c r="AC475" s="1"/>
       <c r="AD475" s="1"/>
     </row>
-    <row r="476" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="1"/>
       <c r="B476" s="1" t="s">
         <v>2296</v>
@@ -36943,7 +36942,7 @@
       </c>
       <c r="AD476" s="1"/>
     </row>
-    <row r="477" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="1"/>
       <c r="B477" s="1" t="s">
         <v>1179</v>
@@ -37003,7 +37002,7 @@
       <c r="AC477" s="1"/>
       <c r="AD477" s="1"/>
     </row>
-    <row r="478" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="1"/>
       <c r="B478" s="1" t="s">
         <v>1303</v>
@@ -37063,7 +37062,7 @@
       <c r="AC478" s="1"/>
       <c r="AD478" s="1"/>
     </row>
-    <row r="479" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="1"/>
       <c r="B479" s="1" t="s">
         <v>2312</v>
@@ -37123,7 +37122,7 @@
       <c r="AC479" s="1"/>
       <c r="AD479" s="1"/>
     </row>
-    <row r="480" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="1"/>
       <c r="B480" s="1" t="s">
         <v>2318</v>
@@ -37183,7 +37182,7 @@
       <c r="AC480" s="1"/>
       <c r="AD480" s="1"/>
     </row>
-    <row r="481" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" s="1"/>
       <c r="B481" s="1" t="s">
         <v>777</v>
@@ -37243,7 +37242,7 @@
       <c r="AC481" s="1"/>
       <c r="AD481" s="1"/>
     </row>
-    <row r="482" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="1"/>
       <c r="B482" s="1" t="s">
         <v>2327</v>
@@ -37303,7 +37302,7 @@
       <c r="AC482" s="1"/>
       <c r="AD482" s="1"/>
     </row>
-    <row r="483" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="1"/>
       <c r="B483" s="1" t="s">
         <v>2333</v>
@@ -37363,7 +37362,7 @@
       <c r="AC483" s="1"/>
       <c r="AD483" s="1"/>
     </row>
-    <row r="484" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="1"/>
       <c r="B484" s="1" t="s">
         <v>578</v>
@@ -37423,7 +37422,7 @@
       <c r="AC484" s="1"/>
       <c r="AD484" s="1"/>
     </row>
-    <row r="485" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="1"/>
       <c r="B485" s="1" t="s">
         <v>2343</v>
@@ -37483,7 +37482,7 @@
       <c r="AC485" s="1"/>
       <c r="AD485" s="1"/>
     </row>
-    <row r="486" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="1"/>
       <c r="B486" s="1" t="s">
         <v>726</v>
@@ -37547,7 +37546,7 @@
       <c r="AC486" s="1"/>
       <c r="AD486" s="1"/>
     </row>
-    <row r="487" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="1"/>
       <c r="B487" s="1" t="s">
         <v>2354</v>
@@ -37607,7 +37606,7 @@
       <c r="AC487" s="1"/>
       <c r="AD487" s="1"/>
     </row>
-    <row r="488" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="1"/>
       <c r="B488" s="1" t="s">
         <v>2360</v>
@@ -37671,7 +37670,7 @@
       <c r="AC488" s="1"/>
       <c r="AD488" s="1"/>
     </row>
-    <row r="489" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="1"/>
       <c r="B489" s="1" t="s">
         <v>918</v>
@@ -37735,7 +37734,7 @@
       <c r="AC489" s="1"/>
       <c r="AD489" s="1"/>
     </row>
-    <row r="490" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="1"/>
       <c r="B490" s="1" t="s">
         <v>2369</v>
@@ -37799,7 +37798,7 @@
       <c r="AC490" s="1"/>
       <c r="AD490" s="1"/>
     </row>
-    <row r="491" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="1"/>
       <c r="B491" s="1" t="s">
         <v>2374</v>
@@ -37859,7 +37858,7 @@
       <c r="AC491" s="1"/>
       <c r="AD491" s="1"/>
     </row>
-    <row r="492" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="1"/>
       <c r="B492" s="1" t="s">
         <v>2374</v>
@@ -37919,7 +37918,7 @@
       <c r="AC492" s="1"/>
       <c r="AD492" s="1"/>
     </row>
-    <row r="493" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="1"/>
       <c r="B493" s="1" t="s">
         <v>2374</v>
@@ -37983,7 +37982,7 @@
       <c r="AC493" s="1"/>
       <c r="AD493" s="1"/>
     </row>
-    <row r="494" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="1"/>
       <c r="B494" s="1" t="s">
         <v>2374</v>
@@ -38047,7 +38046,7 @@
       <c r="AC494" s="1"/>
       <c r="AD494" s="1"/>
     </row>
-    <row r="495" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" s="1"/>
       <c r="B495" s="1" t="s">
         <v>2394</v>
@@ -38107,7 +38106,7 @@
       <c r="AC495" s="1"/>
       <c r="AD495" s="1"/>
     </row>
-    <row r="496" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" s="1"/>
       <c r="B496" s="1" t="s">
         <v>2398</v>
@@ -38171,7 +38170,7 @@
       <c r="AC496" s="1"/>
       <c r="AD496" s="1"/>
     </row>
-    <row r="497" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" s="1"/>
       <c r="B497" s="1" t="s">
         <v>2404</v>
@@ -38235,7 +38234,7 @@
       <c r="AC497" s="1"/>
       <c r="AD497" s="1"/>
     </row>
-    <row r="498" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="1"/>
       <c r="B498" s="1" t="s">
         <v>2404</v>
@@ -38295,7 +38294,7 @@
       <c r="AC498" s="1"/>
       <c r="AD498" s="1"/>
     </row>
-    <row r="499" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" s="1"/>
       <c r="B499" s="1" t="s">
         <v>2416</v>
@@ -38355,7 +38354,7 @@
       <c r="AC499" s="1"/>
       <c r="AD499" s="1"/>
     </row>
-    <row r="500" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" s="1"/>
       <c r="B500" s="1" t="s">
         <v>2420</v>
@@ -38415,7 +38414,7 @@
       <c r="AC500" s="1"/>
       <c r="AD500" s="1"/>
     </row>
-    <row r="501" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="1"/>
       <c r="B501" s="1" t="s">
         <v>2426</v>
@@ -38475,7 +38474,7 @@
       <c r="AC501" s="1"/>
       <c r="AD501" s="1"/>
     </row>
-    <row r="502" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502" s="1"/>
       <c r="B502" s="1" t="s">
         <v>2431</v>
@@ -38535,7 +38534,7 @@
       <c r="AC502" s="1"/>
       <c r="AD502" s="1"/>
     </row>
-    <row r="503" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="1"/>
       <c r="B503" s="1" t="s">
         <v>29</v>
@@ -38599,7 +38598,7 @@
       <c r="AC503" s="1"/>
       <c r="AD503" s="1"/>
     </row>
-    <row r="504" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="1"/>
       <c r="B504" s="1" t="s">
         <v>29</v>
@@ -38663,7 +38662,7 @@
       <c r="AC504" s="1"/>
       <c r="AD504" s="1"/>
     </row>
-    <row r="505" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="1"/>
       <c r="B505" s="1" t="s">
         <v>29</v>
@@ -38727,7 +38726,7 @@
       <c r="AC505" s="1"/>
       <c r="AD505" s="1"/>
     </row>
-    <row r="506" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506" s="1"/>
       <c r="B506" s="1" t="s">
         <v>2451</v>
@@ -38791,7 +38790,7 @@
       <c r="AC506" s="1"/>
       <c r="AD506" s="1"/>
     </row>
-    <row r="507" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507" s="1"/>
       <c r="B507" s="1" t="s">
         <v>2459</v>
@@ -38855,7 +38854,7 @@
       <c r="AC507" s="1"/>
       <c r="AD507" s="1"/>
     </row>
-    <row r="508" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508" s="1"/>
       <c r="B508" s="1" t="s">
         <v>2465</v>
@@ -38919,7 +38918,7 @@
       <c r="AC508" s="1"/>
       <c r="AD508" s="1"/>
     </row>
-    <row r="509" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509" s="1"/>
       <c r="B509" s="1" t="s">
         <v>2471</v>
@@ -38983,7 +38982,7 @@
       <c r="AC509" s="1"/>
       <c r="AD509" s="1"/>
     </row>
-    <row r="510" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510" s="1"/>
       <c r="B510" s="1" t="s">
         <v>2471</v>
@@ -39047,7 +39046,7 @@
       <c r="AC510" s="1"/>
       <c r="AD510" s="1"/>
     </row>
-    <row r="511" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511" s="1"/>
       <c r="B511" s="1" t="s">
         <v>2471</v>
@@ -39111,7 +39110,7 @@
       <c r="AC511" s="1"/>
       <c r="AD511" s="1"/>
     </row>
-    <row r="512" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A512" s="1"/>
       <c r="B512" s="1" t="s">
         <v>2471</v>
@@ -39175,7 +39174,7 @@
       <c r="AC512" s="1"/>
       <c r="AD512" s="1"/>
     </row>
-    <row r="513" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A513" s="1"/>
       <c r="B513" s="1" t="s">
         <v>1384</v>
@@ -39239,7 +39238,7 @@
       <c r="AC513" s="1"/>
       <c r="AD513" s="1"/>
     </row>
-    <row r="514" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A514" s="1"/>
       <c r="B514" s="1" t="s">
         <v>578</v>
@@ -39311,7 +39310,7 @@
       <c r="AC514" s="1"/>
       <c r="AD514" s="1"/>
     </row>
-    <row r="515" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A515" s="1"/>
       <c r="B515" s="1" t="s">
         <v>578</v>
@@ -39383,7 +39382,7 @@
       <c r="AC515" s="1"/>
       <c r="AD515" s="1"/>
     </row>
-    <row r="516" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A516" s="1"/>
       <c r="B516" s="1" t="s">
         <v>2506</v>
@@ -39451,7 +39450,7 @@
       <c r="AC516" s="1"/>
       <c r="AD516" s="1"/>
     </row>
-    <row r="517" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A517" s="1"/>
       <c r="B517" s="1" t="s">
         <v>2513</v>
@@ -39523,7 +39522,7 @@
       <c r="AC517" s="1"/>
       <c r="AD517" s="1"/>
     </row>
-    <row r="518" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A518" s="1"/>
       <c r="B518" s="1" t="s">
         <v>2513</v>
@@ -39595,7 +39594,7 @@
       <c r="AC518" s="1"/>
       <c r="AD518" s="1"/>
     </row>
-    <row r="519" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A519" s="1"/>
       <c r="B519" s="1" t="s">
         <v>2513</v>
@@ -39667,7 +39666,7 @@
       <c r="AC519" s="1"/>
       <c r="AD519" s="1"/>
     </row>
-    <row r="520" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="1"/>
       <c r="B520" s="1" t="s">
         <v>2513</v>
@@ -39739,7 +39738,7 @@
       <c r="AC520" s="1"/>
       <c r="AD520" s="1"/>
     </row>
-    <row r="521" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="1"/>
       <c r="B521" s="1" t="s">
         <v>2513</v>
@@ -39811,7 +39810,7 @@
       <c r="AC521" s="1"/>
       <c r="AD521" s="1"/>
     </row>
-    <row r="522" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A522" s="1"/>
       <c r="B522" s="1" t="s">
         <v>2513</v>
@@ -39883,7 +39882,7 @@
       <c r="AC522" s="1"/>
       <c r="AD522" s="1"/>
     </row>
-    <row r="523" spans="1:30" ht="15.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="1"/>
       <c r="B523" s="1" t="s">
         <v>2513</v>
@@ -40952,13 +40951,7 @@
       <c r="AD539" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC537" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="18">
-      <filters>
-        <filter val="true-&gt;3.20新增"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AC537" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -41134,33 +41127,73 @@
     </row>
     <row r="3" spans="1:30" ht="15.95" customHeight="true">
       <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>2204</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2204</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>2205</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>2206</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2206</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>2207</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>2208</v>
+      </c>
+      <c r="K3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>2209</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>2210</v>
+      </c>
+      <c r="N3" s="1">
+        <v>1</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>2211</v>
+      </c>
       <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
+      <c r="S3" s="1" t="s">
+        <v>223</v>
+      </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
+      <c r="Z3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
     </row>

--- a/excel/机型库-根据算法部修改-回放信号.xlsx
+++ b/excel/机型库-根据算法部修改-回放信号.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="31605" yWindow="3060" windowWidth="29970" windowHeight="14220" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="29970" windowHeight="14220" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="机型库1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8443" uniqueCount="2742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8449" uniqueCount="2744">
   <si>
     <t>ID (命名：协议-子协议-品牌-机型-频段-详细频率)</t>
   </si>
@@ -7981,13 +7981,6 @@
     <t>YRRC_433_8001_433_433</t>
   </si>
   <si>
-    <t>D:\xinhao-all\YRRC\YRRC_433_8001_433_433</t>
-  </si>
-  <si>
-    <t>ARDUPILOT General
-:923000</t>
-  </si>
-  <si>
     <t>01040019/随机</t>
   </si>
   <si>
@@ -8060,12 +8053,6 @@
     <t>Radiolink-R16F_8001_2400_2464</t>
   </si>
   <si>
-    <t>D:\xinhao-all\RadioLink\Radiolink-R16F_8001_2400_2464</t>
-  </si>
-  <si>
-    <t>RADIOLINK R16F:2464000</t>
-  </si>
-  <si>
     <t>80000068/随机</t>
   </si>
   <si>
@@ -8141,12 +8128,6 @@
     <t>MicoAir_LR900_8001_900_923</t>
   </si>
   <si>
-    <t>D:\xinhao-all\Micoair\MicoAir_LR900_8001_900_923</t>
-  </si>
-  <si>
-    <t>MicoAir_LR900:908000</t>
-  </si>
-  <si>
     <t>0501/随机</t>
   </si>
   <si>
@@ -8249,15 +8230,41 @@
     <t>465300080010/随机</t>
   </si>
   <si>
-    <t>true-&gt;8001</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>546</t>
+  </si>
+  <si>
+    <t>E:\xinhao-all\Micoair\MicoAir_LR900_8001_900_923</t>
+  </si>
+  <si>
+    <t>MicoAir LR900:908000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>542</t>
+  </si>
+  <si>
+    <t>E:\xinhao-all\RadioLink\Radiolink-R16F_8001_2400_2464</t>
+  </si>
+  <si>
+    <t>RADIOLINK T16D:2421000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>537</t>
+  </si>
+  <si>
+    <t>E:\xinhao-all\YRRC\YRRC_433_8001_433_433</t>
+  </si>
+  <si>
+    <t>ARDUPILOT General:923000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -8269,6 +8276,7 @@
       <b val="1"/>
       <sz val="14"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -8277,6 +8285,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -8321,7 +8335,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8331,6 +8345,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -8762,7 +8777,9 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2"/>
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
       <c r="B2" s="2" t="s">
         <v>30</v>
       </c>
@@ -8806,7 +8823,9 @@
       <c r="AD2" s="2"/>
     </row>
     <row r="3" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
       <c r="B3" s="2" t="s">
         <v>30</v>
       </c>
@@ -8852,7 +8871,9 @@
       <c r="AD3" s="2"/>
     </row>
     <row r="4" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
       <c r="B4" s="2" t="s">
         <v>30</v>
       </c>
@@ -8896,7 +8917,9 @@
       <c r="AD4" s="2"/>
     </row>
     <row r="5" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
       <c r="B5" s="2" t="s">
         <v>30</v>
       </c>
@@ -8940,7 +8963,9 @@
       <c r="AD5" s="2"/>
     </row>
     <row r="6" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
       <c r="B6" s="2" t="s">
         <v>30</v>
       </c>
@@ -8984,7 +9009,9 @@
       <c r="AD6" s="2"/>
     </row>
     <row r="7" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
       <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
@@ -9028,7 +9055,9 @@
       <c r="AD7" s="2"/>
     </row>
     <row r="8" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
       <c r="B8" s="2" t="s">
         <v>30</v>
       </c>
@@ -9070,7 +9099,9 @@
       <c r="AD8" s="2"/>
     </row>
     <row r="9" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
       <c r="B9" s="2" t="s">
         <v>30</v>
       </c>
@@ -9114,7 +9145,9 @@
       <c r="AD9" s="2"/>
     </row>
     <row r="10" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
       <c r="B10" s="2" t="s">
         <v>30</v>
       </c>
@@ -9184,7 +9217,9 @@
       <c r="AD10" s="2"/>
     </row>
     <row r="11" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
       <c r="B11" s="2" t="s">
         <v>30</v>
       </c>
@@ -9256,7 +9291,9 @@
       <c r="AD11" s="2"/>
     </row>
     <row r="12" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
       <c r="B12" s="2" t="s">
         <v>30</v>
       </c>
@@ -9328,7 +9365,9 @@
       <c r="AD12" s="2"/>
     </row>
     <row r="13" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
       <c r="B13" s="2" t="s">
         <v>30</v>
       </c>
@@ -9402,7 +9441,9 @@
       <c r="AD13" s="2"/>
     </row>
     <row r="14" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
       <c r="B14" s="2" t="s">
         <v>30</v>
       </c>
@@ -9446,7 +9487,9 @@
       <c r="AD14" s="2"/>
     </row>
     <row r="15" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
       <c r="B15" s="2" t="s">
         <v>30</v>
       </c>
@@ -9490,7 +9533,9 @@
       <c r="AD15" s="2"/>
     </row>
     <row r="16" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
       <c r="B16" s="2" t="s">
         <v>30</v>
       </c>
@@ -9534,7 +9579,9 @@
       <c r="AD16" s="2"/>
     </row>
     <row r="17" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
       <c r="B17" s="2" t="s">
         <v>30</v>
       </c>
@@ -9578,7 +9625,9 @@
       <c r="AD17" s="2"/>
     </row>
     <row r="18" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
       <c r="B18" s="2" t="s">
         <v>30</v>
       </c>
@@ -9622,7 +9671,9 @@
       <c r="AD18" s="2"/>
     </row>
     <row r="19" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
       <c r="B19" s="2" t="s">
         <v>30</v>
       </c>
@@ -9680,7 +9731,9 @@
       <c r="AD19" s="2"/>
     </row>
     <row r="20" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
       <c r="B20" s="2" t="s">
         <v>30</v>
       </c>
@@ -9738,7 +9791,9 @@
       <c r="AD20" s="2"/>
     </row>
     <row r="21" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
       <c r="B21" s="2" t="s">
         <v>30</v>
       </c>
@@ -9796,7 +9851,9 @@
       <c r="AD21" s="2"/>
     </row>
     <row r="22" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
       <c r="B22" s="2" t="s">
         <v>30</v>
       </c>
@@ -9854,7 +9911,9 @@
       <c r="AD22" s="2"/>
     </row>
     <row r="23" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
       <c r="B23" s="2" t="s">
         <v>30</v>
       </c>
@@ -9912,7 +9971,9 @@
       <c r="AD23" s="2"/>
     </row>
     <row r="24" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
       <c r="B24" s="2" t="s">
         <v>30</v>
       </c>
@@ -9976,7 +10037,9 @@
       <c r="AD24" s="2"/>
     </row>
     <row r="25" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
       <c r="B25" s="2" t="s">
         <v>30</v>
       </c>
@@ -10026,7 +10089,9 @@
       <c r="AD25" s="2"/>
     </row>
     <row r="26" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
       <c r="B26" s="2" t="s">
         <v>30</v>
       </c>
@@ -10070,7 +10135,9 @@
       <c r="AD26" s="2"/>
     </row>
     <row r="27" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="2"/>
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
@@ -10114,7 +10181,9 @@
       <c r="AD27" s="2"/>
     </row>
     <row r="28" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="2"/>
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
       <c r="B28" s="2" t="s">
         <v>30</v>
       </c>
@@ -10158,7 +10227,9 @@
       <c r="AD28" s="2"/>
     </row>
     <row r="29" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
       <c r="B29" s="2" t="s">
         <v>30</v>
       </c>
@@ -10230,7 +10301,9 @@
       <c r="AD29" s="2"/>
     </row>
     <row r="30" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="2"/>
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
       <c r="B30" s="2" t="s">
         <v>30</v>
       </c>
@@ -10302,7 +10375,9 @@
       <c r="AD30" s="2"/>
     </row>
     <row r="31" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="2"/>
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
       <c r="B31" s="2" t="s">
         <v>30</v>
       </c>
@@ -10374,7 +10449,9 @@
       <c r="AD31" s="2"/>
     </row>
     <row r="32" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="2"/>
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
       <c r="B32" s="2" t="s">
         <v>30</v>
       </c>
@@ -10418,7 +10495,9 @@
       <c r="AD32" s="2"/>
     </row>
     <row r="33" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="2"/>
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
       <c r="B33" s="2" t="s">
         <v>30</v>
       </c>
@@ -10462,7 +10541,9 @@
       <c r="AD33" s="2"/>
     </row>
     <row r="34" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="2"/>
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
       <c r="B34" s="2" t="s">
         <v>30</v>
       </c>
@@ -10534,7 +10615,9 @@
       <c r="AD34" s="2"/>
     </row>
     <row r="35" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="2"/>
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
       <c r="B35" s="2" t="s">
         <v>30</v>
       </c>
@@ -10606,7 +10689,9 @@
       <c r="AD35" s="2"/>
     </row>
     <row r="36" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="2"/>
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
       <c r="B36" s="2" t="s">
         <v>30</v>
       </c>
@@ -10680,7 +10765,9 @@
       <c r="AD36" s="2"/>
     </row>
     <row r="37" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="2"/>
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
       <c r="B37" s="2" t="s">
         <v>30</v>
       </c>
@@ -10754,7 +10841,9 @@
       <c r="AD37" s="2"/>
     </row>
     <row r="38" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="2"/>
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
       <c r="B38" s="2" t="s">
         <v>30</v>
       </c>
@@ -10798,7 +10887,9 @@
       <c r="AD38" s="2"/>
     </row>
     <row r="39" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="2"/>
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
       <c r="B39" s="2" t="s">
         <v>30</v>
       </c>
@@ -10842,7 +10933,9 @@
       <c r="AD39" s="2"/>
     </row>
     <row r="40" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="2"/>
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
       <c r="B40" s="2" t="s">
         <v>30</v>
       </c>
@@ -10886,7 +10979,9 @@
       <c r="AD40" s="2"/>
     </row>
     <row r="41" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="2"/>
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
       <c r="B41" s="2" t="s">
         <v>30</v>
       </c>
@@ -10930,7 +11025,9 @@
       <c r="AD41" s="2"/>
     </row>
     <row r="42" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="2"/>
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
       <c r="B42" s="2" t="s">
         <v>30</v>
       </c>
@@ -11000,7 +11097,9 @@
       <c r="AD42" s="2"/>
     </row>
     <row r="43" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="2"/>
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
       <c r="B43" s="2" t="s">
         <v>30</v>
       </c>
@@ -11070,7 +11169,9 @@
       <c r="AD43" s="2"/>
     </row>
     <row r="44" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="2"/>
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
       <c r="B44" s="2" t="s">
         <v>30</v>
       </c>
@@ -11144,7 +11245,9 @@
       <c r="AD44" s="2"/>
     </row>
     <row r="45" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="2"/>
+      <c r="A45" s="3">
+        <v>44</v>
+      </c>
       <c r="B45" s="2" t="s">
         <v>30</v>
       </c>
@@ -11188,7 +11291,9 @@
       <c r="AD45" s="2"/>
     </row>
     <row r="46" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="2"/>
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
       <c r="B46" s="2" t="s">
         <v>30</v>
       </c>
@@ -11232,7 +11337,9 @@
       <c r="AD46" s="2"/>
     </row>
     <row r="47" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="2"/>
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
       <c r="B47" s="2" t="s">
         <v>30</v>
       </c>
@@ -11304,7 +11411,9 @@
       <c r="AD47" s="2"/>
     </row>
     <row r="48" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="2"/>
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
       <c r="B48" s="2" t="s">
         <v>30</v>
       </c>
@@ -11376,7 +11485,9 @@
       <c r="AD48" s="2"/>
     </row>
     <row r="49" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="2"/>
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
       <c r="B49" s="2" t="s">
         <v>30</v>
       </c>
@@ -11420,7 +11531,9 @@
       <c r="AD49" s="2"/>
     </row>
     <row r="50" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="2"/>
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
       <c r="B50" s="2" t="s">
         <v>30</v>
       </c>
@@ -11464,7 +11577,9 @@
       <c r="AD50" s="2"/>
     </row>
     <row r="51" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="2"/>
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
       <c r="B51" s="2" t="s">
         <v>30</v>
       </c>
@@ -11508,7 +11623,9 @@
       <c r="AD51" s="2"/>
     </row>
     <row r="52" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="2"/>
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
       <c r="B52" s="2" t="s">
         <v>30</v>
       </c>
@@ -11552,7 +11669,9 @@
       <c r="AD52" s="2"/>
     </row>
     <row r="53" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="2"/>
+      <c r="A53" s="3">
+        <v>52</v>
+      </c>
       <c r="B53" s="2" t="s">
         <v>30</v>
       </c>
@@ -11596,7 +11715,9 @@
       <c r="AD53" s="2"/>
     </row>
     <row r="54" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="2"/>
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
       <c r="B54" s="2" t="s">
         <v>30</v>
       </c>
@@ -11640,7 +11761,9 @@
       <c r="AD54" s="2"/>
     </row>
     <row r="55" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="2"/>
+      <c r="A55" s="3">
+        <v>54</v>
+      </c>
       <c r="B55" s="2" t="s">
         <v>30</v>
       </c>
@@ -11684,7 +11807,9 @@
       <c r="AD55" s="2"/>
     </row>
     <row r="56" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="2"/>
+      <c r="A56" s="3">
+        <v>55</v>
+      </c>
       <c r="B56" s="2" t="s">
         <v>30</v>
       </c>
@@ -11728,7 +11853,9 @@
       <c r="AD56" s="2"/>
     </row>
     <row r="57" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="2"/>
+      <c r="A57" s="3">
+        <v>56</v>
+      </c>
       <c r="B57" s="2" t="s">
         <v>30</v>
       </c>
@@ -11772,7 +11899,9 @@
       <c r="AD57" s="2"/>
     </row>
     <row r="58" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="2"/>
+      <c r="A58" s="3">
+        <v>57</v>
+      </c>
       <c r="B58" s="2" t="s">
         <v>30</v>
       </c>
@@ -11816,7 +11945,9 @@
       <c r="AD58" s="2"/>
     </row>
     <row r="59" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="2"/>
+      <c r="A59" s="3">
+        <v>58</v>
+      </c>
       <c r="B59" s="2" t="s">
         <v>30</v>
       </c>
@@ -11860,7 +11991,9 @@
       <c r="AD59" s="2"/>
     </row>
     <row r="60" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="2"/>
+      <c r="A60" s="3">
+        <v>59</v>
+      </c>
       <c r="B60" s="2" t="s">
         <v>30</v>
       </c>
@@ -11934,7 +12067,9 @@
       <c r="AD60" s="2"/>
     </row>
     <row r="61" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="2"/>
+      <c r="A61" s="3">
+        <v>60</v>
+      </c>
       <c r="B61" s="2" t="s">
         <v>30</v>
       </c>
@@ -12008,7 +12143,9 @@
       <c r="AD61" s="2"/>
     </row>
     <row r="62" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="2"/>
+      <c r="A62" s="3">
+        <v>61</v>
+      </c>
       <c r="B62" s="2" t="s">
         <v>30</v>
       </c>
@@ -12080,7 +12217,9 @@
       <c r="AD62" s="2"/>
     </row>
     <row r="63" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="2"/>
+      <c r="A63" s="3">
+        <v>62</v>
+      </c>
       <c r="B63" s="2" t="s">
         <v>30</v>
       </c>
@@ -12124,7 +12263,9 @@
       <c r="AD63" s="2"/>
     </row>
     <row r="64" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="2"/>
+      <c r="A64" s="3">
+        <v>63</v>
+      </c>
       <c r="B64" s="2" t="s">
         <v>30</v>
       </c>
@@ -12196,7 +12337,9 @@
       <c r="AD64" s="2"/>
     </row>
     <row r="65" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="2"/>
+      <c r="A65" s="3">
+        <v>64</v>
+      </c>
       <c r="B65" s="2" t="s">
         <v>30</v>
       </c>
@@ -12268,7 +12411,9 @@
       <c r="AD65" s="2"/>
     </row>
     <row r="66" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="2"/>
+      <c r="A66" s="3">
+        <v>65</v>
+      </c>
       <c r="B66" s="2" t="s">
         <v>30</v>
       </c>
@@ -12312,7 +12457,9 @@
       <c r="AD66" s="2"/>
     </row>
     <row r="67" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="2"/>
+      <c r="A67" s="3">
+        <v>66</v>
+      </c>
       <c r="B67" s="2" t="s">
         <v>30</v>
       </c>
@@ -12356,7 +12503,9 @@
       <c r="AD67" s="2"/>
     </row>
     <row r="68" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="2"/>
+      <c r="A68" s="3">
+        <v>67</v>
+      </c>
       <c r="B68" s="2" t="s">
         <v>30</v>
       </c>
@@ -12400,7 +12549,9 @@
       <c r="AD68" s="2"/>
     </row>
     <row r="69" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="2"/>
+      <c r="A69" s="3">
+        <v>68</v>
+      </c>
       <c r="B69" s="2" t="s">
         <v>30</v>
       </c>
@@ -12444,7 +12595,9 @@
       <c r="AD69" s="2"/>
     </row>
     <row r="70" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="2"/>
+      <c r="A70" s="3">
+        <v>69</v>
+      </c>
       <c r="B70" s="2" t="s">
         <v>255</v>
       </c>
@@ -12502,7 +12655,9 @@
       <c r="AD70" s="2"/>
     </row>
     <row r="71" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="2"/>
+      <c r="A71" s="3">
+        <v>70</v>
+      </c>
       <c r="B71" s="2" t="s">
         <v>255</v>
       </c>
@@ -12558,7 +12713,9 @@
       <c r="AD71" s="2"/>
     </row>
     <row r="72" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="2"/>
+      <c r="A72" s="3">
+        <v>71</v>
+      </c>
       <c r="B72" s="2" t="s">
         <v>255</v>
       </c>
@@ -12616,7 +12773,9 @@
       <c r="AD72" s="2"/>
     </row>
     <row r="73" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="2"/>
+      <c r="A73" s="3">
+        <v>72</v>
+      </c>
       <c r="B73" s="2" t="s">
         <v>255</v>
       </c>
@@ -12672,7 +12831,9 @@
       <c r="AD73" s="2"/>
     </row>
     <row r="74" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="2"/>
+      <c r="A74" s="3">
+        <v>73</v>
+      </c>
       <c r="B74" s="2" t="s">
         <v>255</v>
       </c>
@@ -12734,7 +12895,9 @@
       <c r="AD74" s="2"/>
     </row>
     <row r="75" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="2"/>
+      <c r="A75" s="3">
+        <v>74</v>
+      </c>
       <c r="B75" s="2" t="s">
         <v>255</v>
       </c>
@@ -12778,7 +12941,9 @@
       <c r="AD75" s="2"/>
     </row>
     <row r="76" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="2"/>
+      <c r="A76" s="3">
+        <v>75</v>
+      </c>
       <c r="B76" s="2" t="s">
         <v>255</v>
       </c>
@@ -12822,7 +12987,9 @@
       <c r="AD76" s="2"/>
     </row>
     <row r="77" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="2"/>
+      <c r="A77" s="3">
+        <v>76</v>
+      </c>
       <c r="B77" s="2" t="s">
         <v>255</v>
       </c>
@@ -12894,7 +13061,9 @@
       <c r="AD77" s="2"/>
     </row>
     <row r="78" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="2"/>
+      <c r="A78" s="3">
+        <v>77</v>
+      </c>
       <c r="B78" s="2" t="s">
         <v>255</v>
       </c>
@@ -12944,7 +13113,9 @@
       <c r="AD78" s="2"/>
     </row>
     <row r="79" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="2"/>
+      <c r="A79" s="3">
+        <v>78</v>
+      </c>
       <c r="B79" s="2" t="s">
         <v>255</v>
       </c>
@@ -12988,7 +13159,9 @@
       <c r="AD79" s="2"/>
     </row>
     <row r="80" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="2"/>
+      <c r="A80" s="3">
+        <v>79</v>
+      </c>
       <c r="B80" s="2" t="s">
         <v>255</v>
       </c>
@@ -13056,7 +13229,9 @@
       <c r="AD80" s="2"/>
     </row>
     <row r="81" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="2"/>
+      <c r="A81" s="3">
+        <v>80</v>
+      </c>
       <c r="B81" s="2" t="s">
         <v>255</v>
       </c>
@@ -13100,7 +13275,9 @@
       <c r="AD81" s="2"/>
     </row>
     <row r="82" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="2"/>
+      <c r="A82" s="3">
+        <v>81</v>
+      </c>
       <c r="B82" s="2" t="s">
         <v>255</v>
       </c>
@@ -13144,7 +13321,9 @@
       <c r="AD82" s="2"/>
     </row>
     <row r="83" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="2"/>
+      <c r="A83" s="3">
+        <v>82</v>
+      </c>
       <c r="B83" s="2" t="s">
         <v>255</v>
       </c>
@@ -13188,7 +13367,9 @@
       <c r="AD83" s="2"/>
     </row>
     <row r="84" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="2"/>
+      <c r="A84" s="3">
+        <v>83</v>
+      </c>
       <c r="B84" s="2" t="s">
         <v>255</v>
       </c>
@@ -13254,7 +13435,9 @@
       <c r="AD84" s="2"/>
     </row>
     <row r="85" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="2"/>
+      <c r="A85" s="3">
+        <v>84</v>
+      </c>
       <c r="B85" s="2" t="s">
         <v>255</v>
       </c>
@@ -13314,7 +13497,9 @@
       <c r="AD85" s="2"/>
     </row>
     <row r="86" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="2"/>
+      <c r="A86" s="3">
+        <v>85</v>
+      </c>
       <c r="B86" s="2" t="s">
         <v>255</v>
       </c>
@@ -13378,7 +13563,9 @@
       <c r="AD86" s="2"/>
     </row>
     <row r="87" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="2"/>
+      <c r="A87" s="3">
+        <v>86</v>
+      </c>
       <c r="B87" s="2" t="s">
         <v>255</v>
       </c>
@@ -13442,7 +13629,9 @@
       <c r="AD87" s="2"/>
     </row>
     <row r="88" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="2"/>
+      <c r="A88" s="3">
+        <v>87</v>
+      </c>
       <c r="B88" s="2" t="s">
         <v>329</v>
       </c>
@@ -13514,7 +13703,9 @@
       <c r="AD88" s="2"/>
     </row>
     <row r="89" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="2"/>
+      <c r="A89" s="3">
+        <v>88</v>
+      </c>
       <c r="B89" s="2" t="s">
         <v>329</v>
       </c>
@@ -13586,7 +13777,9 @@
       <c r="AD89" s="2"/>
     </row>
     <row r="90" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="2"/>
+      <c r="A90" s="3">
+        <v>89</v>
+      </c>
       <c r="B90" s="2" t="s">
         <v>329</v>
       </c>
@@ -13658,7 +13851,9 @@
       <c r="AD90" s="2"/>
     </row>
     <row r="91" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="2"/>
+      <c r="A91" s="3">
+        <v>90</v>
+      </c>
       <c r="B91" s="2" t="s">
         <v>329</v>
       </c>
@@ -13730,7 +13925,9 @@
       <c r="AD91" s="2"/>
     </row>
     <row r="92" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="2"/>
+      <c r="A92" s="3">
+        <v>91</v>
+      </c>
       <c r="B92" s="2" t="s">
         <v>329</v>
       </c>
@@ -13774,7 +13971,9 @@
       <c r="AD92" s="2"/>
     </row>
     <row r="93" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="2"/>
+      <c r="A93" s="3">
+        <v>92</v>
+      </c>
       <c r="B93" s="2" t="s">
         <v>329</v>
       </c>
@@ -13844,7 +14043,9 @@
       <c r="AD93" s="2"/>
     </row>
     <row r="94" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="2"/>
+      <c r="A94" s="3">
+        <v>93</v>
+      </c>
       <c r="B94" s="2" t="s">
         <v>368</v>
       </c>
@@ -13916,7 +14117,9 @@
       <c r="AD94" s="2"/>
     </row>
     <row r="95" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="2"/>
+      <c r="A95" s="3">
+        <v>94</v>
+      </c>
       <c r="B95" s="2" t="s">
         <v>368</v>
       </c>
@@ -13988,7 +14191,9 @@
       <c r="AD95" s="2"/>
     </row>
     <row r="96" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="2"/>
+      <c r="A96" s="3">
+        <v>95</v>
+      </c>
       <c r="B96" s="2" t="s">
         <v>368</v>
       </c>
@@ -14060,7 +14265,9 @@
       <c r="AD96" s="2"/>
     </row>
     <row r="97" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="2"/>
+      <c r="A97" s="3">
+        <v>96</v>
+      </c>
       <c r="B97" s="2" t="s">
         <v>368</v>
       </c>
@@ -14132,7 +14339,9 @@
       <c r="AD97" s="2"/>
     </row>
     <row r="98" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="2"/>
+      <c r="A98" s="3">
+        <v>97</v>
+      </c>
       <c r="B98" s="2" t="s">
         <v>368</v>
       </c>
@@ -14204,7 +14413,9 @@
       <c r="AD98" s="2"/>
     </row>
     <row r="99" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="2"/>
+      <c r="A99" s="3">
+        <v>98</v>
+      </c>
       <c r="B99" s="2" t="s">
         <v>368</v>
       </c>
@@ -14264,7 +14475,9 @@
       <c r="AD99" s="2"/>
     </row>
     <row r="100" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="2"/>
+      <c r="A100" s="3">
+        <v>99</v>
+      </c>
       <c r="B100" s="2" t="s">
         <v>368</v>
       </c>
@@ -14336,7 +14549,9 @@
       <c r="AD100" s="2"/>
     </row>
     <row r="101" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="2"/>
+      <c r="A101" s="3">
+        <v>100</v>
+      </c>
       <c r="B101" s="2" t="s">
         <v>413</v>
       </c>
@@ -14408,7 +14623,9 @@
       <c r="AD101" s="2"/>
     </row>
     <row r="102" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="2"/>
+      <c r="A102" s="3">
+        <v>101</v>
+      </c>
       <c r="B102" s="2" t="s">
         <v>413</v>
       </c>
@@ -14480,7 +14697,9 @@
       <c r="AD102" s="2"/>
     </row>
     <row r="103" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="2"/>
+      <c r="A103" s="3">
+        <v>102</v>
+      </c>
       <c r="B103" s="2" t="s">
         <v>413</v>
       </c>
@@ -14552,7 +14771,9 @@
       <c r="AD103" s="2"/>
     </row>
     <row r="104" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="2"/>
+      <c r="A104" s="3">
+        <v>103</v>
+      </c>
       <c r="B104" s="2" t="s">
         <v>431</v>
       </c>
@@ -14624,7 +14845,9 @@
       <c r="AD104" s="2"/>
     </row>
     <row r="105" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="2"/>
+      <c r="A105" s="3">
+        <v>104</v>
+      </c>
       <c r="B105" s="2" t="s">
         <v>431</v>
       </c>
@@ -14696,7 +14919,9 @@
       <c r="AD105" s="2"/>
     </row>
     <row r="106" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="2"/>
+      <c r="A106" s="3">
+        <v>105</v>
+      </c>
       <c r="B106" s="2" t="s">
         <v>431</v>
       </c>
@@ -14768,7 +14993,9 @@
       <c r="AD106" s="2"/>
     </row>
     <row r="107" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="2"/>
+      <c r="A107" s="3">
+        <v>106</v>
+      </c>
       <c r="B107" s="2" t="s">
         <v>431</v>
       </c>
@@ -14828,7 +15055,9 @@
       <c r="AD107" s="2"/>
     </row>
     <row r="108" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="2"/>
+      <c r="A108" s="3">
+        <v>107</v>
+      </c>
       <c r="B108" s="2" t="s">
         <v>463</v>
       </c>
@@ -14900,7 +15129,9 @@
       <c r="AD108" s="2"/>
     </row>
     <row r="109" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="2"/>
+      <c r="A109" s="3">
+        <v>108</v>
+      </c>
       <c r="B109" s="2" t="s">
         <v>475</v>
       </c>
@@ -14966,7 +15197,9 @@
       <c r="AD109" s="2"/>
     </row>
     <row r="110" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="2"/>
+      <c r="A110" s="3">
+        <v>109</v>
+      </c>
       <c r="B110" s="2" t="s">
         <v>475</v>
       </c>
@@ -15038,7 +15271,9 @@
       <c r="AD110" s="2"/>
     </row>
     <row r="111" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="2"/>
+      <c r="A111" s="3">
+        <v>110</v>
+      </c>
       <c r="B111" s="2" t="s">
         <v>488</v>
       </c>
@@ -15110,7 +15345,9 @@
       <c r="AD111" s="2"/>
     </row>
     <row r="112" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="2"/>
+      <c r="A112" s="3">
+        <v>111</v>
+      </c>
       <c r="B112" s="2" t="s">
         <v>497</v>
       </c>
@@ -15154,7 +15391,9 @@
       <c r="AD112" s="2"/>
     </row>
     <row r="113" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="2"/>
+      <c r="A113" s="3">
+        <v>112</v>
+      </c>
       <c r="B113" s="2" t="s">
         <v>500</v>
       </c>
@@ -15226,7 +15465,9 @@
       <c r="AD113" s="2"/>
     </row>
     <row r="114" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="2"/>
+      <c r="A114" s="3">
+        <v>113</v>
+      </c>
       <c r="B114" s="2" t="s">
         <v>500</v>
       </c>
@@ -15286,7 +15527,9 @@
       <c r="AD114" s="2"/>
     </row>
     <row r="115" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="2"/>
+      <c r="A115" s="3">
+        <v>114</v>
+      </c>
       <c r="B115" s="2" t="s">
         <v>500</v>
       </c>
@@ -15330,7 +15573,9 @@
       <c r="AD115" s="2"/>
     </row>
     <row r="116" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="2"/>
+      <c r="A116" s="3">
+        <v>115</v>
+      </c>
       <c r="B116" s="2" t="s">
         <v>500</v>
       </c>
@@ -15402,7 +15647,9 @@
       <c r="AD116" s="2"/>
     </row>
     <row r="117" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="2"/>
+      <c r="A117" s="3">
+        <v>116</v>
+      </c>
       <c r="B117" s="2" t="s">
         <v>500</v>
       </c>
@@ -15474,7 +15721,9 @@
       <c r="AD117" s="2"/>
     </row>
     <row r="118" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="2"/>
+      <c r="A118" s="3">
+        <v>117</v>
+      </c>
       <c r="B118" s="2" t="s">
         <v>500</v>
       </c>
@@ -15548,7 +15797,9 @@
       <c r="AD118" s="2"/>
     </row>
     <row r="119" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="2"/>
+      <c r="A119" s="3">
+        <v>118</v>
+      </c>
       <c r="B119" s="2" t="s">
         <v>546</v>
       </c>
@@ -15620,7 +15871,9 @@
       <c r="AD119" s="2"/>
     </row>
     <row r="120" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="2"/>
+      <c r="A120" s="3">
+        <v>119</v>
+      </c>
       <c r="B120" s="2" t="s">
         <v>546</v>
       </c>
@@ -15664,7 +15917,9 @@
       <c r="AD120" s="2"/>
     </row>
     <row r="121" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="2"/>
+      <c r="A121" s="3">
+        <v>120</v>
+      </c>
       <c r="B121" s="2" t="s">
         <v>546</v>
       </c>
@@ -15736,7 +15991,9 @@
       <c r="AD121" s="2"/>
     </row>
     <row r="122" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="2"/>
+      <c r="A122" s="3">
+        <v>121</v>
+      </c>
       <c r="B122" s="2" t="s">
         <v>546</v>
       </c>
@@ -15810,7 +16067,9 @@
       <c r="AD122" s="2"/>
     </row>
     <row r="123" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="2"/>
+      <c r="A123" s="3">
+        <v>122</v>
+      </c>
       <c r="B123" s="2" t="s">
         <v>546</v>
       </c>
@@ -15882,7 +16141,9 @@
       <c r="AD123" s="2"/>
     </row>
     <row r="124" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="2"/>
+      <c r="A124" s="3">
+        <v>123</v>
+      </c>
       <c r="B124" s="2" t="s">
         <v>546</v>
       </c>
@@ -15926,7 +16187,9 @@
       <c r="AD124" s="2"/>
     </row>
     <row r="125" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="2"/>
+      <c r="A125" s="3">
+        <v>124</v>
+      </c>
       <c r="B125" s="2" t="s">
         <v>579</v>
       </c>
@@ -15996,7 +16259,9 @@
       <c r="AD125" s="2"/>
     </row>
     <row r="126" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="2"/>
+      <c r="A126" s="3">
+        <v>125</v>
+      </c>
       <c r="B126" s="2" t="s">
         <v>579</v>
       </c>
@@ -16066,7 +16331,9 @@
       <c r="AD126" s="2"/>
     </row>
     <row r="127" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="2"/>
+      <c r="A127" s="3">
+        <v>126</v>
+      </c>
       <c r="B127" s="2" t="s">
         <v>579</v>
       </c>
@@ -16140,7 +16407,9 @@
       <c r="AD127" s="2"/>
     </row>
     <row r="128" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="2"/>
+      <c r="A128" s="3">
+        <v>127</v>
+      </c>
       <c r="B128" s="2" t="s">
         <v>579</v>
       </c>
@@ -16214,7 +16483,9 @@
       <c r="AD128" s="2"/>
     </row>
     <row r="129" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="2"/>
+      <c r="A129" s="3">
+        <v>128</v>
+      </c>
       <c r="B129" s="2" t="s">
         <v>579</v>
       </c>
@@ -16284,7 +16555,9 @@
       <c r="AD129" s="2"/>
     </row>
     <row r="130" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="2"/>
+      <c r="A130" s="3">
+        <v>129</v>
+      </c>
       <c r="B130" s="2" t="s">
         <v>579</v>
       </c>
@@ -16354,7 +16627,9 @@
       <c r="AD130" s="2"/>
     </row>
     <row r="131" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="2"/>
+      <c r="A131" s="3">
+        <v>130</v>
+      </c>
       <c r="B131" s="2" t="s">
         <v>579</v>
       </c>
@@ -16398,7 +16673,9 @@
       <c r="AD131" s="2"/>
     </row>
     <row r="132" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="2"/>
+      <c r="A132" s="3">
+        <v>131</v>
+      </c>
       <c r="B132" s="2" t="s">
         <v>579</v>
       </c>
@@ -16468,7 +16745,9 @@
       <c r="AD132" s="2"/>
     </row>
     <row r="133" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="2"/>
+      <c r="A133" s="3">
+        <v>132</v>
+      </c>
       <c r="B133" s="2" t="s">
         <v>579</v>
       </c>
@@ -16538,7 +16817,9 @@
       <c r="AD133" s="2"/>
     </row>
     <row r="134" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="2"/>
+      <c r="A134" s="3">
+        <v>133</v>
+      </c>
       <c r="B134" s="2" t="s">
         <v>579</v>
       </c>
@@ -16608,7 +16889,9 @@
       <c r="AD134" s="2"/>
     </row>
     <row r="135" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="2"/>
+      <c r="A135" s="3">
+        <v>134</v>
+      </c>
       <c r="B135" s="2" t="s">
         <v>579</v>
       </c>
@@ -16680,7 +16963,9 @@
       <c r="AD135" s="2"/>
     </row>
     <row r="136" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="2"/>
+      <c r="A136" s="3">
+        <v>135</v>
+      </c>
       <c r="B136" s="2" t="s">
         <v>579</v>
       </c>
@@ -16750,7 +17035,9 @@
       <c r="AD136" s="2"/>
     </row>
     <row r="137" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="2"/>
+      <c r="A137" s="3">
+        <v>136</v>
+      </c>
       <c r="B137" s="2" t="s">
         <v>579</v>
       </c>
@@ -16820,7 +17107,9 @@
       <c r="AD137" s="2"/>
     </row>
     <row r="138" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="2"/>
+      <c r="A138" s="3">
+        <v>137</v>
+      </c>
       <c r="B138" s="2" t="s">
         <v>579</v>
       </c>
@@ -16884,7 +17173,9 @@
       <c r="AD138" s="2"/>
     </row>
     <row r="139" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="2"/>
+      <c r="A139" s="3">
+        <v>138</v>
+      </c>
       <c r="B139" s="2" t="s">
         <v>579</v>
       </c>
@@ -16944,7 +17235,9 @@
       <c r="AD139" s="2"/>
     </row>
     <row r="140" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="2"/>
+      <c r="A140" s="3">
+        <v>139</v>
+      </c>
       <c r="B140" s="2" t="s">
         <v>669</v>
       </c>
@@ -17016,7 +17309,9 @@
       <c r="AD140" s="2"/>
     </row>
     <row r="141" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="2"/>
+      <c r="A141" s="3">
+        <v>140</v>
+      </c>
       <c r="B141" s="2" t="s">
         <v>669</v>
       </c>
@@ -17092,7 +17387,9 @@
       <c r="AD141" s="2"/>
     </row>
     <row r="142" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="2"/>
+      <c r="A142" s="3">
+        <v>141</v>
+      </c>
       <c r="B142" s="2" t="s">
         <v>669</v>
       </c>
@@ -17164,7 +17461,9 @@
       <c r="AD142" s="2"/>
     </row>
     <row r="143" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="2"/>
+      <c r="A143" s="3">
+        <v>142</v>
+      </c>
       <c r="B143" s="2" t="s">
         <v>669</v>
       </c>
@@ -17236,7 +17535,9 @@
       <c r="AD143" s="2"/>
     </row>
     <row r="144" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="2"/>
+      <c r="A144" s="3">
+        <v>143</v>
+      </c>
       <c r="B144" s="2" t="s">
         <v>703</v>
       </c>
@@ -17308,7 +17609,9 @@
       <c r="AD144" s="2"/>
     </row>
     <row r="145" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="2"/>
+      <c r="A145" s="3">
+        <v>144</v>
+      </c>
       <c r="B145" s="2" t="s">
         <v>703</v>
       </c>
@@ -17380,7 +17683,9 @@
       <c r="AD145" s="2"/>
     </row>
     <row r="146" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="2"/>
+      <c r="A146" s="3">
+        <v>145</v>
+      </c>
       <c r="B146" s="2" t="s">
         <v>703</v>
       </c>
@@ -17452,7 +17757,9 @@
       <c r="AD146" s="2"/>
     </row>
     <row r="147" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="2"/>
+      <c r="A147" s="3">
+        <v>146</v>
+      </c>
       <c r="B147" s="2" t="s">
         <v>703</v>
       </c>
@@ -17524,7 +17831,9 @@
       <c r="AD147" s="2"/>
     </row>
     <row r="148" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="2"/>
+      <c r="A148" s="3">
+        <v>147</v>
+      </c>
       <c r="B148" s="2" t="s">
         <v>727</v>
       </c>
@@ -17596,7 +17905,9 @@
       <c r="AD148" s="2"/>
     </row>
     <row r="149" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="2"/>
+      <c r="A149" s="3">
+        <v>148</v>
+      </c>
       <c r="B149" s="2" t="s">
         <v>727</v>
       </c>
@@ -17640,7 +17951,9 @@
       <c r="AD149" s="2"/>
     </row>
     <row r="150" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="2"/>
+      <c r="A150" s="3">
+        <v>149</v>
+      </c>
       <c r="B150" s="2" t="s">
         <v>727</v>
       </c>
@@ -17712,7 +18025,9 @@
       <c r="AD150" s="2"/>
     </row>
     <row r="151" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="2"/>
+      <c r="A151" s="3">
+        <v>150</v>
+      </c>
       <c r="B151" s="2" t="s">
         <v>727</v>
       </c>
@@ -17776,7 +18091,9 @@
       <c r="AD151" s="2"/>
     </row>
     <row r="152" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="2"/>
+      <c r="A152" s="3">
+        <v>151</v>
+      </c>
       <c r="B152" s="2" t="s">
         <v>750</v>
       </c>
@@ -17848,7 +18165,9 @@
       <c r="AD152" s="2"/>
     </row>
     <row r="153" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="2"/>
+      <c r="A153" s="3">
+        <v>152</v>
+      </c>
       <c r="B153" s="2" t="s">
         <v>750</v>
       </c>
@@ -17892,7 +18211,9 @@
       <c r="AD153" s="2"/>
     </row>
     <row r="154" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="2"/>
+      <c r="A154" s="3">
+        <v>153</v>
+      </c>
       <c r="B154" s="2" t="s">
         <v>750</v>
       </c>
@@ -17936,7 +18257,9 @@
       <c r="AD154" s="2"/>
     </row>
     <row r="155" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="2"/>
+      <c r="A155" s="3">
+        <v>154</v>
+      </c>
       <c r="B155" s="2" t="s">
         <v>750</v>
       </c>
@@ -17980,7 +18303,9 @@
       <c r="AD155" s="2"/>
     </row>
     <row r="156" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="2"/>
+      <c r="A156" s="3">
+        <v>155</v>
+      </c>
       <c r="B156" s="2" t="s">
         <v>750</v>
       </c>
@@ -18024,7 +18349,9 @@
       <c r="AD156" s="2"/>
     </row>
     <row r="157" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="2"/>
+      <c r="A157" s="3">
+        <v>156</v>
+      </c>
       <c r="B157" s="2" t="s">
         <v>750</v>
       </c>
@@ -18090,7 +18417,9 @@
       <c r="AD157" s="2"/>
     </row>
     <row r="158" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="2"/>
+      <c r="A158" s="3">
+        <v>157</v>
+      </c>
       <c r="B158" s="2" t="s">
         <v>750</v>
       </c>
@@ -18156,7 +18485,9 @@
       <c r="AD158" s="2"/>
     </row>
     <row r="159" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="2"/>
+      <c r="A159" s="3">
+        <v>158</v>
+      </c>
       <c r="B159" s="2" t="s">
         <v>750</v>
       </c>
@@ -18222,7 +18553,9 @@
       <c r="AD159" s="2"/>
     </row>
     <row r="160" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="2"/>
+      <c r="A160" s="3">
+        <v>159</v>
+      </c>
       <c r="B160" s="2" t="s">
         <v>778</v>
       </c>
@@ -18294,7 +18627,9 @@
       <c r="AD160" s="2"/>
     </row>
     <row r="161" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="2"/>
+      <c r="A161" s="3">
+        <v>160</v>
+      </c>
       <c r="B161" s="2" t="s">
         <v>778</v>
       </c>
@@ -18366,7 +18701,9 @@
       <c r="AD161" s="2"/>
     </row>
     <row r="162" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="2"/>
+      <c r="A162" s="3">
+        <v>161</v>
+      </c>
       <c r="B162" s="2" t="s">
         <v>778</v>
       </c>
@@ -18438,7 +18775,9 @@
       <c r="AD162" s="2"/>
     </row>
     <row r="163" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="2"/>
+      <c r="A163" s="3">
+        <v>162</v>
+      </c>
       <c r="B163" s="2" t="s">
         <v>778</v>
       </c>
@@ -18510,7 +18849,9 @@
       <c r="AD163" s="2"/>
     </row>
     <row r="164" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="2"/>
+      <c r="A164" s="3">
+        <v>163</v>
+      </c>
       <c r="B164" s="2" t="s">
         <v>778</v>
       </c>
@@ -18582,7 +18923,9 @@
       <c r="AD164" s="2"/>
     </row>
     <row r="165" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="2"/>
+      <c r="A165" s="3">
+        <v>164</v>
+      </c>
       <c r="B165" s="2" t="s">
         <v>778</v>
       </c>
@@ -18654,7 +18997,9 @@
       <c r="AD165" s="2"/>
     </row>
     <row r="166" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="2"/>
+      <c r="A166" s="3">
+        <v>165</v>
+      </c>
       <c r="B166" s="2" t="s">
         <v>778</v>
       </c>
@@ -18726,7 +19071,9 @@
       <c r="AD166" s="2"/>
     </row>
     <row r="167" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="2"/>
+      <c r="A167" s="3">
+        <v>166</v>
+      </c>
       <c r="B167" s="2" t="s">
         <v>778</v>
       </c>
@@ -18798,7 +19145,9 @@
       <c r="AD167" s="2"/>
     </row>
     <row r="168" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="2"/>
+      <c r="A168" s="3">
+        <v>167</v>
+      </c>
       <c r="B168" s="2" t="s">
         <v>778</v>
       </c>
@@ -18870,7 +19219,9 @@
       <c r="AD168" s="2"/>
     </row>
     <row r="169" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="2"/>
+      <c r="A169" s="3">
+        <v>168</v>
+      </c>
       <c r="B169" s="2" t="s">
         <v>778</v>
       </c>
@@ -18914,7 +19265,9 @@
       <c r="AD169" s="2"/>
     </row>
     <row r="170" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="2"/>
+      <c r="A170" s="3">
+        <v>169</v>
+      </c>
       <c r="B170" s="2" t="s">
         <v>778</v>
       </c>
@@ -18974,7 +19327,9 @@
       <c r="AD170" s="2"/>
     </row>
     <row r="171" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="2"/>
+      <c r="A171" s="3">
+        <v>170</v>
+      </c>
       <c r="B171" s="2" t="s">
         <v>778</v>
       </c>
@@ -19018,7 +19373,9 @@
       <c r="AD171" s="2"/>
     </row>
     <row r="172" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="2"/>
+      <c r="A172" s="3">
+        <v>171</v>
+      </c>
       <c r="B172" s="2" t="s">
         <v>852</v>
       </c>
@@ -19090,7 +19447,9 @@
       <c r="AD172" s="2"/>
     </row>
     <row r="173" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="2"/>
+      <c r="A173" s="3">
+        <v>172</v>
+      </c>
       <c r="B173" s="2" t="s">
         <v>852</v>
       </c>
@@ -19162,7 +19521,9 @@
       <c r="AD173" s="2"/>
     </row>
     <row r="174" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="2"/>
+      <c r="A174" s="3">
+        <v>173</v>
+      </c>
       <c r="B174" s="2" t="s">
         <v>852</v>
       </c>
@@ -19234,7 +19595,9 @@
       <c r="AD174" s="2"/>
     </row>
     <row r="175" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="2"/>
+      <c r="A175" s="3">
+        <v>174</v>
+      </c>
       <c r="B175" s="2" t="s">
         <v>852</v>
       </c>
@@ -19278,7 +19641,9 @@
       <c r="AD175" s="2"/>
     </row>
     <row r="176" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="2"/>
+      <c r="A176" s="3">
+        <v>175</v>
+      </c>
       <c r="B176" s="2" t="s">
         <v>852</v>
       </c>
@@ -19350,7 +19715,9 @@
       <c r="AD176" s="2"/>
     </row>
     <row r="177" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="2"/>
+      <c r="A177" s="3">
+        <v>176</v>
+      </c>
       <c r="B177" s="2" t="s">
         <v>852</v>
       </c>
@@ -19422,7 +19789,9 @@
       <c r="AD177" s="2"/>
     </row>
     <row r="178" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="2"/>
+      <c r="A178" s="3">
+        <v>177</v>
+      </c>
       <c r="B178" s="2" t="s">
         <v>852</v>
       </c>
@@ -19494,7 +19863,9 @@
       <c r="AD178" s="2"/>
     </row>
     <row r="179" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="2"/>
+      <c r="A179" s="3">
+        <v>178</v>
+      </c>
       <c r="B179" s="2" t="s">
         <v>852</v>
       </c>
@@ -19566,7 +19937,9 @@
       <c r="AD179" s="2"/>
     </row>
     <row r="180" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="2"/>
+      <c r="A180" s="3">
+        <v>179</v>
+      </c>
       <c r="B180" s="2" t="s">
         <v>852</v>
       </c>
@@ -19638,7 +20011,9 @@
       <c r="AD180" s="2"/>
     </row>
     <row r="181" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="2"/>
+      <c r="A181" s="3">
+        <v>180</v>
+      </c>
       <c r="B181" s="2" t="s">
         <v>912</v>
       </c>
@@ -19682,7 +20057,9 @@
       <c r="AD181" s="2"/>
     </row>
     <row r="182" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="2"/>
+      <c r="A182" s="3">
+        <v>181</v>
+      </c>
       <c r="B182" s="2" t="s">
         <v>912</v>
       </c>
@@ -19726,7 +20103,9 @@
       <c r="AD182" s="2"/>
     </row>
     <row r="183" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="2"/>
+      <c r="A183" s="3">
+        <v>182</v>
+      </c>
       <c r="B183" s="2" t="s">
         <v>912</v>
       </c>
@@ -19770,7 +20149,9 @@
       <c r="AD183" s="2"/>
     </row>
     <row r="184" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="2"/>
+      <c r="A184" s="3">
+        <v>183</v>
+      </c>
       <c r="B184" s="2" t="s">
         <v>912</v>
       </c>
@@ -19814,7 +20195,9 @@
       <c r="AD184" s="2"/>
     </row>
     <row r="185" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="2"/>
+      <c r="A185" s="3">
+        <v>184</v>
+      </c>
       <c r="B185" s="2" t="s">
         <v>912</v>
       </c>
@@ -19858,7 +20241,9 @@
       <c r="AD185" s="2"/>
     </row>
     <row r="186" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="2"/>
+      <c r="A186" s="3">
+        <v>185</v>
+      </c>
       <c r="B186" s="2" t="s">
         <v>912</v>
       </c>
@@ -19902,7 +20287,9 @@
       <c r="AD186" s="2"/>
     </row>
     <row r="187" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="2"/>
+      <c r="A187" s="3">
+        <v>186</v>
+      </c>
       <c r="B187" s="2" t="s">
         <v>912</v>
       </c>
@@ -19946,7 +20333,9 @@
       <c r="AD187" s="2"/>
     </row>
     <row r="188" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="2"/>
+      <c r="A188" s="3">
+        <v>187</v>
+      </c>
       <c r="B188" s="2" t="s">
         <v>919</v>
       </c>
@@ -19990,7 +20379,9 @@
       <c r="AD188" s="2"/>
     </row>
     <row r="189" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="2"/>
+      <c r="A189" s="3">
+        <v>188</v>
+      </c>
       <c r="B189" s="2" t="s">
         <v>919</v>
       </c>
@@ -20034,7 +20425,9 @@
       <c r="AD189" s="2"/>
     </row>
     <row r="190" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="2"/>
+      <c r="A190" s="3">
+        <v>189</v>
+      </c>
       <c r="B190" s="2" t="s">
         <v>919</v>
       </c>
@@ -20106,7 +20499,9 @@
       <c r="AD190" s="2"/>
     </row>
     <row r="191" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="2"/>
+      <c r="A191" s="3">
+        <v>190</v>
+      </c>
       <c r="B191" s="2" t="s">
         <v>919</v>
       </c>
@@ -20150,7 +20545,9 @@
       <c r="AD191" s="2"/>
     </row>
     <row r="192" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="2"/>
+      <c r="A192" s="3">
+        <v>191</v>
+      </c>
       <c r="B192" s="2" t="s">
         <v>929</v>
       </c>
@@ -20222,7 +20619,9 @@
       <c r="AD192" s="2"/>
     </row>
     <row r="193" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="2"/>
+      <c r="A193" s="3">
+        <v>192</v>
+      </c>
       <c r="B193" s="2" t="s">
         <v>929</v>
       </c>
@@ -20296,7 +20695,9 @@
       <c r="AD193" s="2"/>
     </row>
     <row r="194" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="2"/>
+      <c r="A194" s="3">
+        <v>193</v>
+      </c>
       <c r="B194" s="2" t="s">
         <v>929</v>
       </c>
@@ -20370,7 +20771,9 @@
       <c r="AD194" s="2"/>
     </row>
     <row r="195" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="2"/>
+      <c r="A195" s="3">
+        <v>194</v>
+      </c>
       <c r="B195" s="2" t="s">
         <v>929</v>
       </c>
@@ -20442,7 +20845,9 @@
       <c r="AD195" s="2"/>
     </row>
     <row r="196" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="2"/>
+      <c r="A196" s="3">
+        <v>195</v>
+      </c>
       <c r="B196" s="2" t="s">
         <v>929</v>
       </c>
@@ -20486,7 +20891,9 @@
       <c r="AD196" s="2"/>
     </row>
     <row r="197" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="2"/>
+      <c r="A197" s="3">
+        <v>196</v>
+      </c>
       <c r="B197" s="2" t="s">
         <v>958</v>
       </c>
@@ -20558,7 +20965,9 @@
       <c r="AD197" s="2"/>
     </row>
     <row r="198" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="2"/>
+      <c r="A198" s="3">
+        <v>197</v>
+      </c>
       <c r="B198" s="2" t="s">
         <v>958</v>
       </c>
@@ -20630,7 +21039,9 @@
       <c r="AD198" s="2"/>
     </row>
     <row r="199" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="2"/>
+      <c r="A199" s="3">
+        <v>198</v>
+      </c>
       <c r="B199" s="2" t="s">
         <v>958</v>
       </c>
@@ -20674,7 +21085,9 @@
       <c r="AD199" s="2"/>
     </row>
     <row r="200" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="2"/>
+      <c r="A200" s="3">
+        <v>199</v>
+      </c>
       <c r="B200" s="2" t="s">
         <v>978</v>
       </c>
@@ -20718,7 +21131,9 @@
       <c r="AD200" s="2"/>
     </row>
     <row r="201" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="2"/>
+      <c r="A201" s="3">
+        <v>200</v>
+      </c>
       <c r="B201" s="2" t="s">
         <v>978</v>
       </c>
@@ -20762,7 +21177,9 @@
       <c r="AD201" s="2"/>
     </row>
     <row r="202" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="2"/>
+      <c r="A202" s="3">
+        <v>201</v>
+      </c>
       <c r="B202" s="2" t="s">
         <v>978</v>
       </c>
@@ -20806,7 +21223,9 @@
       <c r="AD202" s="2"/>
     </row>
     <row r="203" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="2"/>
+      <c r="A203" s="3">
+        <v>202</v>
+      </c>
       <c r="B203" s="2" t="s">
         <v>978</v>
       </c>
@@ -20850,7 +21269,9 @@
       <c r="AD203" s="2"/>
     </row>
     <row r="204" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="2"/>
+      <c r="A204" s="3">
+        <v>203</v>
+      </c>
       <c r="B204" s="2" t="s">
         <v>978</v>
       </c>
@@ -20894,7 +21315,9 @@
       <c r="AD204" s="2"/>
     </row>
     <row r="205" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="2"/>
+      <c r="A205" s="3">
+        <v>204</v>
+      </c>
       <c r="B205" s="2" t="s">
         <v>978</v>
       </c>
@@ -20962,7 +21385,9 @@
       <c r="AD205" s="2"/>
     </row>
     <row r="206" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="2"/>
+      <c r="A206" s="3">
+        <v>205</v>
+      </c>
       <c r="B206" s="2" t="s">
         <v>990</v>
       </c>
@@ -21034,7 +21459,9 @@
       <c r="AD206" s="2"/>
     </row>
     <row r="207" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="2"/>
+      <c r="A207" s="3">
+        <v>206</v>
+      </c>
       <c r="B207" s="2" t="s">
         <v>990</v>
       </c>
@@ -21078,7 +21505,9 @@
       <c r="AD207" s="2"/>
     </row>
     <row r="208" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="2"/>
+      <c r="A208" s="3">
+        <v>207</v>
+      </c>
       <c r="B208" s="2" t="s">
         <v>990</v>
       </c>
@@ -21122,7 +21551,9 @@
       <c r="AD208" s="2"/>
     </row>
     <row r="209" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="2"/>
+      <c r="A209" s="3">
+        <v>208</v>
+      </c>
       <c r="B209" s="2" t="s">
         <v>990</v>
       </c>
@@ -21166,7 +21597,9 @@
       <c r="AD209" s="2"/>
     </row>
     <row r="210" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="2"/>
+      <c r="A210" s="3">
+        <v>209</v>
+      </c>
       <c r="B210" s="2" t="s">
         <v>990</v>
       </c>
@@ -21210,7 +21643,9 @@
       <c r="AD210" s="2"/>
     </row>
     <row r="211" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="2"/>
+      <c r="A211" s="3">
+        <v>210</v>
+      </c>
       <c r="B211" s="2" t="s">
         <v>990</v>
       </c>
@@ -21282,7 +21717,9 @@
       <c r="AD211" s="2"/>
     </row>
     <row r="212" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="2"/>
+      <c r="A212" s="3">
+        <v>211</v>
+      </c>
       <c r="B212" s="2" t="s">
         <v>990</v>
       </c>
@@ -21326,7 +21763,9 @@
       <c r="AD212" s="2"/>
     </row>
     <row r="213" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A213" s="2"/>
+      <c r="A213" s="3">
+        <v>212</v>
+      </c>
       <c r="B213" s="2" t="s">
         <v>1007</v>
       </c>
@@ -21392,7 +21831,9 @@
       <c r="AD213" s="2"/>
     </row>
     <row r="214" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A214" s="2"/>
+      <c r="A214" s="3">
+        <v>213</v>
+      </c>
       <c r="B214" s="2" t="s">
         <v>1007</v>
       </c>
@@ -21464,7 +21905,9 @@
       <c r="AD214" s="2"/>
     </row>
     <row r="215" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A215" s="2"/>
+      <c r="A215" s="3">
+        <v>214</v>
+      </c>
       <c r="B215" s="2" t="s">
         <v>1007</v>
       </c>
@@ -21532,7 +21975,9 @@
       <c r="AD215" s="2"/>
     </row>
     <row r="216" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A216" s="2"/>
+      <c r="A216" s="3">
+        <v>215</v>
+      </c>
       <c r="B216" s="2" t="s">
         <v>1007</v>
       </c>
@@ -21604,7 +22049,9 @@
       <c r="AD216" s="2"/>
     </row>
     <row r="217" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A217" s="2"/>
+      <c r="A217" s="3">
+        <v>216</v>
+      </c>
       <c r="B217" s="2" t="s">
         <v>1036</v>
       </c>
@@ -21676,7 +22123,9 @@
       <c r="AD217" s="2"/>
     </row>
     <row r="218" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A218" s="2"/>
+      <c r="A218" s="3">
+        <v>217</v>
+      </c>
       <c r="B218" s="2" t="s">
         <v>1036</v>
       </c>
@@ -21720,7 +22169,9 @@
       <c r="AD218" s="2"/>
     </row>
     <row r="219" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A219" s="2"/>
+      <c r="A219" s="3">
+        <v>218</v>
+      </c>
       <c r="B219" s="2" t="s">
         <v>1047</v>
       </c>
@@ -21764,7 +22215,9 @@
       <c r="AD219" s="2"/>
     </row>
     <row r="220" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A220" s="2"/>
+      <c r="A220" s="3">
+        <v>219</v>
+      </c>
       <c r="B220" s="2" t="s">
         <v>1047</v>
       </c>
@@ -21808,7 +22261,9 @@
       <c r="AD220" s="2"/>
     </row>
     <row r="221" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A221" s="2"/>
+      <c r="A221" s="3">
+        <v>220</v>
+      </c>
       <c r="B221" s="2" t="s">
         <v>1050</v>
       </c>
@@ -21878,7 +22333,9 @@
       <c r="AD221" s="2"/>
     </row>
     <row r="222" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A222" s="2"/>
+      <c r="A222" s="3">
+        <v>221</v>
+      </c>
       <c r="B222" s="2" t="s">
         <v>1050</v>
       </c>
@@ -21942,7 +22399,9 @@
       <c r="AD222" s="2"/>
     </row>
     <row r="223" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A223" s="2"/>
+      <c r="A223" s="3">
+        <v>222</v>
+      </c>
       <c r="B223" s="2" t="s">
         <v>1067</v>
       </c>
@@ -21986,7 +22445,9 @@
       <c r="AD223" s="2"/>
     </row>
     <row r="224" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A224" s="2"/>
+      <c r="A224" s="3">
+        <v>223</v>
+      </c>
       <c r="B224" s="2" t="s">
         <v>1068</v>
       </c>
@@ -22058,7 +22519,9 @@
       <c r="AD224" s="2"/>
     </row>
     <row r="225" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A225" s="2"/>
+      <c r="A225" s="3">
+        <v>224</v>
+      </c>
       <c r="B225" s="2" t="s">
         <v>1077</v>
       </c>
@@ -22102,7 +22565,9 @@
       <c r="AD225" s="2"/>
     </row>
     <row r="226" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A226" s="2"/>
+      <c r="A226" s="3">
+        <v>225</v>
+      </c>
       <c r="B226" s="2" t="s">
         <v>1078</v>
       </c>
@@ -22145,8 +22610,10 @@
       <c r="AC226" s="2"/>
       <c r="AD226" s="2"/>
     </row>
-    <row r="227" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A227" s="2"/>
+    <row r="227" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" s="3">
+        <v>226</v>
+      </c>
       <c r="B227" s="2" t="s">
         <v>1079</v>
       </c>
@@ -22218,7 +22685,9 @@
       <c r="AD227" s="2"/>
     </row>
     <row r="228" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A228" s="2"/>
+      <c r="A228" s="3">
+        <v>227</v>
+      </c>
       <c r="B228" s="2" t="s">
         <v>1089</v>
       </c>
@@ -22262,7 +22731,9 @@
       <c r="AD228" s="2"/>
     </row>
     <row r="229" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A229" s="2"/>
+      <c r="A229" s="3">
+        <v>228</v>
+      </c>
       <c r="B229" s="2" t="s">
         <v>1091</v>
       </c>
@@ -22320,7 +22791,9 @@
       <c r="AD229" s="2"/>
     </row>
     <row r="230" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A230" s="2"/>
+      <c r="A230" s="3">
+        <v>229</v>
+      </c>
       <c r="B230" s="2" t="s">
         <v>1098</v>
       </c>
@@ -22378,7 +22851,9 @@
       <c r="AD230" s="2"/>
     </row>
     <row r="231" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A231" s="2"/>
+      <c r="A231" s="3">
+        <v>230</v>
+      </c>
       <c r="B231" s="2" t="s">
         <v>1104</v>
       </c>
@@ -22422,7 +22897,9 @@
       <c r="AD231" s="2"/>
     </row>
     <row r="232" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A232" s="2"/>
+      <c r="A232" s="3">
+        <v>231</v>
+      </c>
       <c r="B232" s="2" t="s">
         <v>1106</v>
       </c>
@@ -22466,7 +22943,9 @@
       <c r="AD232" s="2"/>
     </row>
     <row r="233" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A233" s="2"/>
+      <c r="A233" s="3">
+        <v>232</v>
+      </c>
       <c r="B233" s="2" t="s">
         <v>1108</v>
       </c>
@@ -22510,7 +22989,9 @@
       <c r="AD233" s="2"/>
     </row>
     <row r="234" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A234" s="2"/>
+      <c r="A234" s="3">
+        <v>233</v>
+      </c>
       <c r="B234" s="2" t="s">
         <v>1109</v>
       </c>
@@ -22582,7 +23063,9 @@
       <c r="AD234" s="2"/>
     </row>
     <row r="235" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A235" s="2"/>
+      <c r="A235" s="3">
+        <v>234</v>
+      </c>
       <c r="B235" s="2" t="s">
         <v>1119</v>
       </c>
@@ -22654,7 +23137,9 @@
       <c r="AD235" s="2"/>
     </row>
     <row r="236" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A236" s="2"/>
+      <c r="A236" s="3">
+        <v>235</v>
+      </c>
       <c r="B236" s="2" t="s">
         <v>1129</v>
       </c>
@@ -22698,7 +23183,9 @@
       <c r="AD236" s="2"/>
     </row>
     <row r="237" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A237" s="2"/>
+      <c r="A237" s="3">
+        <v>236</v>
+      </c>
       <c r="B237" s="2" t="s">
         <v>1131</v>
       </c>
@@ -22760,7 +23247,9 @@
       <c r="AD237" s="2"/>
     </row>
     <row r="238" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A238" s="2"/>
+      <c r="A238" s="3">
+        <v>237</v>
+      </c>
       <c r="B238" s="2" t="s">
         <v>1131</v>
       </c>
@@ -22804,7 +23293,9 @@
       <c r="AD238" s="2"/>
     </row>
     <row r="239" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A239" s="2"/>
+      <c r="A239" s="3">
+        <v>238</v>
+      </c>
       <c r="B239" s="2" t="s">
         <v>1140</v>
       </c>
@@ -22848,7 +23339,9 @@
       <c r="AD239" s="2"/>
     </row>
     <row r="240" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A240" s="2"/>
+      <c r="A240" s="3">
+        <v>239</v>
+      </c>
       <c r="B240" s="2" t="s">
         <v>1141</v>
       </c>
@@ -22892,7 +23385,9 @@
       <c r="AD240" s="2"/>
     </row>
     <row r="241" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A241" s="2"/>
+      <c r="A241" s="3">
+        <v>240</v>
+      </c>
       <c r="B241" s="2" t="s">
         <v>1131</v>
       </c>
@@ -22960,7 +23455,9 @@
       <c r="AD241" s="2"/>
     </row>
     <row r="242" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="2"/>
+      <c r="A242" s="3">
+        <v>241</v>
+      </c>
       <c r="B242" s="2" t="s">
         <v>1150</v>
       </c>
@@ -23034,7 +23531,9 @@
       <c r="AD242" s="2"/>
     </row>
     <row r="243" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A243" s="2"/>
+      <c r="A243" s="3">
+        <v>242</v>
+      </c>
       <c r="B243" s="2" t="s">
         <v>1157</v>
       </c>
@@ -23106,7 +23605,9 @@
       <c r="AD243" s="2"/>
     </row>
     <row r="244" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A244" s="2"/>
+      <c r="A244" s="3">
+        <v>243</v>
+      </c>
       <c r="B244" s="2" t="s">
         <v>1164</v>
       </c>
@@ -23163,8 +23664,10 @@
       <c r="AC244" s="2"/>
       <c r="AD244" s="2"/>
     </row>
-    <row r="245" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A245" s="2"/>
+    <row r="245" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A245" s="3">
+        <v>244</v>
+      </c>
       <c r="B245" s="2" t="s">
         <v>1172</v>
       </c>
@@ -23222,7 +23725,9 @@
       <c r="AD245" s="2"/>
     </row>
     <row r="246" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A246" s="2"/>
+      <c r="A246" s="3">
+        <v>245</v>
+      </c>
       <c r="B246" s="2" t="s">
         <v>1179</v>
       </c>
@@ -23266,7 +23771,9 @@
       <c r="AD246" s="2"/>
     </row>
     <row r="247" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A247" s="2"/>
+      <c r="A247" s="3">
+        <v>246</v>
+      </c>
       <c r="B247" s="2" t="s">
         <v>1180</v>
       </c>
@@ -23338,7 +23845,9 @@
       <c r="AD247" s="2"/>
     </row>
     <row r="248" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A248" s="2"/>
+      <c r="A248" s="3">
+        <v>247</v>
+      </c>
       <c r="B248" s="2" t="s">
         <v>1180</v>
       </c>
@@ -23410,7 +23919,9 @@
       <c r="AD248" s="2"/>
     </row>
     <row r="249" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A249" s="2"/>
+      <c r="A249" s="3">
+        <v>248</v>
+      </c>
       <c r="B249" s="2" t="s">
         <v>1194</v>
       </c>
@@ -23454,7 +23965,9 @@
       <c r="AD249" s="2"/>
     </row>
     <row r="250" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A250" s="2"/>
+      <c r="A250" s="3">
+        <v>249</v>
+      </c>
       <c r="B250" s="2" t="s">
         <v>1197</v>
       </c>
@@ -23512,7 +24025,9 @@
       <c r="AD250" s="2"/>
     </row>
     <row r="251" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A251" s="2"/>
+      <c r="A251" s="3">
+        <v>250</v>
+      </c>
       <c r="B251" s="2" t="s">
         <v>1202</v>
       </c>
@@ -23584,7 +24099,9 @@
       <c r="AD251" s="2"/>
     </row>
     <row r="252" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A252" s="2"/>
+      <c r="A252" s="3">
+        <v>251</v>
+      </c>
       <c r="B252" s="2" t="s">
         <v>1210</v>
       </c>
@@ -23628,7 +24145,9 @@
       <c r="AD252" s="2"/>
     </row>
     <row r="253" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A253" s="2"/>
+      <c r="A253" s="3">
+        <v>252</v>
+      </c>
       <c r="B253" s="2" t="s">
         <v>1212</v>
       </c>
@@ -23686,7 +24205,9 @@
       <c r="AD253" s="2"/>
     </row>
     <row r="254" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A254" s="2"/>
+      <c r="A254" s="3">
+        <v>253</v>
+      </c>
       <c r="B254" s="2" t="s">
         <v>1219</v>
       </c>
@@ -23730,7 +24251,9 @@
       <c r="AD254" s="2"/>
     </row>
     <row r="255" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A255" s="2"/>
+      <c r="A255" s="3">
+        <v>254</v>
+      </c>
       <c r="B255" s="2" t="s">
         <v>1221</v>
       </c>
@@ -23774,7 +24297,9 @@
       <c r="AD255" s="2"/>
     </row>
     <row r="256" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A256" s="2"/>
+      <c r="A256" s="3">
+        <v>255</v>
+      </c>
       <c r="B256" s="2" t="s">
         <v>1223</v>
       </c>
@@ -23818,7 +24343,9 @@
       <c r="AD256" s="2"/>
     </row>
     <row r="257" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A257" s="2"/>
+      <c r="A257" s="3">
+        <v>256</v>
+      </c>
       <c r="B257" s="2" t="s">
         <v>1224</v>
       </c>
@@ -23862,7 +24389,9 @@
       <c r="AD257" s="2"/>
     </row>
     <row r="258" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A258" s="2"/>
+      <c r="A258" s="3">
+        <v>257</v>
+      </c>
       <c r="B258" s="2" t="s">
         <v>1219</v>
       </c>
@@ -23906,7 +24435,9 @@
       <c r="AD258" s="2"/>
     </row>
     <row r="259" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A259" s="2"/>
+      <c r="A259" s="3">
+        <v>258</v>
+      </c>
       <c r="B259" s="2" t="s">
         <v>1226</v>
       </c>
@@ -23950,7 +24481,9 @@
       <c r="AD259" s="2"/>
     </row>
     <row r="260" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A260" s="2"/>
+      <c r="A260" s="3">
+        <v>259</v>
+      </c>
       <c r="B260" s="2" t="s">
         <v>1228</v>
       </c>
@@ -23994,7 +24527,9 @@
       <c r="AD260" s="2"/>
     </row>
     <row r="261" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A261" s="2"/>
+      <c r="A261" s="3">
+        <v>260</v>
+      </c>
       <c r="B261" s="2" t="s">
         <v>1229</v>
       </c>
@@ -24038,7 +24573,9 @@
       <c r="AD261" s="2"/>
     </row>
     <row r="262" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A262" s="2"/>
+      <c r="A262" s="3">
+        <v>261</v>
+      </c>
       <c r="B262" s="2" t="s">
         <v>1231</v>
       </c>
@@ -24082,7 +24619,9 @@
       <c r="AD262" s="2"/>
     </row>
     <row r="263" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A263" s="2"/>
+      <c r="A263" s="3">
+        <v>262</v>
+      </c>
       <c r="B263" s="2" t="s">
         <v>1232</v>
       </c>
@@ -24126,7 +24665,9 @@
       <c r="AD263" s="2"/>
     </row>
     <row r="264" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A264" s="2"/>
+      <c r="A264" s="3">
+        <v>263</v>
+      </c>
       <c r="B264" s="2" t="s">
         <v>1233</v>
       </c>
@@ -24170,7 +24711,9 @@
       <c r="AD264" s="2"/>
     </row>
     <row r="265" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A265" s="2"/>
+      <c r="A265" s="3">
+        <v>264</v>
+      </c>
       <c r="B265" s="2" t="s">
         <v>1235</v>
       </c>
@@ -24214,7 +24757,9 @@
       <c r="AD265" s="2"/>
     </row>
     <row r="266" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A266" s="2"/>
+      <c r="A266" s="3">
+        <v>265</v>
+      </c>
       <c r="B266" s="2" t="s">
         <v>1237</v>
       </c>
@@ -24258,7 +24803,9 @@
       <c r="AD266" s="2"/>
     </row>
     <row r="267" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A267" s="2"/>
+      <c r="A267" s="3">
+        <v>266</v>
+      </c>
       <c r="B267" s="2" t="s">
         <v>1239</v>
       </c>
@@ -24302,7 +24849,9 @@
       <c r="AD267" s="2"/>
     </row>
     <row r="268" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A268" s="2"/>
+      <c r="A268" s="3">
+        <v>267</v>
+      </c>
       <c r="B268" s="2" t="s">
         <v>1241</v>
       </c>
@@ -24374,7 +24923,9 @@
       <c r="AD268" s="2"/>
     </row>
     <row r="269" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A269" s="2"/>
+      <c r="A269" s="3">
+        <v>268</v>
+      </c>
       <c r="B269" s="2" t="s">
         <v>1241</v>
       </c>
@@ -24418,7 +24969,9 @@
       <c r="AD269" s="2"/>
     </row>
     <row r="270" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A270" s="2"/>
+      <c r="A270" s="3">
+        <v>269</v>
+      </c>
       <c r="B270" s="2" t="s">
         <v>1241</v>
       </c>
@@ -24462,7 +25015,9 @@
       <c r="AD270" s="2"/>
     </row>
     <row r="271" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A271" s="2"/>
+      <c r="A271" s="3">
+        <v>270</v>
+      </c>
       <c r="B271" s="2" t="s">
         <v>1241</v>
       </c>
@@ -24506,7 +25061,9 @@
       <c r="AD271" s="2"/>
     </row>
     <row r="272" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A272" s="2"/>
+      <c r="A272" s="3">
+        <v>271</v>
+      </c>
       <c r="B272" s="2" t="s">
         <v>1241</v>
       </c>
@@ -24576,7 +25133,9 @@
       <c r="AD272" s="2"/>
     </row>
     <row r="273" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A273" s="2"/>
+      <c r="A273" s="3">
+        <v>272</v>
+      </c>
       <c r="B273" s="2" t="s">
         <v>1263</v>
       </c>
@@ -24620,7 +25179,9 @@
       <c r="AD273" s="2"/>
     </row>
     <row r="274" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A274" s="2"/>
+      <c r="A274" s="3">
+        <v>273</v>
+      </c>
       <c r="B274" s="2" t="s">
         <v>1263</v>
       </c>
@@ -24664,7 +25225,9 @@
       <c r="AD274" s="2"/>
     </row>
     <row r="275" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A275" s="2"/>
+      <c r="A275" s="3">
+        <v>274</v>
+      </c>
       <c r="B275" s="2" t="s">
         <v>1267</v>
       </c>
@@ -24736,7 +25299,9 @@
       <c r="AD275" s="2"/>
     </row>
     <row r="276" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A276" s="2"/>
+      <c r="A276" s="3">
+        <v>275</v>
+      </c>
       <c r="B276" s="2" t="s">
         <v>1267</v>
       </c>
@@ -24808,7 +25373,9 @@
       <c r="AD276" s="2"/>
     </row>
     <row r="277" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A277" s="2"/>
+      <c r="A277" s="3">
+        <v>276</v>
+      </c>
       <c r="B277" s="2" t="s">
         <v>1267</v>
       </c>
@@ -24880,7 +25447,9 @@
       <c r="AD277" s="2"/>
     </row>
     <row r="278" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A278" s="2"/>
+      <c r="A278" s="3">
+        <v>277</v>
+      </c>
       <c r="B278" s="2" t="s">
         <v>1267</v>
       </c>
@@ -24952,7 +25521,9 @@
       <c r="AD278" s="2"/>
     </row>
     <row r="279" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A279" s="2"/>
+      <c r="A279" s="3">
+        <v>278</v>
+      </c>
       <c r="B279" s="2" t="s">
         <v>1267</v>
       </c>
@@ -25024,7 +25595,9 @@
       <c r="AD279" s="2"/>
     </row>
     <row r="280" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A280" s="2"/>
+      <c r="A280" s="3">
+        <v>279</v>
+      </c>
       <c r="B280" s="2" t="s">
         <v>1267</v>
       </c>
@@ -25096,7 +25669,9 @@
       <c r="AD280" s="2"/>
     </row>
     <row r="281" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A281" s="2"/>
+      <c r="A281" s="3">
+        <v>280</v>
+      </c>
       <c r="B281" s="2" t="s">
         <v>1304</v>
       </c>
@@ -25168,7 +25743,9 @@
       <c r="AD281" s="2"/>
     </row>
     <row r="282" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A282" s="2"/>
+      <c r="A282" s="3">
+        <v>281</v>
+      </c>
       <c r="B282" s="2" t="s">
         <v>1304</v>
       </c>
@@ -25228,7 +25805,9 @@
       <c r="AD282" s="2"/>
     </row>
     <row r="283" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A283" s="2"/>
+      <c r="A283" s="3">
+        <v>282</v>
+      </c>
       <c r="B283" s="2" t="s">
         <v>1322</v>
       </c>
@@ -25272,7 +25851,9 @@
       <c r="AD283" s="2"/>
     </row>
     <row r="284" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A284" s="2"/>
+      <c r="A284" s="3">
+        <v>283</v>
+      </c>
       <c r="B284" s="2" t="s">
         <v>1322</v>
       </c>
@@ -25344,7 +25925,9 @@
       <c r="AD284" s="2"/>
     </row>
     <row r="285" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A285" s="2"/>
+      <c r="A285" s="3">
+        <v>284</v>
+      </c>
       <c r="B285" s="2" t="s">
         <v>1334</v>
       </c>
@@ -25416,7 +25999,9 @@
       <c r="AD285" s="2"/>
     </row>
     <row r="286" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A286" s="2"/>
+      <c r="A286" s="3">
+        <v>285</v>
+      </c>
       <c r="B286" s="2" t="s">
         <v>1334</v>
       </c>
@@ -25486,7 +26071,9 @@
       <c r="AD286" s="2"/>
     </row>
     <row r="287" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A287" s="2"/>
+      <c r="A287" s="3">
+        <v>286</v>
+      </c>
       <c r="B287" s="2" t="s">
         <v>1352</v>
       </c>
@@ -25558,7 +26145,9 @@
       <c r="AD287" s="2"/>
     </row>
     <row r="288" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A288" s="2"/>
+      <c r="A288" s="3">
+        <v>287</v>
+      </c>
       <c r="B288" s="2" t="s">
         <v>1352</v>
       </c>
@@ -25622,7 +26211,9 @@
       <c r="AD288" s="2"/>
     </row>
     <row r="289" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A289" s="2"/>
+      <c r="A289" s="3">
+        <v>288</v>
+      </c>
       <c r="B289" s="2" t="s">
         <v>1352</v>
       </c>
@@ -25694,7 +26285,9 @@
       <c r="AD289" s="2"/>
     </row>
     <row r="290" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A290" s="2"/>
+      <c r="A290" s="3">
+        <v>289</v>
+      </c>
       <c r="B290" s="2" t="s">
         <v>1352</v>
       </c>
@@ -25764,7 +26357,9 @@
       <c r="AD290" s="2"/>
     </row>
     <row r="291" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A291" s="2"/>
+      <c r="A291" s="3">
+        <v>290</v>
+      </c>
       <c r="B291" s="2" t="s">
         <v>1385</v>
       </c>
@@ -25838,7 +26433,9 @@
       <c r="AD291" s="2"/>
     </row>
     <row r="292" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A292" s="2"/>
+      <c r="A292" s="3">
+        <v>291</v>
+      </c>
       <c r="B292" s="2" t="s">
         <v>1385</v>
       </c>
@@ -25900,7 +26497,9 @@
       <c r="AD292" s="2"/>
     </row>
     <row r="293" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A293" s="2"/>
+      <c r="A293" s="3">
+        <v>292</v>
+      </c>
       <c r="B293" s="2" t="s">
         <v>1385</v>
       </c>
@@ -25944,7 +26543,9 @@
       <c r="AD293" s="2"/>
     </row>
     <row r="294" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A294" s="2"/>
+      <c r="A294" s="3">
+        <v>293</v>
+      </c>
       <c r="B294" s="2" t="s">
         <v>1401</v>
       </c>
@@ -26004,7 +26605,9 @@
       <c r="AD294" s="2"/>
     </row>
     <row r="295" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A295" s="2"/>
+      <c r="A295" s="3">
+        <v>294</v>
+      </c>
       <c r="B295" s="2" t="s">
         <v>1401</v>
       </c>
@@ -26064,7 +26667,9 @@
       <c r="AD295" s="2"/>
     </row>
     <row r="296" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A296" s="2"/>
+      <c r="A296" s="3">
+        <v>295</v>
+      </c>
       <c r="B296" s="2" t="s">
         <v>1401</v>
       </c>
@@ -26124,7 +26729,9 @@
       <c r="AD296" s="2"/>
     </row>
     <row r="297" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A297" s="2"/>
+      <c r="A297" s="3">
+        <v>296</v>
+      </c>
       <c r="B297" s="2" t="s">
         <v>1401</v>
       </c>
@@ -26184,7 +26791,9 @@
       <c r="AD297" s="2"/>
     </row>
     <row r="298" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A298" s="2"/>
+      <c r="A298" s="3">
+        <v>297</v>
+      </c>
       <c r="B298" s="2" t="s">
         <v>1401</v>
       </c>
@@ -26244,7 +26853,9 @@
       <c r="AD298" s="2"/>
     </row>
     <row r="299" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A299" s="2"/>
+      <c r="A299" s="3">
+        <v>298</v>
+      </c>
       <c r="B299" s="2" t="s">
         <v>1418</v>
       </c>
@@ -26308,7 +26919,9 @@
       <c r="AD299" s="2"/>
     </row>
     <row r="300" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A300" s="2"/>
+      <c r="A300" s="3">
+        <v>299</v>
+      </c>
       <c r="B300" s="2" t="s">
         <v>1428</v>
       </c>
@@ -26380,7 +26993,9 @@
       <c r="AD300" s="2"/>
     </row>
     <row r="301" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A301" s="2"/>
+      <c r="A301" s="3">
+        <v>300</v>
+      </c>
       <c r="B301" s="2" t="s">
         <v>1428</v>
       </c>
@@ -26434,7 +27049,9 @@
       <c r="AD301" s="2"/>
     </row>
     <row r="302" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A302" s="2"/>
+      <c r="A302" s="3">
+        <v>301</v>
+      </c>
       <c r="B302" s="2" t="s">
         <v>1428</v>
       </c>
@@ -26488,7 +27105,9 @@
       <c r="AD302" s="2"/>
     </row>
     <row r="303" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A303" s="2"/>
+      <c r="A303" s="3">
+        <v>302</v>
+      </c>
       <c r="B303" s="2" t="s">
         <v>1428</v>
       </c>
@@ -26542,7 +27161,9 @@
       <c r="AD303" s="2"/>
     </row>
     <row r="304" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A304" s="2"/>
+      <c r="A304" s="3">
+        <v>303</v>
+      </c>
       <c r="B304" s="2" t="s">
         <v>1428</v>
       </c>
@@ -26594,7 +27215,9 @@
       <c r="AD304" s="2"/>
     </row>
     <row r="305" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A305" s="2"/>
+      <c r="A305" s="3">
+        <v>304</v>
+      </c>
       <c r="B305" s="2" t="s">
         <v>1428</v>
       </c>
@@ -26646,7 +27269,9 @@
       <c r="AD305" s="2"/>
     </row>
     <row r="306" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A306" s="2"/>
+      <c r="A306" s="3">
+        <v>305</v>
+      </c>
       <c r="B306" s="2" t="s">
         <v>1428</v>
       </c>
@@ -26690,7 +27315,9 @@
       <c r="AD306" s="2"/>
     </row>
     <row r="307" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A307" s="2"/>
+      <c r="A307" s="3">
+        <v>306</v>
+      </c>
       <c r="B307" s="2" t="s">
         <v>1428</v>
       </c>
@@ -26734,7 +27361,9 @@
       <c r="AD307" s="2"/>
     </row>
     <row r="308" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A308" s="2"/>
+      <c r="A308" s="3">
+        <v>307</v>
+      </c>
       <c r="B308" s="2" t="s">
         <v>1445</v>
       </c>
@@ -26806,7 +27435,9 @@
       <c r="AD308" s="2"/>
     </row>
     <row r="309" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A309" s="2"/>
+      <c r="A309" s="3">
+        <v>308</v>
+      </c>
       <c r="B309" s="2" t="s">
         <v>1456</v>
       </c>
@@ -26878,7 +27509,9 @@
       <c r="AD309" s="2"/>
     </row>
     <row r="310" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A310" s="2"/>
+      <c r="A310" s="3">
+        <v>309</v>
+      </c>
       <c r="B310" s="2" t="s">
         <v>1467</v>
       </c>
@@ -26936,7 +27569,9 @@
       <c r="AD310" s="2"/>
     </row>
     <row r="311" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A311" s="2"/>
+      <c r="A311" s="3">
+        <v>310</v>
+      </c>
       <c r="B311" s="2" t="s">
         <v>1473</v>
       </c>
@@ -26980,7 +27615,9 @@
       <c r="AD311" s="2"/>
     </row>
     <row r="312" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A312" s="2"/>
+      <c r="A312" s="3">
+        <v>311</v>
+      </c>
       <c r="B312" s="2" t="s">
         <v>1475</v>
       </c>
@@ -27040,7 +27677,9 @@
       <c r="AD312" s="2"/>
     </row>
     <row r="313" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A313" s="2"/>
+      <c r="A313" s="3">
+        <v>312</v>
+      </c>
       <c r="B313" s="2" t="s">
         <v>1484</v>
       </c>
@@ -27106,7 +27745,9 @@
       <c r="AD313" s="2"/>
     </row>
     <row r="314" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A314" s="2"/>
+      <c r="A314" s="3">
+        <v>313</v>
+      </c>
       <c r="B314" s="2" t="s">
         <v>1491</v>
       </c>
@@ -27152,7 +27793,9 @@
       <c r="AD314" s="2"/>
     </row>
     <row r="315" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A315" s="2"/>
+      <c r="A315" s="3">
+        <v>314</v>
+      </c>
       <c r="B315" s="2" t="s">
         <v>1495</v>
       </c>
@@ -27218,7 +27861,9 @@
       <c r="AD315" s="2"/>
     </row>
     <row r="316" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A316" s="2"/>
+      <c r="A316" s="3">
+        <v>315</v>
+      </c>
       <c r="B316" s="2" t="s">
         <v>1503</v>
       </c>
@@ -27270,7 +27915,9 @@
       <c r="AD316" s="2"/>
     </row>
     <row r="317" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A317" s="2"/>
+      <c r="A317" s="3">
+        <v>316</v>
+      </c>
       <c r="B317" s="2" t="s">
         <v>1505</v>
       </c>
@@ -27342,7 +27989,9 @@
       <c r="AD317" s="2"/>
     </row>
     <row r="318" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A318" s="2"/>
+      <c r="A318" s="3">
+        <v>317</v>
+      </c>
       <c r="B318" s="2" t="s">
         <v>1505</v>
       </c>
@@ -27408,7 +28057,9 @@
       <c r="AD318" s="2"/>
     </row>
     <row r="319" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A319" s="2"/>
+      <c r="A319" s="3">
+        <v>318</v>
+      </c>
       <c r="B319" s="2" t="s">
         <v>1505</v>
       </c>
@@ -27480,7 +28131,9 @@
       <c r="AD319" s="2"/>
     </row>
     <row r="320" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A320" s="2"/>
+      <c r="A320" s="3">
+        <v>319</v>
+      </c>
       <c r="B320" s="2" t="s">
         <v>1505</v>
       </c>
@@ -27552,7 +28205,9 @@
       <c r="AD320" s="2"/>
     </row>
     <row r="321" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A321" s="2"/>
+      <c r="A321" s="3">
+        <v>320</v>
+      </c>
       <c r="B321" s="2" t="s">
         <v>1505</v>
       </c>
@@ -27614,7 +28269,9 @@
       <c r="AD321" s="2"/>
     </row>
     <row r="322" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A322" s="2"/>
+      <c r="A322" s="3">
+        <v>321</v>
+      </c>
       <c r="B322" s="2" t="s">
         <v>1541</v>
       </c>
@@ -27684,7 +28341,9 @@
       <c r="AD322" s="2"/>
     </row>
     <row r="323" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A323" s="2"/>
+      <c r="A323" s="3">
+        <v>322</v>
+      </c>
       <c r="B323" s="2" t="s">
         <v>1541</v>
       </c>
@@ -27742,7 +28401,9 @@
       <c r="AD323" s="2"/>
     </row>
     <row r="324" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A324" s="2"/>
+      <c r="A324" s="3">
+        <v>323</v>
+      </c>
       <c r="B324" s="2" t="s">
         <v>1541</v>
       </c>
@@ -27814,7 +28475,9 @@
       <c r="AD324" s="2"/>
     </row>
     <row r="325" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A325" s="2"/>
+      <c r="A325" s="3">
+        <v>324</v>
+      </c>
       <c r="B325" s="2" t="s">
         <v>1541</v>
       </c>
@@ -27858,7 +28521,9 @@
       <c r="AD325" s="2"/>
     </row>
     <row r="326" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A326" s="2"/>
+      <c r="A326" s="3">
+        <v>325</v>
+      </c>
       <c r="B326" s="2" t="s">
         <v>1562</v>
       </c>
@@ -27922,7 +28587,9 @@
       <c r="AD326" s="2"/>
     </row>
     <row r="327" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A327" s="2"/>
+      <c r="A327" s="3">
+        <v>326</v>
+      </c>
       <c r="B327" s="2" t="s">
         <v>1570</v>
       </c>
@@ -27980,7 +28647,9 @@
       <c r="AD327" s="2"/>
     </row>
     <row r="328" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A328" s="2"/>
+      <c r="A328" s="3">
+        <v>327</v>
+      </c>
       <c r="B328" s="2" t="s">
         <v>1334</v>
       </c>
@@ -28052,7 +28721,9 @@
       <c r="AD328" s="2"/>
     </row>
     <row r="329" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A329" s="2"/>
+      <c r="A329" s="3">
+        <v>328</v>
+      </c>
       <c r="B329" s="2" t="s">
         <v>1585</v>
       </c>
@@ -28112,7 +28783,9 @@
       <c r="AD329" s="2"/>
     </row>
     <row r="330" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A330" s="2"/>
+      <c r="A330" s="3">
+        <v>329</v>
+      </c>
       <c r="B330" s="2" t="s">
         <v>1585</v>
       </c>
@@ -28172,7 +28845,9 @@
       <c r="AD330" s="2"/>
     </row>
     <row r="331" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A331" s="2"/>
+      <c r="A331" s="3">
+        <v>330</v>
+      </c>
       <c r="B331" s="2" t="s">
         <v>1428</v>
       </c>
@@ -28236,7 +28911,9 @@
       <c r="AD331" s="2"/>
     </row>
     <row r="332" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A332" s="2"/>
+      <c r="A332" s="3">
+        <v>331</v>
+      </c>
       <c r="B332" s="2" t="s">
         <v>1428</v>
       </c>
@@ -28302,7 +28979,9 @@
       <c r="AD332" s="2"/>
     </row>
     <row r="333" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A333" s="2"/>
+      <c r="A333" s="3">
+        <v>332</v>
+      </c>
       <c r="B333" s="2" t="s">
         <v>1602</v>
       </c>
@@ -28364,7 +29043,9 @@
       <c r="AD333" s="2"/>
     </row>
     <row r="334" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A334" s="2"/>
+      <c r="A334" s="3">
+        <v>333</v>
+      </c>
       <c r="B334" s="2" t="s">
         <v>1602</v>
       </c>
@@ -28408,7 +29089,9 @@
       <c r="AD334" s="2"/>
     </row>
     <row r="335" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A335" s="2"/>
+      <c r="A335" s="3">
+        <v>334</v>
+      </c>
       <c r="B335" s="2" t="s">
         <v>1612</v>
       </c>
@@ -28468,7 +29151,9 @@
       <c r="AD335" s="2"/>
     </row>
     <row r="336" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A336" s="2"/>
+      <c r="A336" s="3">
+        <v>335</v>
+      </c>
       <c r="B336" s="2" t="s">
         <v>1612</v>
       </c>
@@ -28526,7 +29211,9 @@
       <c r="AD336" s="2"/>
     </row>
     <row r="337" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A337" s="2"/>
+      <c r="A337" s="3">
+        <v>336</v>
+      </c>
       <c r="B337" s="2" t="s">
         <v>1612</v>
       </c>
@@ -28584,7 +29271,9 @@
       <c r="AD337" s="2"/>
     </row>
     <row r="338" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A338" s="2"/>
+      <c r="A338" s="3">
+        <v>337</v>
+      </c>
       <c r="B338" s="2" t="s">
         <v>1612</v>
       </c>
@@ -28640,7 +29329,9 @@
       <c r="AD338" s="2"/>
     </row>
     <row r="339" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A339" s="2"/>
+      <c r="A339" s="3">
+        <v>338</v>
+      </c>
       <c r="B339" s="2" t="s">
         <v>1612</v>
       </c>
@@ -28696,7 +29387,9 @@
       <c r="AD339" s="2"/>
     </row>
     <row r="340" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A340" s="2"/>
+      <c r="A340" s="3">
+        <v>339</v>
+      </c>
       <c r="B340" s="2" t="s">
         <v>1636</v>
       </c>
@@ -28768,7 +29461,9 @@
       <c r="AD340" s="2"/>
     </row>
     <row r="341" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A341" s="2"/>
+      <c r="A341" s="3">
+        <v>340</v>
+      </c>
       <c r="B341" s="2" t="s">
         <v>1645</v>
       </c>
@@ -28840,7 +29535,9 @@
       <c r="AD341" s="2"/>
     </row>
     <row r="342" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A342" s="2"/>
+      <c r="A342" s="3">
+        <v>341</v>
+      </c>
       <c r="B342" s="2" t="s">
         <v>340</v>
       </c>
@@ -28914,7 +29611,9 @@
       <c r="AD342" s="2"/>
     </row>
     <row r="343" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A343" s="2"/>
+      <c r="A343" s="3">
+        <v>342</v>
+      </c>
       <c r="B343" s="2" t="s">
         <v>340</v>
       </c>
@@ -28988,7 +29687,9 @@
       <c r="AD343" s="2"/>
     </row>
     <row r="344" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A344" s="2"/>
+      <c r="A344" s="3">
+        <v>343</v>
+      </c>
       <c r="B344" s="2" t="s">
         <v>340</v>
       </c>
@@ -29062,7 +29763,9 @@
       <c r="AD344" s="2"/>
     </row>
     <row r="345" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A345" s="2"/>
+      <c r="A345" s="3">
+        <v>344</v>
+      </c>
       <c r="B345" s="2" t="s">
         <v>340</v>
       </c>
@@ -29136,7 +29839,9 @@
       <c r="AD345" s="2"/>
     </row>
     <row r="346" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A346" s="2"/>
+      <c r="A346" s="3">
+        <v>345</v>
+      </c>
       <c r="B346" s="2" t="s">
         <v>340</v>
       </c>
@@ -29198,7 +29903,9 @@
       <c r="AD346" s="2"/>
     </row>
     <row r="347" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A347" s="2"/>
+      <c r="A347" s="3">
+        <v>346</v>
+      </c>
       <c r="B347" s="2" t="s">
         <v>1675</v>
       </c>
@@ -29270,7 +29977,9 @@
       <c r="AD347" s="2"/>
     </row>
     <row r="348" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A348" s="2"/>
+      <c r="A348" s="3">
+        <v>347</v>
+      </c>
       <c r="B348" s="2" t="s">
         <v>1675</v>
       </c>
@@ -29342,7 +30051,9 @@
       <c r="AD348" s="2"/>
     </row>
     <row r="349" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A349" s="2"/>
+      <c r="A349" s="3">
+        <v>348</v>
+      </c>
       <c r="B349" s="2" t="s">
         <v>1602</v>
       </c>
@@ -29386,7 +30097,9 @@
       <c r="AD349" s="2"/>
     </row>
     <row r="350" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A350" s="2"/>
+      <c r="A350" s="3">
+        <v>349</v>
+      </c>
       <c r="B350" s="2" t="s">
         <v>1602</v>
       </c>
@@ -29430,7 +30143,9 @@
       <c r="AD350" s="2"/>
     </row>
     <row r="351" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A351" s="2"/>
+      <c r="A351" s="3">
+        <v>350</v>
+      </c>
       <c r="B351" s="2" t="s">
         <v>1602</v>
       </c>
@@ -29474,7 +30189,9 @@
       <c r="AD351" s="2"/>
     </row>
     <row r="352" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A352" s="2"/>
+      <c r="A352" s="3">
+        <v>351</v>
+      </c>
       <c r="B352" s="2" t="s">
         <v>1602</v>
       </c>
@@ -29518,7 +30235,9 @@
       <c r="AD352" s="2"/>
     </row>
     <row r="353" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A353" s="2"/>
+      <c r="A353" s="3">
+        <v>352</v>
+      </c>
       <c r="B353" s="2" t="s">
         <v>1602</v>
       </c>
@@ -29562,7 +30281,9 @@
       <c r="AD353" s="2"/>
     </row>
     <row r="354" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A354" s="2"/>
+      <c r="A354" s="3">
+        <v>353</v>
+      </c>
       <c r="B354" s="2" t="s">
         <v>1695</v>
       </c>
@@ -29634,7 +30355,9 @@
       <c r="AD354" s="2"/>
     </row>
     <row r="355" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A355" s="2"/>
+      <c r="A355" s="3">
+        <v>354</v>
+      </c>
       <c r="B355" s="2" t="s">
         <v>1602</v>
       </c>
@@ -29692,7 +30415,9 @@
       <c r="AD355" s="2"/>
     </row>
     <row r="356" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A356" s="2"/>
+      <c r="A356" s="3">
+        <v>355</v>
+      </c>
       <c r="B356" s="2" t="s">
         <v>1602</v>
       </c>
@@ -29758,7 +30483,9 @@
       <c r="AD356" s="2"/>
     </row>
     <row r="357" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A357" s="2"/>
+      <c r="A357" s="3">
+        <v>356</v>
+      </c>
       <c r="B357" s="2" t="s">
         <v>1720</v>
       </c>
@@ -29826,7 +30553,9 @@
       <c r="AD357" s="2"/>
     </row>
     <row r="358" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A358" s="2"/>
+      <c r="A358" s="3">
+        <v>357</v>
+      </c>
       <c r="B358" s="2" t="s">
         <v>1727</v>
       </c>
@@ -29892,7 +30621,9 @@
       <c r="AD358" s="2"/>
     </row>
     <row r="359" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A359" s="2"/>
+      <c r="A359" s="3">
+        <v>358</v>
+      </c>
       <c r="B359" s="2" t="s">
         <v>1334</v>
       </c>
@@ -29958,7 +30689,9 @@
       <c r="AD359" s="2"/>
     </row>
     <row r="360" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A360" s="2"/>
+      <c r="A360" s="3">
+        <v>359</v>
+      </c>
       <c r="B360" s="2" t="s">
         <v>1738</v>
       </c>
@@ -30026,7 +30759,9 @@
       <c r="AD360" s="2"/>
     </row>
     <row r="361" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A361" s="2"/>
+      <c r="A361" s="3">
+        <v>360</v>
+      </c>
       <c r="B361" s="2" t="s">
         <v>1738</v>
       </c>
@@ -30094,7 +30829,9 @@
       <c r="AD361" s="2"/>
     </row>
     <row r="362" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A362" s="2"/>
+      <c r="A362" s="3">
+        <v>361</v>
+      </c>
       <c r="B362" s="2" t="s">
         <v>1750</v>
       </c>
@@ -30162,7 +30899,9 @@
       <c r="AD362" s="2"/>
     </row>
     <row r="363" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A363" s="2"/>
+      <c r="A363" s="3">
+        <v>362</v>
+      </c>
       <c r="B363" s="2" t="s">
         <v>1758</v>
       </c>
@@ -30230,7 +30969,9 @@
       <c r="AD363" s="2"/>
     </row>
     <row r="364" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A364" s="2"/>
+      <c r="A364" s="3">
+        <v>363</v>
+      </c>
       <c r="B364" s="2" t="s">
         <v>1758</v>
       </c>
@@ -30298,7 +31039,9 @@
       <c r="AD364" s="2"/>
     </row>
     <row r="365" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A365" s="2"/>
+      <c r="A365" s="3">
+        <v>364</v>
+      </c>
       <c r="B365" s="2" t="s">
         <v>1771</v>
       </c>
@@ -30366,7 +31109,9 @@
       <c r="AD365" s="2"/>
     </row>
     <row r="366" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A366" s="2"/>
+      <c r="A366" s="3">
+        <v>365</v>
+      </c>
       <c r="B366" s="2" t="s">
         <v>1771</v>
       </c>
@@ -30434,7 +31179,9 @@
       <c r="AD366" s="2"/>
     </row>
     <row r="367" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A367" s="2"/>
+      <c r="A367" s="3">
+        <v>366</v>
+      </c>
       <c r="B367" s="2" t="s">
         <v>1781</v>
       </c>
@@ -30502,7 +31249,9 @@
       <c r="AD367" s="2"/>
     </row>
     <row r="368" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A368" s="2"/>
+      <c r="A368" s="3">
+        <v>367</v>
+      </c>
       <c r="B368" s="2" t="s">
         <v>1781</v>
       </c>
@@ -30570,7 +31319,9 @@
       <c r="AD368" s="2"/>
     </row>
     <row r="369" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A369" s="2"/>
+      <c r="A369" s="3">
+        <v>368</v>
+      </c>
       <c r="B369" s="2" t="s">
         <v>1781</v>
       </c>
@@ -30638,7 +31389,9 @@
       <c r="AD369" s="2"/>
     </row>
     <row r="370" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A370" s="2"/>
+      <c r="A370" s="3">
+        <v>369</v>
+      </c>
       <c r="B370" s="2" t="s">
         <v>1781</v>
       </c>
@@ -30706,7 +31459,9 @@
       <c r="AD370" s="2"/>
     </row>
     <row r="371" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A371" s="2"/>
+      <c r="A371" s="3">
+        <v>370</v>
+      </c>
       <c r="B371" s="2" t="s">
         <v>1781</v>
       </c>
@@ -30774,7 +31529,9 @@
       <c r="AD371" s="2"/>
     </row>
     <row r="372" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A372" s="2"/>
+      <c r="A372" s="3">
+        <v>371</v>
+      </c>
       <c r="B372" s="2" t="s">
         <v>1781</v>
       </c>
@@ -30842,7 +31599,9 @@
       <c r="AD372" s="2"/>
     </row>
     <row r="373" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A373" s="2"/>
+      <c r="A373" s="3">
+        <v>372</v>
+      </c>
       <c r="B373" s="2" t="s">
         <v>1781</v>
       </c>
@@ -30910,7 +31669,9 @@
       <c r="AD373" s="2"/>
     </row>
     <row r="374" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A374" s="2"/>
+      <c r="A374" s="3">
+        <v>373</v>
+      </c>
       <c r="B374" s="2" t="s">
         <v>1781</v>
       </c>
@@ -30978,7 +31739,9 @@
       <c r="AD374" s="2"/>
     </row>
     <row r="375" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A375" s="2"/>
+      <c r="A375" s="3">
+        <v>374</v>
+      </c>
       <c r="B375" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31038,7 +31801,9 @@
       <c r="AD375" s="2"/>
     </row>
     <row r="376" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A376" s="2"/>
+      <c r="A376" s="3">
+        <v>375</v>
+      </c>
       <c r="B376" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31098,7 +31863,9 @@
       <c r="AD376" s="2"/>
     </row>
     <row r="377" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A377" s="2"/>
+      <c r="A377" s="3">
+        <v>376</v>
+      </c>
       <c r="B377" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31158,7 +31925,9 @@
       <c r="AD377" s="2"/>
     </row>
     <row r="378" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A378" s="2"/>
+      <c r="A378" s="3">
+        <v>377</v>
+      </c>
       <c r="B378" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31218,7 +31987,9 @@
       <c r="AD378" s="2"/>
     </row>
     <row r="379" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A379" s="2"/>
+      <c r="A379" s="3">
+        <v>378</v>
+      </c>
       <c r="B379" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31278,7 +32049,9 @@
       <c r="AD379" s="2"/>
     </row>
     <row r="380" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A380" s="2"/>
+      <c r="A380" s="3">
+        <v>379</v>
+      </c>
       <c r="B380" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31338,7 +32111,9 @@
       <c r="AD380" s="2"/>
     </row>
     <row r="381" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A381" s="2"/>
+      <c r="A381" s="3">
+        <v>380</v>
+      </c>
       <c r="B381" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31398,7 +32173,9 @@
       <c r="AD381" s="2"/>
     </row>
     <row r="382" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A382" s="2"/>
+      <c r="A382" s="3">
+        <v>381</v>
+      </c>
       <c r="B382" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31458,7 +32235,9 @@
       <c r="AD382" s="2"/>
     </row>
     <row r="383" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A383" s="2"/>
+      <c r="A383" s="3">
+        <v>382</v>
+      </c>
       <c r="B383" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31518,7 +32297,9 @@
       <c r="AD383" s="2"/>
     </row>
     <row r="384" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A384" s="2"/>
+      <c r="A384" s="3">
+        <v>383</v>
+      </c>
       <c r="B384" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31578,7 +32359,9 @@
       <c r="AD384" s="2"/>
     </row>
     <row r="385" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A385" s="2"/>
+      <c r="A385" s="3">
+        <v>384</v>
+      </c>
       <c r="B385" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31638,7 +32421,9 @@
       <c r="AD385" s="2"/>
     </row>
     <row r="386" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A386" s="2"/>
+      <c r="A386" s="3">
+        <v>385</v>
+      </c>
       <c r="B386" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31698,7 +32483,9 @@
       <c r="AD386" s="2"/>
     </row>
     <row r="387" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A387" s="2"/>
+      <c r="A387" s="3">
+        <v>386</v>
+      </c>
       <c r="B387" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31758,7 +32545,9 @@
       <c r="AD387" s="2"/>
     </row>
     <row r="388" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A388" s="2"/>
+      <c r="A388" s="3">
+        <v>387</v>
+      </c>
       <c r="B388" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31818,7 +32607,9 @@
       <c r="AD388" s="2"/>
     </row>
     <row r="389" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A389" s="2"/>
+      <c r="A389" s="3">
+        <v>388</v>
+      </c>
       <c r="B389" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31878,7 +32669,9 @@
       <c r="AD389" s="2"/>
     </row>
     <row r="390" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A390" s="2"/>
+      <c r="A390" s="3">
+        <v>389</v>
+      </c>
       <c r="B390" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31938,7 +32731,9 @@
       <c r="AD390" s="2"/>
     </row>
     <row r="391" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A391" s="2"/>
+      <c r="A391" s="3">
+        <v>390</v>
+      </c>
       <c r="B391" s="2" t="s">
         <v>1781</v>
       </c>
@@ -31998,7 +32793,9 @@
       <c r="AD391" s="2"/>
     </row>
     <row r="392" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A392" s="2"/>
+      <c r="A392" s="3">
+        <v>391</v>
+      </c>
       <c r="B392" s="2" t="s">
         <v>1781</v>
       </c>
@@ -32058,7 +32855,9 @@
       <c r="AD392" s="2"/>
     </row>
     <row r="393" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A393" s="2"/>
+      <c r="A393" s="3">
+        <v>392</v>
+      </c>
       <c r="B393" s="2" t="s">
         <v>1781</v>
       </c>
@@ -32118,7 +32917,9 @@
       <c r="AD393" s="2"/>
     </row>
     <row r="394" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A394" s="2"/>
+      <c r="A394" s="3">
+        <v>393</v>
+      </c>
       <c r="B394" s="2" t="s">
         <v>1781</v>
       </c>
@@ -32178,7 +32979,9 @@
       <c r="AD394" s="2"/>
     </row>
     <row r="395" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A395" s="2"/>
+      <c r="A395" s="3">
+        <v>394</v>
+      </c>
       <c r="B395" s="2" t="s">
         <v>1781</v>
       </c>
@@ -32238,7 +33041,9 @@
       <c r="AD395" s="2"/>
     </row>
     <row r="396" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A396" s="2"/>
+      <c r="A396" s="3">
+        <v>395</v>
+      </c>
       <c r="B396" s="2" t="s">
         <v>1781</v>
       </c>
@@ -32298,7 +33103,9 @@
       <c r="AD396" s="2"/>
     </row>
     <row r="397" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A397" s="2"/>
+      <c r="A397" s="3">
+        <v>396</v>
+      </c>
       <c r="B397" s="2" t="s">
         <v>1781</v>
       </c>
@@ -32358,7 +33165,9 @@
       <c r="AD397" s="2"/>
     </row>
     <row r="398" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A398" s="2"/>
+      <c r="A398" s="3">
+        <v>397</v>
+      </c>
       <c r="B398" s="2" t="s">
         <v>1781</v>
       </c>
@@ -32418,7 +33227,9 @@
       <c r="AD398" s="2"/>
     </row>
     <row r="399" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A399" s="2"/>
+      <c r="A399" s="3">
+        <v>398</v>
+      </c>
       <c r="B399" s="2" t="s">
         <v>1781</v>
       </c>
@@ -32478,7 +33289,9 @@
       <c r="AD399" s="2"/>
     </row>
     <row r="400" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A400" s="2"/>
+      <c r="A400" s="3">
+        <v>399</v>
+      </c>
       <c r="B400" s="2" t="s">
         <v>1781</v>
       </c>
@@ -32538,7 +33351,9 @@
       <c r="AD400" s="2"/>
     </row>
     <row r="401" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A401" s="2"/>
+      <c r="A401" s="3">
+        <v>400</v>
+      </c>
       <c r="B401" s="2" t="s">
         <v>1781</v>
       </c>
@@ -32598,7 +33413,9 @@
       <c r="AD401" s="2"/>
     </row>
     <row r="402" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A402" s="2"/>
+      <c r="A402" s="3">
+        <v>401</v>
+      </c>
       <c r="B402" s="2" t="s">
         <v>1781</v>
       </c>
@@ -32658,7 +33475,9 @@
       <c r="AD402" s="2"/>
     </row>
     <row r="403" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A403" s="2"/>
+      <c r="A403" s="3">
+        <v>402</v>
+      </c>
       <c r="B403" s="2" t="s">
         <v>1781</v>
       </c>
@@ -32718,7 +33537,9 @@
       <c r="AD403" s="2"/>
     </row>
     <row r="404" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A404" s="2"/>
+      <c r="A404" s="3">
+        <v>403</v>
+      </c>
       <c r="B404" s="2" t="s">
         <v>1781</v>
       </c>
@@ -32786,7 +33607,9 @@
       <c r="AD404" s="2"/>
     </row>
     <row r="405" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A405" s="2"/>
+      <c r="A405" s="3">
+        <v>404</v>
+      </c>
       <c r="B405" s="2" t="s">
         <v>1781</v>
       </c>
@@ -32846,7 +33669,9 @@
       <c r="AD405" s="2"/>
     </row>
     <row r="406" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A406" s="2"/>
+      <c r="A406" s="3">
+        <v>405</v>
+      </c>
       <c r="B406" s="2" t="s">
         <v>1781</v>
       </c>
@@ -32906,7 +33731,9 @@
       <c r="AD406" s="2"/>
     </row>
     <row r="407" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A407" s="2"/>
+      <c r="A407" s="3">
+        <v>406</v>
+      </c>
       <c r="B407" s="2" t="s">
         <v>1781</v>
       </c>
@@ -32974,7 +33801,9 @@
       <c r="AD407" s="2"/>
     </row>
     <row r="408" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A408" s="2"/>
+      <c r="A408" s="3">
+        <v>407</v>
+      </c>
       <c r="B408" s="2" t="s">
         <v>1781</v>
       </c>
@@ -33042,7 +33871,9 @@
       <c r="AD408" s="2"/>
     </row>
     <row r="409" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A409" s="2"/>
+      <c r="A409" s="3">
+        <v>408</v>
+      </c>
       <c r="B409" s="2" t="s">
         <v>1781</v>
       </c>
@@ -33110,7 +33941,9 @@
       <c r="AD409" s="2"/>
     </row>
     <row r="410" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A410" s="2"/>
+      <c r="A410" s="3">
+        <v>409</v>
+      </c>
       <c r="B410" s="2" t="s">
         <v>1781</v>
       </c>
@@ -33178,7 +34011,9 @@
       <c r="AD410" s="2"/>
     </row>
     <row r="411" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A411" s="2"/>
+      <c r="A411" s="3">
+        <v>410</v>
+      </c>
       <c r="B411" s="2" t="s">
         <v>1781</v>
       </c>
@@ -33246,7 +34081,9 @@
       <c r="AD411" s="2"/>
     </row>
     <row r="412" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A412" s="2"/>
+      <c r="A412" s="3">
+        <v>411</v>
+      </c>
       <c r="B412" s="2" t="s">
         <v>1781</v>
       </c>
@@ -33314,7 +34151,9 @@
       <c r="AD412" s="2"/>
     </row>
     <row r="413" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A413" s="2"/>
+      <c r="A413" s="3">
+        <v>412</v>
+      </c>
       <c r="B413" s="2" t="s">
         <v>1781</v>
       </c>
@@ -33382,7 +34221,9 @@
       <c r="AD413" s="2"/>
     </row>
     <row r="414" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A414" s="2"/>
+      <c r="A414" s="3">
+        <v>413</v>
+      </c>
       <c r="B414" s="2" t="s">
         <v>1781</v>
       </c>
@@ -33450,7 +34291,9 @@
       <c r="AD414" s="2"/>
     </row>
     <row r="415" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A415" s="2"/>
+      <c r="A415" s="3">
+        <v>414</v>
+      </c>
       <c r="B415" s="2" t="s">
         <v>1781</v>
       </c>
@@ -33518,7 +34361,9 @@
       <c r="AD415" s="2"/>
     </row>
     <row r="416" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A416" s="2"/>
+      <c r="A416" s="3">
+        <v>415</v>
+      </c>
       <c r="B416" s="2" t="s">
         <v>1781</v>
       </c>
@@ -33586,7 +34431,9 @@
       <c r="AD416" s="2"/>
     </row>
     <row r="417" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A417" s="2"/>
+      <c r="A417" s="3">
+        <v>416</v>
+      </c>
       <c r="B417" s="2" t="s">
         <v>1781</v>
       </c>
@@ -33654,7 +34501,9 @@
       <c r="AD417" s="2"/>
     </row>
     <row r="418" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A418" s="2"/>
+      <c r="A418" s="3">
+        <v>417</v>
+      </c>
       <c r="B418" s="2" t="s">
         <v>1781</v>
       </c>
@@ -33714,7 +34563,9 @@
       <c r="AD418" s="2"/>
     </row>
     <row r="419" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A419" s="2"/>
+      <c r="A419" s="3">
+        <v>418</v>
+      </c>
       <c r="B419" s="2" t="s">
         <v>1781</v>
       </c>
@@ -33774,7 +34625,9 @@
       <c r="AD419" s="2"/>
     </row>
     <row r="420" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A420" s="2"/>
+      <c r="A420" s="3">
+        <v>419</v>
+      </c>
       <c r="B420" s="2" t="s">
         <v>1781</v>
       </c>
@@ -33834,7 +34687,9 @@
       <c r="AD420" s="2"/>
     </row>
     <row r="421" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A421" s="2"/>
+      <c r="A421" s="3">
+        <v>420</v>
+      </c>
       <c r="B421" s="2" t="s">
         <v>1781</v>
       </c>
@@ -33894,7 +34749,9 @@
       <c r="AD421" s="2"/>
     </row>
     <row r="422" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A422" s="2"/>
+      <c r="A422" s="3">
+        <v>421</v>
+      </c>
       <c r="B422" s="2" t="s">
         <v>1781</v>
       </c>
@@ -33954,7 +34811,9 @@
       <c r="AD422" s="2"/>
     </row>
     <row r="423" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A423" s="2"/>
+      <c r="A423" s="3">
+        <v>422</v>
+      </c>
       <c r="B423" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34014,7 +34873,9 @@
       <c r="AD423" s="2"/>
     </row>
     <row r="424" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A424" s="2"/>
+      <c r="A424" s="3">
+        <v>423</v>
+      </c>
       <c r="B424" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34074,7 +34935,9 @@
       <c r="AD424" s="2"/>
     </row>
     <row r="425" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A425" s="2"/>
+      <c r="A425" s="3">
+        <v>424</v>
+      </c>
       <c r="B425" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34134,7 +34997,9 @@
       <c r="AD425" s="2"/>
     </row>
     <row r="426" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A426" s="2"/>
+      <c r="A426" s="3">
+        <v>425</v>
+      </c>
       <c r="B426" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34194,7 +35059,9 @@
       <c r="AD426" s="2"/>
     </row>
     <row r="427" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A427" s="2"/>
+      <c r="A427" s="3">
+        <v>426</v>
+      </c>
       <c r="B427" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34254,7 +35121,9 @@
       <c r="AD427" s="2"/>
     </row>
     <row r="428" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A428" s="2"/>
+      <c r="A428" s="3">
+        <v>427</v>
+      </c>
       <c r="B428" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34314,7 +35183,9 @@
       <c r="AD428" s="2"/>
     </row>
     <row r="429" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A429" s="2"/>
+      <c r="A429" s="3">
+        <v>428</v>
+      </c>
       <c r="B429" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34374,7 +35245,9 @@
       <c r="AD429" s="2"/>
     </row>
     <row r="430" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A430" s="2"/>
+      <c r="A430" s="3">
+        <v>429</v>
+      </c>
       <c r="B430" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34434,7 +35307,9 @@
       <c r="AD430" s="2"/>
     </row>
     <row r="431" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A431" s="2"/>
+      <c r="A431" s="3">
+        <v>430</v>
+      </c>
       <c r="B431" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34494,7 +35369,9 @@
       <c r="AD431" s="2"/>
     </row>
     <row r="432" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A432" s="2"/>
+      <c r="A432" s="3">
+        <v>431</v>
+      </c>
       <c r="B432" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34554,7 +35431,9 @@
       <c r="AD432" s="2"/>
     </row>
     <row r="433" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A433" s="2"/>
+      <c r="A433" s="3">
+        <v>432</v>
+      </c>
       <c r="B433" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34614,7 +35493,9 @@
       <c r="AD433" s="2"/>
     </row>
     <row r="434" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A434" s="2"/>
+      <c r="A434" s="3">
+        <v>433</v>
+      </c>
       <c r="B434" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34674,7 +35555,9 @@
       <c r="AD434" s="2"/>
     </row>
     <row r="435" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A435" s="2"/>
+      <c r="A435" s="3">
+        <v>434</v>
+      </c>
       <c r="B435" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34734,7 +35617,9 @@
       <c r="AD435" s="2"/>
     </row>
     <row r="436" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A436" s="2"/>
+      <c r="A436" s="3">
+        <v>435</v>
+      </c>
       <c r="B436" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34794,7 +35679,9 @@
       <c r="AD436" s="2"/>
     </row>
     <row r="437" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A437" s="2"/>
+      <c r="A437" s="3">
+        <v>436</v>
+      </c>
       <c r="B437" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34854,7 +35741,9 @@
       <c r="AD437" s="2"/>
     </row>
     <row r="438" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A438" s="2"/>
+      <c r="A438" s="3">
+        <v>437</v>
+      </c>
       <c r="B438" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34914,7 +35803,9 @@
       <c r="AD438" s="2"/>
     </row>
     <row r="439" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A439" s="2"/>
+      <c r="A439" s="3">
+        <v>438</v>
+      </c>
       <c r="B439" s="2" t="s">
         <v>1781</v>
       </c>
@@ -34974,7 +35865,9 @@
       <c r="AD439" s="2"/>
     </row>
     <row r="440" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A440" s="2"/>
+      <c r="A440" s="3">
+        <v>439</v>
+      </c>
       <c r="B440" s="2" t="s">
         <v>1781</v>
       </c>
@@ -35034,7 +35927,9 @@
       <c r="AD440" s="2"/>
     </row>
     <row r="441" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A441" s="2"/>
+      <c r="A441" s="3">
+        <v>440</v>
+      </c>
       <c r="B441" s="2" t="s">
         <v>1781</v>
       </c>
@@ -35094,7 +35989,9 @@
       <c r="AD441" s="2"/>
     </row>
     <row r="442" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A442" s="2"/>
+      <c r="A442" s="3">
+        <v>441</v>
+      </c>
       <c r="B442" s="2" t="s">
         <v>1781</v>
       </c>
@@ -35154,7 +36051,9 @@
       <c r="AD442" s="2"/>
     </row>
     <row r="443" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A443" s="2"/>
+      <c r="A443" s="3">
+        <v>442</v>
+      </c>
       <c r="B443" s="2" t="s">
         <v>1781</v>
       </c>
@@ -35214,7 +36113,9 @@
       <c r="AD443" s="2"/>
     </row>
     <row r="444" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A444" s="2"/>
+      <c r="A444" s="3">
+        <v>443</v>
+      </c>
       <c r="B444" s="2" t="s">
         <v>1781</v>
       </c>
@@ -35274,7 +36175,9 @@
       <c r="AD444" s="2"/>
     </row>
     <row r="445" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A445" s="2"/>
+      <c r="A445" s="3">
+        <v>444</v>
+      </c>
       <c r="B445" s="2" t="s">
         <v>1781</v>
       </c>
@@ -35334,7 +36237,9 @@
       <c r="AD445" s="2"/>
     </row>
     <row r="446" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A446" s="2"/>
+      <c r="A446" s="3">
+        <v>445</v>
+      </c>
       <c r="B446" s="2" t="s">
         <v>1781</v>
       </c>
@@ -35394,7 +36299,9 @@
       <c r="AD446" s="2"/>
     </row>
     <row r="447" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A447" s="2"/>
+      <c r="A447" s="3">
+        <v>446</v>
+      </c>
       <c r="B447" s="2" t="s">
         <v>1781</v>
       </c>
@@ -35454,7 +36361,9 @@
       <c r="AD447" s="2"/>
     </row>
     <row r="448" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A448" s="2"/>
+      <c r="A448" s="3">
+        <v>447</v>
+      </c>
       <c r="B448" s="2" t="s">
         <v>1781</v>
       </c>
@@ -35514,7 +36423,9 @@
       <c r="AD448" s="2"/>
     </row>
     <row r="449" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A449" s="2"/>
+      <c r="A449" s="3">
+        <v>448</v>
+      </c>
       <c r="B449" s="2" t="s">
         <v>1781</v>
       </c>
@@ -35574,7 +36485,9 @@
       <c r="AD449" s="2"/>
     </row>
     <row r="450" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A450" s="2"/>
+      <c r="A450" s="3">
+        <v>449</v>
+      </c>
       <c r="B450" s="2" t="s">
         <v>1781</v>
       </c>
@@ -35634,7 +36547,9 @@
       <c r="AD450" s="2"/>
     </row>
     <row r="451" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A451" s="2"/>
+      <c r="A451" s="3">
+        <v>450</v>
+      </c>
       <c r="B451" s="2" t="s">
         <v>1781</v>
       </c>
@@ -35694,7 +36609,9 @@
       <c r="AD451" s="2"/>
     </row>
     <row r="452" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A452" s="2"/>
+      <c r="A452" s="3">
+        <v>451</v>
+      </c>
       <c r="B452" s="2" t="s">
         <v>1781</v>
       </c>
@@ -35754,7 +36671,9 @@
       <c r="AD452" s="2"/>
     </row>
     <row r="453" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A453" s="2"/>
+      <c r="A453" s="3">
+        <v>452</v>
+      </c>
       <c r="B453" s="2" t="s">
         <v>30</v>
       </c>
@@ -35822,7 +36741,9 @@
       <c r="AD453" s="2"/>
     </row>
     <row r="454" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A454" s="2"/>
+      <c r="A454" s="3">
+        <v>453</v>
+      </c>
       <c r="B454" s="2" t="s">
         <v>30</v>
       </c>
@@ -35890,7 +36811,9 @@
       <c r="AD454" s="2"/>
     </row>
     <row r="455" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A455" s="2"/>
+      <c r="A455" s="3">
+        <v>454</v>
+      </c>
       <c r="B455" s="2" t="s">
         <v>30</v>
       </c>
@@ -35958,7 +36881,9 @@
       <c r="AD455" s="2"/>
     </row>
     <row r="456" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A456" s="2"/>
+      <c r="A456" s="3">
+        <v>455</v>
+      </c>
       <c r="B456" s="2" t="s">
         <v>2191</v>
       </c>
@@ -36012,7 +36937,9 @@
       <c r="AD456" s="2"/>
     </row>
     <row r="457" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A457" s="2"/>
+      <c r="A457" s="3">
+        <v>456</v>
+      </c>
       <c r="B457" s="2" t="s">
         <v>2194</v>
       </c>
@@ -36074,7 +37001,9 @@
       <c r="AD457" s="2"/>
     </row>
     <row r="458" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A458" s="2"/>
+      <c r="A458" s="3">
+        <v>457</v>
+      </c>
       <c r="B458" s="2" t="s">
         <v>2194</v>
       </c>
@@ -36136,7 +37065,9 @@
       <c r="AD458" s="2"/>
     </row>
     <row r="459" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A459" s="2"/>
+      <c r="A459" s="3">
+        <v>458</v>
+      </c>
       <c r="B459" s="2" t="s">
         <v>2205</v>
       </c>
@@ -36204,7 +37135,9 @@
       <c r="AD459" s="2"/>
     </row>
     <row r="460" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A460" s="2"/>
+      <c r="A460" s="3">
+        <v>459</v>
+      </c>
       <c r="B460" s="2" t="s">
         <v>1727</v>
       </c>
@@ -36270,7 +37203,9 @@
       <c r="AD460" s="2"/>
     </row>
     <row r="461" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A461" s="2"/>
+      <c r="A461" s="3">
+        <v>460</v>
+      </c>
       <c r="B461" s="2" t="s">
         <v>2218</v>
       </c>
@@ -36332,7 +37267,9 @@
       <c r="AD461" s="2"/>
     </row>
     <row r="462" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A462" s="2"/>
+      <c r="A462" s="3">
+        <v>461</v>
+      </c>
       <c r="B462" s="2" t="s">
         <v>500</v>
       </c>
@@ -36398,7 +37335,9 @@
       <c r="AD462" s="2"/>
     </row>
     <row r="463" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A463" s="2"/>
+      <c r="A463" s="3">
+        <v>462</v>
+      </c>
       <c r="B463" s="2" t="s">
         <v>2232</v>
       </c>
@@ -36468,7 +37407,9 @@
       <c r="AD463" s="2"/>
     </row>
     <row r="464" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A464" s="2"/>
+      <c r="A464" s="3">
+        <v>463</v>
+      </c>
       <c r="B464" s="2" t="s">
         <v>2232</v>
       </c>
@@ -36538,7 +37479,9 @@
       <c r="AD464" s="2"/>
     </row>
     <row r="465" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A465" s="2"/>
+      <c r="A465" s="3">
+        <v>464</v>
+      </c>
       <c r="B465" s="2" t="s">
         <v>2243</v>
       </c>
@@ -36604,7 +37547,9 @@
       <c r="AD465" s="2"/>
     </row>
     <row r="466" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A466" s="2"/>
+      <c r="A466" s="3">
+        <v>465</v>
+      </c>
       <c r="B466" s="2" t="s">
         <v>2243</v>
       </c>
@@ -36670,7 +37615,9 @@
       <c r="AD466" s="2"/>
     </row>
     <row r="467" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A467" s="2"/>
+      <c r="A467" s="3">
+        <v>466</v>
+      </c>
       <c r="B467" s="2" t="s">
         <v>2243</v>
       </c>
@@ -36736,7 +37683,9 @@
       <c r="AD467" s="2"/>
     </row>
     <row r="468" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A468" s="2"/>
+      <c r="A468" s="3">
+        <v>467</v>
+      </c>
       <c r="B468" s="2" t="s">
         <v>2243</v>
       </c>
@@ -36802,7 +37751,9 @@
       <c r="AD468" s="2"/>
     </row>
     <row r="469" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A469" s="2"/>
+      <c r="A469" s="3">
+        <v>468</v>
+      </c>
       <c r="B469" s="2" t="s">
         <v>2243</v>
       </c>
@@ -36868,7 +37819,9 @@
       <c r="AD469" s="2"/>
     </row>
     <row r="470" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A470" s="2"/>
+      <c r="A470" s="3">
+        <v>469</v>
+      </c>
       <c r="B470" s="2" t="s">
         <v>2267</v>
       </c>
@@ -36934,7 +37887,9 @@
       <c r="AD470" s="2"/>
     </row>
     <row r="471" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A471" s="2"/>
+      <c r="A471" s="3">
+        <v>470</v>
+      </c>
       <c r="B471" s="2" t="s">
         <v>2267</v>
       </c>
@@ -37000,7 +37955,9 @@
       <c r="AD471" s="2"/>
     </row>
     <row r="472" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A472" s="2"/>
+      <c r="A472" s="3">
+        <v>471</v>
+      </c>
       <c r="B472" s="2" t="s">
         <v>2267</v>
       </c>
@@ -37066,7 +38023,9 @@
       <c r="AD472" s="2"/>
     </row>
     <row r="473" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A473" s="2"/>
+      <c r="A473" s="3">
+        <v>472</v>
+      </c>
       <c r="B473" s="2" t="s">
         <v>500</v>
       </c>
@@ -37132,7 +38091,9 @@
       <c r="AD473" s="2"/>
     </row>
     <row r="474" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A474" s="2"/>
+      <c r="A474" s="3">
+        <v>473</v>
+      </c>
       <c r="B474" s="2" t="s">
         <v>500</v>
       </c>
@@ -37198,7 +38159,9 @@
       <c r="AD474" s="2"/>
     </row>
     <row r="475" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A475" s="2"/>
+      <c r="A475" s="3">
+        <v>474</v>
+      </c>
       <c r="B475" s="2" t="s">
         <v>2291</v>
       </c>
@@ -37264,7 +38227,9 @@
       <c r="AD475" s="2"/>
     </row>
     <row r="476" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A476" s="2"/>
+      <c r="A476" s="3">
+        <v>475</v>
+      </c>
       <c r="B476" s="2" t="s">
         <v>2297</v>
       </c>
@@ -37328,7 +38293,9 @@
       <c r="AD476" s="2"/>
     </row>
     <row r="477" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A477" s="2"/>
+      <c r="A477" s="3">
+        <v>476</v>
+      </c>
       <c r="B477" s="2" t="s">
         <v>1180</v>
       </c>
@@ -37388,7 +38355,9 @@
       <c r="AD477" s="2"/>
     </row>
     <row r="478" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A478" s="2"/>
+      <c r="A478" s="3">
+        <v>477</v>
+      </c>
       <c r="B478" s="2" t="s">
         <v>1304</v>
       </c>
@@ -37448,7 +38417,9 @@
       <c r="AD478" s="2"/>
     </row>
     <row r="479" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A479" s="2"/>
+      <c r="A479" s="3">
+        <v>478</v>
+      </c>
       <c r="B479" s="2" t="s">
         <v>2313</v>
       </c>
@@ -37508,7 +38479,9 @@
       <c r="AD479" s="2"/>
     </row>
     <row r="480" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A480" s="2"/>
+      <c r="A480" s="3">
+        <v>479</v>
+      </c>
       <c r="B480" s="2" t="s">
         <v>2319</v>
       </c>
@@ -37568,7 +38541,9 @@
       <c r="AD480" s="2"/>
     </row>
     <row r="481" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A481" s="2"/>
+      <c r="A481" s="3">
+        <v>480</v>
+      </c>
       <c r="B481" s="2" t="s">
         <v>778</v>
       </c>
@@ -37628,7 +38603,9 @@
       <c r="AD481" s="2"/>
     </row>
     <row r="482" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A482" s="2"/>
+      <c r="A482" s="3">
+        <v>481</v>
+      </c>
       <c r="B482" s="2" t="s">
         <v>2328</v>
       </c>
@@ -37688,7 +38665,9 @@
       <c r="AD482" s="2"/>
     </row>
     <row r="483" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A483" s="2"/>
+      <c r="A483" s="3">
+        <v>482</v>
+      </c>
       <c r="B483" s="2" t="s">
         <v>2334</v>
       </c>
@@ -37748,7 +38727,9 @@
       <c r="AD483" s="2"/>
     </row>
     <row r="484" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A484" s="2"/>
+      <c r="A484" s="3">
+        <v>483</v>
+      </c>
       <c r="B484" s="2" t="s">
         <v>579</v>
       </c>
@@ -37808,7 +38789,9 @@
       <c r="AD484" s="2"/>
     </row>
     <row r="485" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A485" s="2"/>
+      <c r="A485" s="3">
+        <v>484</v>
+      </c>
       <c r="B485" s="2" t="s">
         <v>2344</v>
       </c>
@@ -37868,7 +38851,9 @@
       <c r="AD485" s="2"/>
     </row>
     <row r="486" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A486" s="2"/>
+      <c r="A486" s="3">
+        <v>485</v>
+      </c>
       <c r="B486" s="2" t="s">
         <v>727</v>
       </c>
@@ -37932,7 +38917,9 @@
       <c r="AD486" s="2"/>
     </row>
     <row r="487" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A487" s="2"/>
+      <c r="A487" s="3">
+        <v>486</v>
+      </c>
       <c r="B487" s="2" t="s">
         <v>2355</v>
       </c>
@@ -37992,7 +38979,9 @@
       <c r="AD487" s="2"/>
     </row>
     <row r="488" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A488" s="2"/>
+      <c r="A488" s="3">
+        <v>487</v>
+      </c>
       <c r="B488" s="2" t="s">
         <v>2361</v>
       </c>
@@ -38056,7 +39045,9 @@
       <c r="AD488" s="2"/>
     </row>
     <row r="489" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A489" s="2"/>
+      <c r="A489" s="3">
+        <v>488</v>
+      </c>
       <c r="B489" s="2" t="s">
         <v>919</v>
       </c>
@@ -38120,7 +39111,9 @@
       <c r="AD489" s="2"/>
     </row>
     <row r="490" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A490" s="2"/>
+      <c r="A490" s="3">
+        <v>489</v>
+      </c>
       <c r="B490" s="2" t="s">
         <v>2370</v>
       </c>
@@ -38184,7 +39177,9 @@
       <c r="AD490" s="2"/>
     </row>
     <row r="491" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A491" s="2"/>
+      <c r="A491" s="3">
+        <v>490</v>
+      </c>
       <c r="B491" s="2" t="s">
         <v>2375</v>
       </c>
@@ -38244,7 +39239,9 @@
       <c r="AD491" s="2"/>
     </row>
     <row r="492" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A492" s="2"/>
+      <c r="A492" s="3">
+        <v>491</v>
+      </c>
       <c r="B492" s="2" t="s">
         <v>2375</v>
       </c>
@@ -38304,7 +39301,9 @@
       <c r="AD492" s="2"/>
     </row>
     <row r="493" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A493" s="2"/>
+      <c r="A493" s="3">
+        <v>492</v>
+      </c>
       <c r="B493" s="2" t="s">
         <v>2375</v>
       </c>
@@ -38368,7 +39367,9 @@
       <c r="AD493" s="2"/>
     </row>
     <row r="494" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A494" s="2"/>
+      <c r="A494" s="3">
+        <v>493</v>
+      </c>
       <c r="B494" s="2" t="s">
         <v>2375</v>
       </c>
@@ -38432,7 +39433,9 @@
       <c r="AD494" s="2"/>
     </row>
     <row r="495" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A495" s="2"/>
+      <c r="A495" s="3">
+        <v>494</v>
+      </c>
       <c r="B495" s="2" t="s">
         <v>2395</v>
       </c>
@@ -38492,7 +39495,9 @@
       <c r="AD495" s="2"/>
     </row>
     <row r="496" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A496" s="2"/>
+      <c r="A496" s="3">
+        <v>495</v>
+      </c>
       <c r="B496" s="2" t="s">
         <v>2399</v>
       </c>
@@ -38556,7 +39561,9 @@
       <c r="AD496" s="2"/>
     </row>
     <row r="497" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A497" s="2"/>
+      <c r="A497" s="3">
+        <v>496</v>
+      </c>
       <c r="B497" s="2" t="s">
         <v>2405</v>
       </c>
@@ -38620,7 +39627,9 @@
       <c r="AD497" s="2"/>
     </row>
     <row r="498" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A498" s="2"/>
+      <c r="A498" s="3">
+        <v>497</v>
+      </c>
       <c r="B498" s="2" t="s">
         <v>2405</v>
       </c>
@@ -38680,7 +39689,9 @@
       <c r="AD498" s="2"/>
     </row>
     <row r="499" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A499" s="2"/>
+      <c r="A499" s="3">
+        <v>498</v>
+      </c>
       <c r="B499" s="2" t="s">
         <v>2417</v>
       </c>
@@ -38740,7 +39751,9 @@
       <c r="AD499" s="2"/>
     </row>
     <row r="500" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A500" s="2"/>
+      <c r="A500" s="3">
+        <v>499</v>
+      </c>
       <c r="B500" s="2" t="s">
         <v>2421</v>
       </c>
@@ -38800,7 +39813,9 @@
       <c r="AD500" s="2"/>
     </row>
     <row r="501" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A501" s="2"/>
+      <c r="A501" s="3">
+        <v>500</v>
+      </c>
       <c r="B501" s="2" t="s">
         <v>2427</v>
       </c>
@@ -38860,7 +39875,9 @@
       <c r="AD501" s="2"/>
     </row>
     <row r="502" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A502" s="2"/>
+      <c r="A502" s="3">
+        <v>501</v>
+      </c>
       <c r="B502" s="2" t="s">
         <v>2432</v>
       </c>
@@ -38920,7 +39937,9 @@
       <c r="AD502" s="2"/>
     </row>
     <row r="503" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A503" s="2"/>
+      <c r="A503" s="3">
+        <v>502</v>
+      </c>
       <c r="B503" s="2" t="s">
         <v>30</v>
       </c>
@@ -38984,7 +40003,9 @@
       <c r="AD503" s="2"/>
     </row>
     <row r="504" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A504" s="2"/>
+      <c r="A504" s="3">
+        <v>503</v>
+      </c>
       <c r="B504" s="2" t="s">
         <v>30</v>
       </c>
@@ -39048,7 +40069,9 @@
       <c r="AD504" s="2"/>
     </row>
     <row r="505" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A505" s="2"/>
+      <c r="A505" s="3">
+        <v>504</v>
+      </c>
       <c r="B505" s="2" t="s">
         <v>30</v>
       </c>
@@ -39112,7 +40135,9 @@
       <c r="AD505" s="2"/>
     </row>
     <row r="506" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A506" s="2"/>
+      <c r="A506" s="3">
+        <v>505</v>
+      </c>
       <c r="B506" s="2" t="s">
         <v>2452</v>
       </c>
@@ -39176,7 +40201,9 @@
       <c r="AD506" s="2"/>
     </row>
     <row r="507" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A507" s="2"/>
+      <c r="A507" s="3">
+        <v>506</v>
+      </c>
       <c r="B507" s="2" t="s">
         <v>2460</v>
       </c>
@@ -39240,7 +40267,9 @@
       <c r="AD507" s="2"/>
     </row>
     <row r="508" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A508" s="2"/>
+      <c r="A508" s="3">
+        <v>507</v>
+      </c>
       <c r="B508" s="2" t="s">
         <v>2466</v>
       </c>
@@ -39304,7 +40333,9 @@
       <c r="AD508" s="2"/>
     </row>
     <row r="509" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A509" s="2"/>
+      <c r="A509" s="3">
+        <v>508</v>
+      </c>
       <c r="B509" s="2" t="s">
         <v>2472</v>
       </c>
@@ -39368,7 +40399,9 @@
       <c r="AD509" s="2"/>
     </row>
     <row r="510" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A510" s="2"/>
+      <c r="A510" s="3">
+        <v>509</v>
+      </c>
       <c r="B510" s="2" t="s">
         <v>2472</v>
       </c>
@@ -39432,7 +40465,9 @@
       <c r="AD510" s="2"/>
     </row>
     <row r="511" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A511" s="2"/>
+      <c r="A511" s="3">
+        <v>510</v>
+      </c>
       <c r="B511" s="2" t="s">
         <v>2472</v>
       </c>
@@ -39496,7 +40531,9 @@
       <c r="AD511" s="2"/>
     </row>
     <row r="512" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A512" s="2"/>
+      <c r="A512" s="3">
+        <v>511</v>
+      </c>
       <c r="B512" s="2" t="s">
         <v>2472</v>
       </c>
@@ -39560,7 +40597,9 @@
       <c r="AD512" s="2"/>
     </row>
     <row r="513" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A513" s="2"/>
+      <c r="A513" s="3">
+        <v>512</v>
+      </c>
       <c r="B513" s="2" t="s">
         <v>1385</v>
       </c>
@@ -39624,7 +40663,9 @@
       <c r="AD513" s="2"/>
     </row>
     <row r="514" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A514" s="2"/>
+      <c r="A514" s="3">
+        <v>513</v>
+      </c>
       <c r="B514" s="2" t="s">
         <v>579</v>
       </c>
@@ -39696,7 +40737,9 @@
       <c r="AD514" s="2"/>
     </row>
     <row r="515" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A515" s="2"/>
+      <c r="A515" s="3">
+        <v>514</v>
+      </c>
       <c r="B515" s="2" t="s">
         <v>579</v>
       </c>
@@ -39768,7 +40811,9 @@
       <c r="AD515" s="2"/>
     </row>
     <row r="516" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A516" s="2"/>
+      <c r="A516" s="3">
+        <v>515</v>
+      </c>
       <c r="B516" s="2" t="s">
         <v>2507</v>
       </c>
@@ -39836,7 +40881,9 @@
       <c r="AD516" s="2"/>
     </row>
     <row r="517" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A517" s="2"/>
+      <c r="A517" s="3">
+        <v>516</v>
+      </c>
       <c r="B517" s="2" t="s">
         <v>2514</v>
       </c>
@@ -39908,7 +40955,9 @@
       <c r="AD517" s="2"/>
     </row>
     <row r="518" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A518" s="2"/>
+      <c r="A518" s="3">
+        <v>517</v>
+      </c>
       <c r="B518" s="2" t="s">
         <v>2514</v>
       </c>
@@ -39980,7 +41029,9 @@
       <c r="AD518" s="2"/>
     </row>
     <row r="519" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A519" s="2"/>
+      <c r="A519" s="3">
+        <v>518</v>
+      </c>
       <c r="B519" s="2" t="s">
         <v>2514</v>
       </c>
@@ -40052,7 +41103,9 @@
       <c r="AD519" s="2"/>
     </row>
     <row r="520" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A520" s="2"/>
+      <c r="A520" s="3">
+        <v>519</v>
+      </c>
       <c r="B520" s="2" t="s">
         <v>2514</v>
       </c>
@@ -40124,7 +41177,9 @@
       <c r="AD520" s="2"/>
     </row>
     <row r="521" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A521" s="2"/>
+      <c r="A521" s="3">
+        <v>520</v>
+      </c>
       <c r="B521" s="2" t="s">
         <v>2514</v>
       </c>
@@ -40196,7 +41251,9 @@
       <c r="AD521" s="2"/>
     </row>
     <row r="522" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A522" s="2"/>
+      <c r="A522" s="3">
+        <v>521</v>
+      </c>
       <c r="B522" s="2" t="s">
         <v>2514</v>
       </c>
@@ -40268,7 +41325,9 @@
       <c r="AD522" s="2"/>
     </row>
     <row r="523" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A523" s="2"/>
+      <c r="A523" s="3">
+        <v>522</v>
+      </c>
       <c r="B523" s="2" t="s">
         <v>2514</v>
       </c>
@@ -40340,7 +41399,9 @@
       <c r="AD523" s="2"/>
     </row>
     <row r="524" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A524" s="2"/>
+      <c r="A524" s="3">
+        <v>523</v>
+      </c>
       <c r="B524" s="2" t="s">
         <v>2554</v>
       </c>
@@ -40410,7 +41471,9 @@
       <c r="AD524" s="2"/>
     </row>
     <row r="525" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A525" s="2"/>
+      <c r="A525" s="3">
+        <v>524</v>
+      </c>
       <c r="B525" s="2" t="s">
         <v>2565</v>
       </c>
@@ -40480,7 +41543,9 @@
       <c r="AD525" s="2"/>
     </row>
     <row r="526" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A526" s="2"/>
+      <c r="A526" s="3">
+        <v>525</v>
+      </c>
       <c r="B526" s="2" t="s">
         <v>2573</v>
       </c>
@@ -40550,7 +41615,9 @@
       <c r="AD526" s="2"/>
     </row>
     <row r="527" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A527" s="2"/>
+      <c r="A527" s="3">
+        <v>526</v>
+      </c>
       <c r="B527" s="2" t="s">
         <v>2579</v>
       </c>
@@ -40620,7 +41687,9 @@
       <c r="AD527" s="2"/>
     </row>
     <row r="528" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A528" s="2"/>
+      <c r="A528" s="3">
+        <v>527</v>
+      </c>
       <c r="B528" s="2" t="s">
         <v>2585</v>
       </c>
@@ -40690,7 +41759,9 @@
       <c r="AD528" s="2"/>
     </row>
     <row r="529" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A529" s="2"/>
+      <c r="A529" s="3">
+        <v>528</v>
+      </c>
       <c r="B529" s="2" t="s">
         <v>2593</v>
       </c>
@@ -40760,7 +41831,9 @@
       <c r="AD529" s="2"/>
     </row>
     <row r="530" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A530" s="2"/>
+      <c r="A530" s="3">
+        <v>529</v>
+      </c>
       <c r="B530" s="2" t="s">
         <v>2599</v>
       </c>
@@ -40830,7 +41903,9 @@
       <c r="AD530" s="2"/>
     </row>
     <row r="531" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A531" s="2"/>
+      <c r="A531" s="3">
+        <v>530</v>
+      </c>
       <c r="B531" s="2" t="s">
         <v>2603</v>
       </c>
@@ -40900,7 +41975,9 @@
       <c r="AD531" s="2"/>
     </row>
     <row r="532" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A532" s="2"/>
+      <c r="A532" s="3">
+        <v>531</v>
+      </c>
       <c r="B532" s="2" t="s">
         <v>2610</v>
       </c>
@@ -40970,7 +42047,9 @@
       <c r="AD532" s="2"/>
     </row>
     <row r="533" spans="1:30" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A533" s="2"/>
+      <c r="A533" s="3">
+        <v>532</v>
+      </c>
       <c r="B533" s="2" t="s">
         <v>2615</v>
       </c>
@@ -41040,7 +42119,9 @@
       <c r="AD533" s="2"/>
     </row>
     <row r="534" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A534" s="2"/>
+      <c r="A534" s="3">
+        <v>533</v>
+      </c>
       <c r="B534" s="2" t="s">
         <v>1505</v>
       </c>
@@ -41110,7 +42191,9 @@
       <c r="AD534" s="2"/>
     </row>
     <row r="535" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A535" s="2"/>
+      <c r="A535" s="3">
+        <v>534</v>
+      </c>
       <c r="B535" s="2" t="s">
         <v>69</v>
       </c>
@@ -41180,7 +42263,9 @@
       <c r="AD535" s="2"/>
     </row>
     <row r="536" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A536" s="2"/>
+      <c r="A536" s="3">
+        <v>535</v>
+      </c>
       <c r="B536" s="2" t="s">
         <v>2638</v>
       </c>
@@ -41250,7 +42335,9 @@
       <c r="AD536" s="2"/>
     </row>
     <row r="537" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A537" s="2"/>
+      <c r="A537" s="3">
+        <v>536</v>
+      </c>
       <c r="B537" s="2" t="s">
         <v>2638</v>
       </c>
@@ -41320,49 +42407,55 @@
       <c r="AD537" s="2"/>
     </row>
     <row r="538" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A538" s="2"/>
-      <c r="B538" s="2" t="s">
+      <c r="A538" s="3" t="s">
+        <v>2741</v>
+      </c>
+      <c r="B538" s="3" t="s">
         <v>2472</v>
       </c>
-      <c r="C538" s="2" t="s">
+      <c r="C538" s="3" t="s">
         <v>2472</v>
       </c>
-      <c r="D538" s="2" t="s">
+      <c r="D538" s="3" t="s">
         <v>2650</v>
       </c>
-      <c r="E538" s="2" t="s">
+      <c r="E538" s="3" t="s">
         <v>1739</v>
       </c>
-      <c r="F538" s="2" t="s">
+      <c r="F538" s="3" t="s">
         <v>1740</v>
       </c>
-      <c r="G538" s="2" t="s">
+      <c r="G538" s="3" t="s">
         <v>1478</v>
       </c>
-      <c r="H538" s="2" t="s">
+      <c r="H538" s="3" t="s">
         <v>1478</v>
       </c>
-      <c r="I538" s="2" t="s">
+      <c r="I538" s="3" t="s">
         <v>2651</v>
       </c>
-      <c r="J538" s="2" t="s">
+      <c r="J538" s="3" t="s">
+        <v>2742</v>
+      </c>
+      <c r="K538" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L538" s="3" t="s">
+        <v>2743</v>
+      </c>
+      <c r="M538" s="3" t="s">
         <v>2652</v>
       </c>
-      <c r="K538" s="2"/>
-      <c r="L538" s="2" t="s">
-        <v>2653</v>
-      </c>
-      <c r="M538" s="2" t="s">
-        <v>2654</v>
-      </c>
-      <c r="N538" s="2"/>
-      <c r="O538" s="2" t="s">
+      <c r="N538" s="3">
+        <v>1</v>
+      </c>
+      <c r="O538" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="P538" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q538" s="2" t="s">
+      <c r="P538" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q538" s="3" t="s">
         <v>2212</v>
       </c>
       <c r="R538" s="2"/>
@@ -41390,7 +42483,9 @@
       <c r="AD538" s="2"/>
     </row>
     <row r="539" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A539" s="2"/>
+      <c r="A539" s="3">
+        <v>538</v>
+      </c>
       <c r="B539" s="2" t="s">
         <v>1418</v>
       </c>
@@ -41398,7 +42493,7 @@
         <v>1418</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>2655</v>
+        <v>2653</v>
       </c>
       <c r="E539" s="2" t="s">
         <v>1421</v>
@@ -41413,17 +42508,17 @@
         <v>1122</v>
       </c>
       <c r="I539" s="2" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
       <c r="J539" s="2" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="K539" s="2"/>
       <c r="L539" s="2" t="s">
-        <v>2658</v>
+        <v>2656</v>
       </c>
       <c r="M539" s="2" t="s">
-        <v>2659</v>
+        <v>2657</v>
       </c>
       <c r="N539" s="2"/>
       <c r="O539" s="2" t="s">
@@ -41460,15 +42555,17 @@
       <c r="AD539" s="2"/>
     </row>
     <row r="540" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A540" s="2"/>
+      <c r="A540" s="3">
+        <v>539</v>
+      </c>
       <c r="B540" s="2" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="D540" s="2" t="s">
-        <v>2661</v>
+        <v>2659</v>
       </c>
       <c r="E540" s="2" t="s">
         <v>1553</v>
@@ -41483,17 +42580,17 @@
         <v>891</v>
       </c>
       <c r="I540" s="2" t="s">
-        <v>2662</v>
+        <v>2660</v>
       </c>
       <c r="J540" s="2" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="K540" s="2"/>
       <c r="L540" s="2" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
       <c r="M540" s="2" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="N540" s="2"/>
       <c r="O540" s="2" t="s">
@@ -41530,15 +42627,17 @@
       <c r="AD540" s="2"/>
     </row>
     <row r="541" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A541" s="2"/>
+      <c r="A541" s="3">
+        <v>540</v>
+      </c>
       <c r="B541" s="2" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="D541" s="2" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
       <c r="E541" s="2" t="s">
         <v>1553</v>
@@ -41553,17 +42652,17 @@
         <v>2219</v>
       </c>
       <c r="I541" s="2" t="s">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="J541" s="2" t="s">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="K541" s="2"/>
       <c r="L541" s="2" t="s">
-        <v>2669</v>
+        <v>2667</v>
       </c>
       <c r="M541" s="2" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="N541" s="2"/>
       <c r="O541" s="2" t="s">
@@ -41600,15 +42699,17 @@
       <c r="AD541" s="2"/>
     </row>
     <row r="542" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A542" s="2"/>
+      <c r="A542" s="3">
+        <v>541</v>
+      </c>
       <c r="B542" s="2" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
       <c r="D542" s="2" t="s">
-        <v>2672</v>
+        <v>2670</v>
       </c>
       <c r="E542" s="2"/>
       <c r="F542" s="2"/>
@@ -41666,49 +42767,55 @@
       <c r="AD542" s="2"/>
     </row>
     <row r="543" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A543" s="2"/>
-      <c r="B543" s="2" t="s">
+      <c r="A543" s="3" t="s">
+        <v>2738</v>
+      </c>
+      <c r="B543" s="3" t="s">
+        <v>2671</v>
+      </c>
+      <c r="C543" s="3" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D543" s="3" t="s">
+        <v>2672</v>
+      </c>
+      <c r="E543" s="3" t="s">
         <v>2673</v>
       </c>
-      <c r="C543" s="2" t="s">
-        <v>2673</v>
-      </c>
-      <c r="D543" s="2" t="s">
+      <c r="F543" s="3" t="s">
         <v>2674</v>
       </c>
-      <c r="E543" s="2" t="s">
+      <c r="G543" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H543" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I543" s="3" t="s">
         <v>2675</v>
       </c>
-      <c r="F543" s="2" t="s">
+      <c r="J543" s="3" t="s">
+        <v>2739</v>
+      </c>
+      <c r="K543" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L543" s="3" t="s">
+        <v>2740</v>
+      </c>
+      <c r="M543" s="3" t="s">
         <v>2676</v>
       </c>
-      <c r="G543" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H543" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I543" s="2" t="s">
-        <v>2677</v>
-      </c>
-      <c r="J543" s="2" t="s">
-        <v>2678</v>
-      </c>
-      <c r="K543" s="2"/>
-      <c r="L543" s="2" t="s">
-        <v>2679</v>
-      </c>
-      <c r="M543" s="2" t="s">
-        <v>2680</v>
-      </c>
-      <c r="N543" s="2"/>
-      <c r="O543" s="2" t="s">
+      <c r="N543" s="3">
+        <v>1</v>
+      </c>
+      <c r="O543" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="P543" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q543" s="2" t="s">
+      <c r="P543" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q543" s="3" t="s">
         <v>2212</v>
       </c>
       <c r="R543" s="2"/>
@@ -41736,40 +42843,42 @@
       <c r="AD543" s="2"/>
     </row>
     <row r="544" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A544" s="2"/>
+      <c r="A544" s="3">
+        <v>543</v>
+      </c>
       <c r="B544" s="2" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="D544" s="2" t="s">
-        <v>2682</v>
+        <v>2678</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>2683</v>
+        <v>2679</v>
       </c>
       <c r="F544" s="2" t="s">
-        <v>2684</v>
+        <v>2680</v>
       </c>
       <c r="G544" s="2" t="s">
         <v>62</v>
       </c>
       <c r="H544" s="2" t="s">
-        <v>2685</v>
+        <v>2681</v>
       </c>
       <c r="I544" s="2" t="s">
-        <v>2686</v>
+        <v>2682</v>
       </c>
       <c r="J544" s="2" t="s">
-        <v>2687</v>
+        <v>2683</v>
       </c>
       <c r="K544" s="2"/>
       <c r="L544" s="2" t="s">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="M544" s="2" t="s">
-        <v>2689</v>
+        <v>2685</v>
       </c>
       <c r="N544" s="2"/>
       <c r="O544" s="2" t="s">
@@ -41806,40 +42915,42 @@
       <c r="AD544" s="2"/>
     </row>
     <row r="545" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A545" s="2"/>
+      <c r="A545" s="3">
+        <v>544</v>
+      </c>
       <c r="B545" s="2" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="D545" s="2" t="s">
-        <v>2690</v>
+        <v>2686</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>2683</v>
+        <v>2679</v>
       </c>
       <c r="F545" s="2" t="s">
-        <v>2691</v>
+        <v>2687</v>
       </c>
       <c r="G545" s="2" t="s">
         <v>62</v>
       </c>
       <c r="H545" s="2" t="s">
-        <v>2685</v>
+        <v>2681</v>
       </c>
       <c r="I545" s="2" t="s">
-        <v>2692</v>
+        <v>2688</v>
       </c>
       <c r="J545" s="2" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
       <c r="K545" s="2"/>
       <c r="L545" s="2" t="s">
-        <v>2694</v>
+        <v>2690</v>
       </c>
       <c r="M545" s="2" t="s">
-        <v>2689</v>
+        <v>2685</v>
       </c>
       <c r="N545" s="2"/>
       <c r="O545" s="2" t="s">
@@ -41876,40 +42987,42 @@
       <c r="AD545" s="2"/>
     </row>
     <row r="546" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A546" s="2"/>
+      <c r="A546" s="3">
+        <v>545</v>
+      </c>
       <c r="B546" s="2" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="D546" s="2" t="s">
-        <v>2695</v>
+        <v>2691</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>2683</v>
+        <v>2679</v>
       </c>
       <c r="F546" s="2" t="s">
-        <v>2696</v>
+        <v>2692</v>
       </c>
       <c r="G546" s="2" t="s">
         <v>62</v>
       </c>
       <c r="H546" s="2" t="s">
-        <v>2685</v>
+        <v>2681</v>
       </c>
       <c r="I546" s="2" t="s">
-        <v>2697</v>
+        <v>2693</v>
       </c>
       <c r="J546" s="2" t="s">
-        <v>2698</v>
+        <v>2694</v>
       </c>
       <c r="K546" s="2"/>
       <c r="L546" s="2" t="s">
-        <v>2699</v>
+        <v>2695</v>
       </c>
       <c r="M546" s="2" t="s">
-        <v>2689</v>
+        <v>2685</v>
       </c>
       <c r="N546" s="2"/>
       <c r="O546" s="2" t="s">
@@ -41946,49 +43059,55 @@
       <c r="AD546" s="2"/>
     </row>
     <row r="547" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A547" s="2"/>
-      <c r="B547" s="2" t="s">
+      <c r="A547" s="3" t="s">
+        <v>2735</v>
+      </c>
+      <c r="B547" s="3" t="s">
         <v>2243</v>
       </c>
-      <c r="C547" s="2" t="s">
+      <c r="C547" s="3" t="s">
         <v>2243</v>
       </c>
-      <c r="D547" s="2" t="s">
+      <c r="D547" s="3" t="s">
+        <v>2696</v>
+      </c>
+      <c r="E547" s="3" t="s">
+        <v>2697</v>
+      </c>
+      <c r="F547" s="3" t="s">
+        <v>2698</v>
+      </c>
+      <c r="G547" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="H547" s="3" t="s">
+        <v>2699</v>
+      </c>
+      <c r="I547" s="3" t="s">
         <v>2700</v>
       </c>
-      <c r="E547" s="2" t="s">
+      <c r="J547" s="3" t="s">
+        <v>2736</v>
+      </c>
+      <c r="K547" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L547" s="3" t="s">
+        <v>2737</v>
+      </c>
+      <c r="M547" s="3" t="s">
         <v>2701</v>
       </c>
-      <c r="F547" s="2" t="s">
-        <v>2702</v>
-      </c>
-      <c r="G547" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="H547" s="2" t="s">
-        <v>2703</v>
-      </c>
-      <c r="I547" s="2" t="s">
-        <v>2704</v>
-      </c>
-      <c r="J547" s="2" t="s">
-        <v>2705</v>
-      </c>
-      <c r="K547" s="2"/>
-      <c r="L547" s="2" t="s">
-        <v>2706</v>
-      </c>
-      <c r="M547" s="2" t="s">
-        <v>2707</v>
-      </c>
-      <c r="N547" s="2"/>
-      <c r="O547" s="2" t="s">
+      <c r="N547" s="3">
+        <v>1</v>
+      </c>
+      <c r="O547" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="P547" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q547" s="2" t="s">
+      <c r="P547" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q547" s="3" t="s">
         <v>2212</v>
       </c>
       <c r="R547" s="2"/>
@@ -42016,7 +43135,9 @@
       <c r="AD547" s="2"/>
     </row>
     <row r="548" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A548" s="2"/>
+      <c r="A548" s="3">
+        <v>547</v>
+      </c>
       <c r="B548" s="2" t="s">
         <v>2243</v>
       </c>
@@ -42024,13 +43145,13 @@
         <v>2243</v>
       </c>
       <c r="D548" s="2" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>2709</v>
+        <v>2703</v>
       </c>
       <c r="F548" s="2" t="s">
-        <v>2710</v>
+        <v>2704</v>
       </c>
       <c r="G548" s="2" t="s">
         <v>62</v>
@@ -42039,14 +43160,14 @@
         <v>62</v>
       </c>
       <c r="I548" s="2" t="s">
-        <v>2711</v>
+        <v>2705</v>
       </c>
       <c r="J548" s="2" t="s">
-        <v>2712</v>
+        <v>2706</v>
       </c>
       <c r="K548" s="2"/>
       <c r="L548" s="2" t="s">
-        <v>2713</v>
+        <v>2707</v>
       </c>
       <c r="M548" s="2" t="s">
         <v>279</v>
@@ -42086,12 +43207,14 @@
       <c r="AD548" s="2"/>
     </row>
     <row r="549" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A549" s="2"/>
+      <c r="A549" s="3">
+        <v>548</v>
+      </c>
       <c r="B549" s="2" t="s">
-        <v>2714</v>
+        <v>2708</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>2714</v>
+        <v>2708</v>
       </c>
       <c r="D549" s="2" t="s">
         <v>2650</v>
@@ -42109,17 +43232,17 @@
         <v>1478</v>
       </c>
       <c r="I549" s="2" t="s">
-        <v>2715</v>
+        <v>2709</v>
       </c>
       <c r="J549" s="2" t="s">
-        <v>2716</v>
+        <v>2710</v>
       </c>
       <c r="K549" s="2"/>
       <c r="L549" s="2" t="s">
         <v>1748</v>
       </c>
       <c r="M549" s="2" t="s">
-        <v>2717</v>
+        <v>2711</v>
       </c>
       <c r="N549" s="2"/>
       <c r="O549" s="2" t="s">
@@ -42156,15 +43279,17 @@
       <c r="AD549" s="2"/>
     </row>
     <row r="550" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A550" s="2"/>
+      <c r="A550" s="3">
+        <v>549</v>
+      </c>
       <c r="B550" s="2" t="s">
-        <v>2714</v>
+        <v>2708</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>2714</v>
+        <v>2708</v>
       </c>
       <c r="D550" s="2" t="s">
-        <v>2718</v>
+        <v>2712</v>
       </c>
       <c r="E550" s="2" t="s">
         <v>1739</v>
@@ -42179,17 +43304,17 @@
         <v>2646</v>
       </c>
       <c r="I550" s="2" t="s">
-        <v>2719</v>
+        <v>2713</v>
       </c>
       <c r="J550" s="2" t="s">
-        <v>2720</v>
+        <v>2714</v>
       </c>
       <c r="K550" s="2"/>
       <c r="L550" s="2" t="s">
-        <v>2721</v>
+        <v>2715</v>
       </c>
       <c r="M550" s="2" t="s">
-        <v>2717</v>
+        <v>2711</v>
       </c>
       <c r="N550" s="2"/>
       <c r="O550" s="2" t="s">
@@ -42226,7 +43351,9 @@
       <c r="AD550" s="2"/>
     </row>
     <row r="551" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A551" s="2"/>
+      <c r="A551" s="3">
+        <v>550</v>
+      </c>
       <c r="B551" s="2" t="s">
         <v>1428</v>
       </c>
@@ -42234,13 +43361,13 @@
         <v>1428</v>
       </c>
       <c r="D551" s="2" t="s">
-        <v>2722</v>
+        <v>2716</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>2723</v>
+        <v>2717</v>
       </c>
       <c r="F551" s="2" t="s">
-        <v>2724</v>
+        <v>2718</v>
       </c>
       <c r="G551" s="2" t="s">
         <v>62</v>
@@ -42249,17 +43376,17 @@
         <v>1364</v>
       </c>
       <c r="I551" s="2" t="s">
-        <v>2725</v>
+        <v>2719</v>
       </c>
       <c r="J551" s="2" t="s">
-        <v>2726</v>
+        <v>2720</v>
       </c>
       <c r="K551" s="2"/>
       <c r="L551" s="2" t="s">
-        <v>2727</v>
+        <v>2721</v>
       </c>
       <c r="M551" s="2" t="s">
-        <v>2728</v>
+        <v>2722</v>
       </c>
       <c r="N551" s="2"/>
       <c r="O551" s="2" t="s">
@@ -42296,7 +43423,9 @@
       <c r="AD551" s="2"/>
     </row>
     <row r="552" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A552" s="2"/>
+      <c r="A552" s="3">
+        <v>551</v>
+      </c>
       <c r="B552" s="2" t="s">
         <v>1428</v>
       </c>
@@ -42304,13 +43433,13 @@
         <v>1428</v>
       </c>
       <c r="D552" s="2" t="s">
-        <v>2729</v>
+        <v>2723</v>
       </c>
       <c r="E552" s="2" t="s">
-        <v>2730</v>
+        <v>2724</v>
       </c>
       <c r="F552" s="2" t="s">
-        <v>2731</v>
+        <v>2725</v>
       </c>
       <c r="G552" s="2" t="s">
         <v>62</v>
@@ -42319,17 +43448,17 @@
         <v>100</v>
       </c>
       <c r="I552" s="2" t="s">
-        <v>2732</v>
+        <v>2726</v>
       </c>
       <c r="J552" s="2" t="s">
-        <v>2733</v>
+        <v>2727</v>
       </c>
       <c r="K552" s="2"/>
       <c r="L552" s="2" t="s">
-        <v>2734</v>
+        <v>2728</v>
       </c>
       <c r="M552" s="2" t="s">
-        <v>2735</v>
+        <v>2729</v>
       </c>
       <c r="N552" s="2"/>
       <c r="O552" s="2" t="s">
@@ -42366,7 +43495,9 @@
       <c r="AD552" s="2"/>
     </row>
     <row r="553" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A553" s="2"/>
+      <c r="A553" s="3">
+        <v>552</v>
+      </c>
       <c r="B553" s="2" t="s">
         <v>1428</v>
       </c>
@@ -42374,13 +43505,13 @@
         <v>1428</v>
       </c>
       <c r="D553" s="2" t="s">
-        <v>2736</v>
+        <v>2730</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>2730</v>
+        <v>2724</v>
       </c>
       <c r="F553" s="2" t="s">
-        <v>2731</v>
+        <v>2725</v>
       </c>
       <c r="G553" s="2" t="s">
         <v>257</v>
@@ -42389,17 +43520,17 @@
         <v>372</v>
       </c>
       <c r="I553" s="2" t="s">
-        <v>2737</v>
+        <v>2731</v>
       </c>
       <c r="J553" s="2" t="s">
-        <v>2738</v>
+        <v>2732</v>
       </c>
       <c r="K553" s="2"/>
       <c r="L553" s="2" t="s">
-        <v>2739</v>
+        <v>2733</v>
       </c>
       <c r="M553" s="2" t="s">
-        <v>2740</v>
+        <v>2734</v>
       </c>
       <c r="N553" s="2"/>
       <c r="O553" s="2" t="s">
@@ -42504,8 +43635,6 @@
     <filterColumn colId="18">
       <filters>
         <filter val="true-&gt;8001"/>
-        <filter val="true-&gt;待定-&gt;影响其它"/>
-        <filter val="true-&gt;待定-&gt;影响其它信号"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -42612,7 +43741,9 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="15" customHeight="true">
-      <c r="A2" s="2"/>
+      <c r="A2" s="3">
+        <v>533</v>
+      </c>
       <c r="B2" s="2" t="s">
         <v>1505</v>
       </c>
@@ -42686,7 +43817,9 @@
       <c r="AD2" s="2"/>
     </row>
     <row r="3" spans="1:30" ht="15" customHeight="true">
-      <c r="A3" s="2"/>
+      <c r="A3" s="3">
+        <v>534</v>
+      </c>
       <c r="B3" s="2" t="s">
         <v>69</v>
       </c>
@@ -42760,7 +43893,9 @@
       <c r="AD3" s="2"/>
     </row>
     <row r="4" spans="1:30" ht="15" customHeight="true">
-      <c r="A4" s="2"/>
+      <c r="A4" s="3">
+        <v>535</v>
+      </c>
       <c r="B4" s="2" t="s">
         <v>2638</v>
       </c>
@@ -42834,7 +43969,9 @@
       <c r="AD4" s="2"/>
     </row>
     <row r="5" spans="1:30" ht="15" customHeight="true">
-      <c r="A5" s="2"/>
+      <c r="A5" s="3">
+        <v>536</v>
+      </c>
       <c r="B5" s="2" t="s">
         <v>2638</v>
       </c>
@@ -42908,58 +44045,60 @@
       <c r="AD5" s="2"/>
     </row>
     <row r="6" spans="1:30" ht="15" customHeight="true">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="3" t="s">
+        <v>2741</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>2472</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>2472</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>2650</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>1739</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>1740</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>1478</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>1478</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>2651</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="3" t="s">
+        <v>2742</v>
+      </c>
+      <c r="K6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>2743</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>2652</v>
       </c>
-      <c r="K6" s="2" t="b">
+      <c r="N6" s="3">
         <v>1</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>2653</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>2654</v>
-      </c>
-      <c r="N6" s="2">
-        <v>1</v>
-      </c>
-      <c r="O6" s="2" t="s">
+      <c r="O6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q6" s="2" t="s">
+      <c r="P6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q6" s="3" t="s">
         <v>2212</v>
       </c>
       <c r="R6" s="2"/>
       <c r="S6" s="2" t="s">
-        <v>2741</v>
+        <v>2629</v>
       </c>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -42982,7 +44121,9 @@
       <c r="AD6" s="2"/>
     </row>
     <row r="7" spans="1:30" ht="15" customHeight="true">
-      <c r="A7" s="2"/>
+      <c r="A7" s="3">
+        <v>538</v>
+      </c>
       <c r="B7" s="2" t="s">
         <v>1418</v>
       </c>
@@ -42990,7 +44131,7 @@
         <v>1418</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>2655</v>
+        <v>2653</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>1421</v>
@@ -43005,19 +44146,19 @@
         <v>1122</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>2658</v>
+        <v>2656</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>2659</v>
+        <v>2657</v>
       </c>
       <c r="N7" s="2">
         <v>1</v>
@@ -43056,15 +44197,17 @@
       <c r="AD7" s="2"/>
     </row>
     <row r="8" spans="1:30" ht="15" customHeight="true">
-      <c r="A8" s="2"/>
+      <c r="A8" s="3">
+        <v>539</v>
+      </c>
       <c r="B8" s="2" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>2661</v>
+        <v>2659</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>1553</v>
@@ -43079,19 +44222,19 @@
         <v>891</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>2662</v>
+        <v>2660</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="K8" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="N8" s="2">
         <v>1</v>
@@ -43130,15 +44273,17 @@
       <c r="AD8" s="2"/>
     </row>
     <row r="9" spans="1:30" ht="15" customHeight="true">
-      <c r="A9" s="2"/>
+      <c r="A9" s="3">
+        <v>540</v>
+      </c>
       <c r="B9" s="2" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>1553</v>
@@ -43153,19 +44298,19 @@
         <v>2219</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="K9" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>2669</v>
+        <v>2667</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="N9" s="2">
         <v>1</v>
@@ -43204,15 +44349,17 @@
       <c r="AD9" s="2"/>
     </row>
     <row r="10" spans="1:30" ht="15" customHeight="true">
-      <c r="A10" s="2"/>
+      <c r="A10" s="3">
+        <v>541</v>
+      </c>
       <c r="B10" s="2" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>2672</v>
+        <v>2670</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -43274,53 +44421,55 @@
       <c r="AD10" s="2"/>
     </row>
     <row r="11" spans="1:30" ht="15" customHeight="true">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="3" t="s">
+        <v>2738</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>2671</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>2672</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>2673</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>2673</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>2674</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="G11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>2675</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="J11" s="3" t="s">
+        <v>2739</v>
+      </c>
+      <c r="K11" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>2740</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>2676</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>2677</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>2678</v>
-      </c>
-      <c r="K11" s="2" t="b">
+      <c r="N11" s="3">
         <v>1</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>2679</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>2680</v>
-      </c>
-      <c r="N11" s="2">
-        <v>1</v>
-      </c>
-      <c r="O11" s="2" t="s">
+      <c r="O11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="P11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q11" s="2" t="s">
+      <c r="P11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q11" s="3" t="s">
         <v>2212</v>
       </c>
       <c r="R11" s="2"/>
@@ -43348,42 +44497,44 @@
       <c r="AD11" s="2"/>
     </row>
     <row r="12" spans="1:30" ht="15" customHeight="true">
-      <c r="A12" s="2"/>
+      <c r="A12" s="3">
+        <v>543</v>
+      </c>
       <c r="B12" s="2" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>2682</v>
+        <v>2678</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>2683</v>
+        <v>2679</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>2684</v>
+        <v>2680</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>62</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>2685</v>
+        <v>2681</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>2686</v>
+        <v>2682</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>2687</v>
+        <v>2683</v>
       </c>
       <c r="K12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>2689</v>
+        <v>2685</v>
       </c>
       <c r="N12" s="2">
         <v>1</v>
@@ -43422,42 +44573,44 @@
       <c r="AD12" s="2"/>
     </row>
     <row r="13" spans="1:30" ht="15" customHeight="true">
-      <c r="A13" s="2"/>
+      <c r="A13" s="3">
+        <v>544</v>
+      </c>
       <c r="B13" s="2" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>2690</v>
+        <v>2686</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>2683</v>
+        <v>2679</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>2691</v>
+        <v>2687</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>2685</v>
+        <v>2681</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>2692</v>
+        <v>2688</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
       <c r="K13" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>2694</v>
+        <v>2690</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>2689</v>
+        <v>2685</v>
       </c>
       <c r="N13" s="2">
         <v>1</v>
@@ -43496,42 +44649,44 @@
       <c r="AD13" s="2"/>
     </row>
     <row r="14" spans="1:30" ht="15" customHeight="true">
-      <c r="A14" s="2"/>
+      <c r="A14" s="3">
+        <v>545</v>
+      </c>
       <c r="B14" s="2" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>2695</v>
+        <v>2691</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>2683</v>
+        <v>2679</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>2696</v>
+        <v>2692</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>62</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>2685</v>
+        <v>2681</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>2697</v>
+        <v>2693</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>2698</v>
+        <v>2694</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>2699</v>
+        <v>2695</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>2689</v>
+        <v>2685</v>
       </c>
       <c r="N14" s="2">
         <v>1</v>
@@ -43570,53 +44725,55 @@
       <c r="AD14" s="2"/>
     </row>
     <row r="15" spans="1:30" ht="15" customHeight="true">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="3" t="s">
+        <v>2735</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>2243</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>2243</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
+        <v>2696</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>2697</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>2698</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>2699</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>2700</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="J15" s="3" t="s">
+        <v>2736</v>
+      </c>
+      <c r="K15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>2737</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>2701</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>2702</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>2703</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>2704</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>2705</v>
-      </c>
-      <c r="K15" s="2" t="b">
+      <c r="N15" s="3">
         <v>1</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>2706</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>2707</v>
-      </c>
-      <c r="N15" s="2">
-        <v>1</v>
-      </c>
-      <c r="O15" s="2" t="s">
+      <c r="O15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q15" s="2" t="s">
+      <c r="P15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q15" s="3" t="s">
         <v>2212</v>
       </c>
       <c r="R15" s="2"/>
@@ -43644,7 +44801,9 @@
       <c r="AD15" s="2"/>
     </row>
     <row r="16" spans="1:30" ht="15" customHeight="true">
-      <c r="A16" s="2"/>
+      <c r="A16" s="3">
+        <v>547</v>
+      </c>
       <c r="B16" s="2" t="s">
         <v>2243</v>
       </c>
@@ -43652,13 +44811,13 @@
         <v>2243</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>2709</v>
+        <v>2703</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>2710</v>
+        <v>2704</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>62</v>
@@ -43667,16 +44826,16 @@
         <v>62</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>2711</v>
+        <v>2705</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>2712</v>
+        <v>2706</v>
       </c>
       <c r="K16" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>2713</v>
+        <v>2707</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>279</v>
@@ -43718,12 +44877,14 @@
       <c r="AD16" s="2"/>
     </row>
     <row r="17" spans="1:30" ht="15" customHeight="true">
-      <c r="A17" s="2"/>
+      <c r="A17" s="3">
+        <v>548</v>
+      </c>
       <c r="B17" s="2" t="s">
-        <v>2714</v>
+        <v>2708</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>2714</v>
+        <v>2708</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>2650</v>
@@ -43741,10 +44902,10 @@
         <v>1478</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>2715</v>
+        <v>2709</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>2716</v>
+        <v>2710</v>
       </c>
       <c r="K17" s="2" t="b">
         <v>1</v>
@@ -43753,7 +44914,7 @@
         <v>1748</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>2717</v>
+        <v>2711</v>
       </c>
       <c r="N17" s="2">
         <v>1</v>
@@ -43792,15 +44953,17 @@
       <c r="AD17" s="2"/>
     </row>
     <row r="18" spans="1:30" ht="15" customHeight="true">
-      <c r="A18" s="2"/>
+      <c r="A18" s="3">
+        <v>549</v>
+      </c>
       <c r="B18" s="2" t="s">
-        <v>2714</v>
+        <v>2708</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>2714</v>
+        <v>2708</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>2718</v>
+        <v>2712</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>1739</v>
@@ -43815,19 +44978,19 @@
         <v>2646</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>2719</v>
+        <v>2713</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>2720</v>
+        <v>2714</v>
       </c>
       <c r="K18" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>2721</v>
+        <v>2715</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>2717</v>
+        <v>2711</v>
       </c>
       <c r="N18" s="2">
         <v>1</v>
@@ -43866,7 +45029,9 @@
       <c r="AD18" s="2"/>
     </row>
     <row r="19" spans="1:30" ht="15" customHeight="true">
-      <c r="A19" s="2"/>
+      <c r="A19" s="3">
+        <v>550</v>
+      </c>
       <c r="B19" s="2" t="s">
         <v>1428</v>
       </c>
@@ -43874,13 +45039,13 @@
         <v>1428</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>2722</v>
+        <v>2716</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>2723</v>
+        <v>2717</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>2724</v>
+        <v>2718</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>62</v>
@@ -43889,19 +45054,19 @@
         <v>1364</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>2725</v>
+        <v>2719</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>2726</v>
+        <v>2720</v>
       </c>
       <c r="K19" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>2727</v>
+        <v>2721</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>2728</v>
+        <v>2722</v>
       </c>
       <c r="N19" s="2">
         <v>1</v>
@@ -43940,7 +45105,9 @@
       <c r="AD19" s="2"/>
     </row>
     <row r="20" spans="1:30" ht="15" customHeight="true">
-      <c r="A20" s="2"/>
+      <c r="A20" s="3">
+        <v>551</v>
+      </c>
       <c r="B20" s="2" t="s">
         <v>1428</v>
       </c>
@@ -43948,13 +45115,13 @@
         <v>1428</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>2729</v>
+        <v>2723</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>2730</v>
+        <v>2724</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>2731</v>
+        <v>2725</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>62</v>
@@ -43963,19 +45130,19 @@
         <v>100</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>2732</v>
+        <v>2726</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>2733</v>
+        <v>2727</v>
       </c>
       <c r="K20" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>2734</v>
+        <v>2728</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>2735</v>
+        <v>2729</v>
       </c>
       <c r="N20" s="2">
         <v>1</v>
@@ -44014,7 +45181,9 @@
       <c r="AD20" s="2"/>
     </row>
     <row r="21" spans="1:30" ht="15" customHeight="true">
-      <c r="A21" s="2"/>
+      <c r="A21" s="3">
+        <v>552</v>
+      </c>
       <c r="B21" s="2" t="s">
         <v>1428</v>
       </c>
@@ -44022,13 +45191,13 @@
         <v>1428</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>2736</v>
+        <v>2730</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>2730</v>
+        <v>2724</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>2731</v>
+        <v>2725</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>257</v>
@@ -44037,19 +45206,19 @@
         <v>372</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>2737</v>
+        <v>2731</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>2738</v>
+        <v>2732</v>
       </c>
       <c r="K21" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>2739</v>
+        <v>2733</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>2740</v>
+        <v>2734</v>
       </c>
       <c r="N21" s="2">
         <v>1</v>
